--- a/artfynd/A 36883-2023 artfynd.xlsx
+++ b/artfynd/A 36883-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36883-2023 artfynd.xlsx
+++ b/artfynd/A 36883-2023 artfynd.xlsx
@@ -3666,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118601727</v>
+        <v>118601658</v>
       </c>
       <c r="B30" t="n">
-        <v>78220</v>
+        <v>78518</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466269</v>
+        <v>466276</v>
       </c>
       <c r="R30" t="n">
-        <v>6821081</v>
+        <v>6820477</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3768,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118601813</v>
+        <v>118601727</v>
       </c>
       <c r="B31" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466463</v>
+        <v>466269</v>
       </c>
       <c r="R31" t="n">
-        <v>6820672</v>
+        <v>6821081</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118601658</v>
+        <v>118601813</v>
       </c>
       <c r="B32" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3886,21 +3886,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466276</v>
+        <v>466463</v>
       </c>
       <c r="R32" t="n">
-        <v>6820477</v>
+        <v>6820672</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4903,7 +4903,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118601842</v>
+        <v>118601825</v>
       </c>
       <c r="B42" t="n">
         <v>78484</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466394</v>
+        <v>466450</v>
       </c>
       <c r="R42" t="n">
-        <v>6820329</v>
+        <v>6820356</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5005,10 +5005,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118601671</v>
+        <v>118601842</v>
       </c>
       <c r="B43" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5021,21 +5021,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466329</v>
+        <v>466394</v>
       </c>
       <c r="R43" t="n">
-        <v>6820672</v>
+        <v>6820329</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5107,10 +5107,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118601772</v>
+        <v>118601671</v>
       </c>
       <c r="B44" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5123,21 +5123,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466213</v>
+        <v>466329</v>
       </c>
       <c r="R44" t="n">
-        <v>6820752</v>
+        <v>6820672</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5209,10 +5209,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118601703</v>
+        <v>118601772</v>
       </c>
       <c r="B45" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5225,42 +5225,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466470</v>
+        <v>466213</v>
       </c>
       <c r="R45" t="n">
-        <v>6820354</v>
+        <v>6820752</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5293,11 +5285,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5426,10 +5413,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118601825</v>
+        <v>118601703</v>
       </c>
       <c r="B47" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5442,34 +5429,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466450</v>
+        <v>466470</v>
       </c>
       <c r="R47" t="n">
-        <v>6820356</v>
+        <v>6820354</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5502,6 +5497,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5528,10 +5528,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118601809</v>
+        <v>118601686</v>
       </c>
       <c r="B48" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5544,21 +5544,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5568,10 +5568,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466431</v>
+        <v>466290</v>
       </c>
       <c r="R48" t="n">
-        <v>6820682</v>
+        <v>6820662</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5630,7 +5630,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118601811</v>
+        <v>118601835</v>
       </c>
       <c r="B49" t="n">
         <v>78484</v>
@@ -5670,10 +5670,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466447</v>
+        <v>466455</v>
       </c>
       <c r="R49" t="n">
-        <v>6820672</v>
+        <v>6820335</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5732,7 +5732,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118601771</v>
+        <v>118601809</v>
       </c>
       <c r="B50" t="n">
         <v>78484</v>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466259</v>
+        <v>466431</v>
       </c>
       <c r="R50" t="n">
-        <v>6820893</v>
+        <v>6820682</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118601739</v>
+        <v>118601811</v>
       </c>
       <c r="B51" t="n">
         <v>78484</v>
@@ -5874,10 +5874,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>466404</v>
+        <v>466447</v>
       </c>
       <c r="R51" t="n">
-        <v>6820864</v>
+        <v>6820672</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5936,7 +5936,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118601835</v>
+        <v>118601771</v>
       </c>
       <c r="B52" t="n">
         <v>78484</v>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>466455</v>
+        <v>466259</v>
       </c>
       <c r="R52" t="n">
-        <v>6820335</v>
+        <v>6820893</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6038,10 +6038,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118601686</v>
+        <v>118601739</v>
       </c>
       <c r="B53" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6054,21 +6054,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6078,10 +6078,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>466290</v>
+        <v>466404</v>
       </c>
       <c r="R53" t="n">
-        <v>6820662</v>
+        <v>6820864</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6140,10 +6140,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118601661</v>
+        <v>118601822</v>
       </c>
       <c r="B54" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6156,21 +6156,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>466471</v>
+        <v>466341</v>
       </c>
       <c r="R54" t="n">
-        <v>6820336</v>
+        <v>6820450</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6242,10 +6242,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118601722</v>
+        <v>118601679</v>
       </c>
       <c r="B55" t="n">
-        <v>78221</v>
+        <v>79102</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6258,21 +6258,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6282,10 +6282,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466289</v>
+        <v>466318</v>
       </c>
       <c r="R55" t="n">
-        <v>6820603</v>
+        <v>6820464</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6344,10 +6344,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118601822</v>
+        <v>118601722</v>
       </c>
       <c r="B56" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6360,21 +6360,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>466341</v>
+        <v>466289</v>
       </c>
       <c r="R56" t="n">
-        <v>6820450</v>
+        <v>6820603</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6446,10 +6446,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118601679</v>
+        <v>118601661</v>
       </c>
       <c r="B57" t="n">
-        <v>79102</v>
+        <v>78518</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6462,21 +6462,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6486,10 +6486,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466318</v>
+        <v>466471</v>
       </c>
       <c r="R57" t="n">
-        <v>6820464</v>
+        <v>6820336</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6650,7 +6650,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118601748</v>
+        <v>118601769</v>
       </c>
       <c r="B59" t="n">
         <v>78484</v>
@@ -6690,10 +6690,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466269</v>
+        <v>466252</v>
       </c>
       <c r="R59" t="n">
-        <v>6821098</v>
+        <v>6820916</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6752,7 +6752,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118601769</v>
+        <v>118601818</v>
       </c>
       <c r="B60" t="n">
         <v>78484</v>
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466252</v>
+        <v>466307</v>
       </c>
       <c r="R60" t="n">
-        <v>6820916</v>
+        <v>6820533</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6854,7 +6854,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118601818</v>
+        <v>118601748</v>
       </c>
       <c r="B61" t="n">
         <v>78484</v>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466307</v>
+        <v>466269</v>
       </c>
       <c r="R61" t="n">
-        <v>6820533</v>
+        <v>6821098</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8181,10 +8181,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118601834</v>
+        <v>118601657</v>
       </c>
       <c r="B74" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8197,21 +8197,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>466471</v>
+        <v>466303</v>
       </c>
       <c r="R74" t="n">
-        <v>6820336</v>
+        <v>6820542</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8283,7 +8283,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118601844</v>
+        <v>118601834</v>
       </c>
       <c r="B75" t="n">
         <v>78484</v>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>466418</v>
+        <v>466471</v>
       </c>
       <c r="R75" t="n">
-        <v>6820392</v>
+        <v>6820336</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8385,7 +8385,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118601765</v>
+        <v>118601844</v>
       </c>
       <c r="B76" t="n">
         <v>78484</v>
@@ -8425,10 +8425,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>466239</v>
+        <v>466418</v>
       </c>
       <c r="R76" t="n">
-        <v>6820936</v>
+        <v>6820392</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8487,7 +8487,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118601815</v>
+        <v>118601765</v>
       </c>
       <c r="B77" t="n">
         <v>78484</v>
@@ -8527,10 +8527,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>466490</v>
+        <v>466239</v>
       </c>
       <c r="R77" t="n">
-        <v>6820635</v>
+        <v>6820936</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8589,7 +8589,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118601843</v>
+        <v>118601815</v>
       </c>
       <c r="B78" t="n">
         <v>78484</v>
@@ -8629,10 +8629,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>466412</v>
+        <v>466490</v>
       </c>
       <c r="R78" t="n">
-        <v>6820369</v>
+        <v>6820635</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8691,10 +8691,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118601731</v>
+        <v>118601843</v>
       </c>
       <c r="B79" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8707,21 +8707,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8731,10 +8731,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>466306</v>
+        <v>466412</v>
       </c>
       <c r="R79" t="n">
-        <v>6820562</v>
+        <v>6820369</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8793,10 +8793,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118601706</v>
+        <v>118601731</v>
       </c>
       <c r="B80" t="n">
-        <v>57290</v>
+        <v>78220</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8809,42 +8809,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>466265</v>
+        <v>466306</v>
       </c>
       <c r="R80" t="n">
-        <v>6820475</v>
+        <v>6820562</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8877,11 +8869,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8908,7 +8895,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118601702</v>
+        <v>118601706</v>
       </c>
       <c r="B81" t="n">
         <v>57290</v>
@@ -8946,7 +8933,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -8956,10 +8943,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>466455</v>
+        <v>466265</v>
       </c>
       <c r="R81" t="n">
-        <v>6820642</v>
+        <v>6820475</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8996,7 +8983,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Färska ringhack (gran)</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9023,10 +9010,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118601657</v>
+        <v>118601702</v>
       </c>
       <c r="B82" t="n">
-        <v>78518</v>
+        <v>57290</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9039,34 +9026,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>466303</v>
+        <v>466455</v>
       </c>
       <c r="R82" t="n">
-        <v>6820542</v>
+        <v>6820642</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9099,6 +9094,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9852,10 +9852,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118601750</v>
+        <v>118601848</v>
       </c>
       <c r="B90" t="n">
-        <v>78484</v>
+        <v>94513</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9864,25 +9864,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9892,10 +9892,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>466256</v>
+        <v>466442</v>
       </c>
       <c r="R90" t="n">
-        <v>6821102</v>
+        <v>6820579</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9954,7 +9954,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118601814</v>
+        <v>118601750</v>
       </c>
       <c r="B91" t="n">
         <v>78484</v>
@@ -9994,10 +9994,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>466476</v>
+        <v>466256</v>
       </c>
       <c r="R91" t="n">
-        <v>6820673</v>
+        <v>6821102</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10056,7 +10056,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118601840</v>
+        <v>118601814</v>
       </c>
       <c r="B92" t="n">
         <v>78484</v>
@@ -10096,10 +10096,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>466421</v>
+        <v>466476</v>
       </c>
       <c r="R92" t="n">
-        <v>6820332</v>
+        <v>6820673</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10158,10 +10158,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118601673</v>
+        <v>118601840</v>
       </c>
       <c r="B93" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10174,21 +10174,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10198,10 +10198,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>466480</v>
+        <v>466421</v>
       </c>
       <c r="R93" t="n">
-        <v>6820672</v>
+        <v>6820332</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10260,10 +10260,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118601728</v>
+        <v>118601673</v>
       </c>
       <c r="B94" t="n">
-        <v>78220</v>
+        <v>79102</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10276,21 +10276,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10300,10 +10300,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>466290</v>
+        <v>466480</v>
       </c>
       <c r="R94" t="n">
-        <v>6820662</v>
+        <v>6820672</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10362,10 +10362,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118601668</v>
+        <v>118601728</v>
       </c>
       <c r="B95" t="n">
-        <v>79102</v>
+        <v>78220</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10378,21 +10378,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10402,10 +10402,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>466198</v>
+        <v>466290</v>
       </c>
       <c r="R95" t="n">
-        <v>6820787</v>
+        <v>6820662</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10464,7 +10464,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118601666</v>
+        <v>118601668</v>
       </c>
       <c r="B96" t="n">
         <v>79102</v>
@@ -10504,10 +10504,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>466233</v>
+        <v>466198</v>
       </c>
       <c r="R96" t="n">
-        <v>6821097</v>
+        <v>6820787</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10566,10 +10566,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118601848</v>
+        <v>118601666</v>
       </c>
       <c r="B97" t="n">
-        <v>94513</v>
+        <v>79102</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10578,25 +10578,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>466442</v>
+        <v>466233</v>
       </c>
       <c r="R97" t="n">
-        <v>6820579</v>
+        <v>6821097</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10668,10 +10668,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118601850</v>
+        <v>118601841</v>
       </c>
       <c r="B98" t="n">
-        <v>78129</v>
+        <v>78484</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10684,21 +10684,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10708,10 +10708,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>466318</v>
+        <v>466411</v>
       </c>
       <c r="R98" t="n">
-        <v>6820439</v>
+        <v>6820346</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10770,10 +10770,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118601688</v>
+        <v>118601680</v>
       </c>
       <c r="B99" t="n">
-        <v>79073</v>
+        <v>79102</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10786,21 +10786,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10810,10 +10810,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>466309</v>
+        <v>466464</v>
       </c>
       <c r="R99" t="n">
-        <v>6820526</v>
+        <v>6820342</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10872,7 +10872,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118601801</v>
+        <v>118601845</v>
       </c>
       <c r="B100" t="n">
         <v>78484</v>
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>466410</v>
+        <v>466405</v>
       </c>
       <c r="R100" t="n">
-        <v>6820722</v>
+        <v>6820389</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10974,7 +10974,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118601777</v>
+        <v>118601801</v>
       </c>
       <c r="B101" t="n">
         <v>78484</v>
@@ -11014,10 +11014,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>466261</v>
+        <v>466410</v>
       </c>
       <c r="R101" t="n">
-        <v>6820701</v>
+        <v>6820722</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11076,7 +11076,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118601841</v>
+        <v>118601777</v>
       </c>
       <c r="B102" t="n">
         <v>78484</v>
@@ -11116,10 +11116,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>466411</v>
+        <v>466261</v>
       </c>
       <c r="R102" t="n">
-        <v>6820346</v>
+        <v>6820701</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11178,10 +11178,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118601680</v>
+        <v>118601850</v>
       </c>
       <c r="B103" t="n">
-        <v>79102</v>
+        <v>78129</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11194,21 +11194,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11218,10 +11218,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>466464</v>
+        <v>466318</v>
       </c>
       <c r="R103" t="n">
-        <v>6820342</v>
+        <v>6820439</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11280,10 +11280,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118601845</v>
+        <v>118601688</v>
       </c>
       <c r="B104" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11296,21 +11296,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11320,10 +11320,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>466405</v>
+        <v>466309</v>
       </c>
       <c r="R104" t="n">
-        <v>6820389</v>
+        <v>6820526</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11382,10 +11382,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118601698</v>
+        <v>118601780</v>
       </c>
       <c r="B105" t="n">
-        <v>57443</v>
+        <v>78484</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11398,21 +11398,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11422,10 +11422,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>466319</v>
+        <v>466301</v>
       </c>
       <c r="R105" t="n">
-        <v>6820440</v>
+        <v>6820686</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11484,7 +11484,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118601780</v>
+        <v>118601791</v>
       </c>
       <c r="B106" t="n">
         <v>78484</v>
@@ -11524,10 +11524,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>466301</v>
+        <v>466470</v>
       </c>
       <c r="R106" t="n">
-        <v>6820686</v>
+        <v>6820774</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11586,7 +11586,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118601791</v>
+        <v>118601774</v>
       </c>
       <c r="B107" t="n">
         <v>78484</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>466470</v>
+        <v>466223</v>
       </c>
       <c r="R107" t="n">
-        <v>6820774</v>
+        <v>6820728</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11688,10 +11688,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118601774</v>
+        <v>118601700</v>
       </c>
       <c r="B108" t="n">
-        <v>78484</v>
+        <v>78573</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11700,25 +11700,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11728,10 +11728,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>466223</v>
+        <v>466247</v>
       </c>
       <c r="R108" t="n">
-        <v>6820728</v>
+        <v>6821087</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11790,10 +11790,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118601700</v>
+        <v>118601724</v>
       </c>
       <c r="B109" t="n">
-        <v>78573</v>
+        <v>79565</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11802,25 +11802,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11830,10 +11830,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>466247</v>
+        <v>466276</v>
       </c>
       <c r="R109" t="n">
-        <v>6821087</v>
+        <v>6821068</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11892,10 +11892,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118601724</v>
+        <v>118601751</v>
       </c>
       <c r="B110" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11908,21 +11908,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11932,10 +11932,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>466276</v>
+        <v>466237</v>
       </c>
       <c r="R110" t="n">
-        <v>6821068</v>
+        <v>6821090</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11994,7 +11994,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118601751</v>
+        <v>118601755</v>
       </c>
       <c r="B111" t="n">
         <v>78484</v>
@@ -12034,10 +12034,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>466237</v>
+        <v>466248</v>
       </c>
       <c r="R111" t="n">
-        <v>6821090</v>
+        <v>6821008</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12096,10 +12096,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118601755</v>
+        <v>118601698</v>
       </c>
       <c r="B112" t="n">
-        <v>78484</v>
+        <v>57443</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12112,21 +12112,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12136,10 +12136,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>466248</v>
+        <v>466319</v>
       </c>
       <c r="R112" t="n">
-        <v>6821008</v>
+        <v>6820440</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13448,10 +13448,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118601685</v>
+        <v>118601721</v>
       </c>
       <c r="B125" t="n">
-        <v>79073</v>
+        <v>78221</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13464,21 +13464,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13488,10 +13488,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>466265</v>
+        <v>466487</v>
       </c>
       <c r="R125" t="n">
-        <v>6821100</v>
+        <v>6820641</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13550,10 +13550,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118601721</v>
+        <v>118601685</v>
       </c>
       <c r="B126" t="n">
-        <v>78221</v>
+        <v>79073</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13566,21 +13566,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13590,10 +13590,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>466487</v>
+        <v>466265</v>
       </c>
       <c r="R126" t="n">
-        <v>6820641</v>
+        <v>6821100</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -16407,10 +16407,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118601704</v>
+        <v>118601776</v>
       </c>
       <c r="B154" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16423,42 +16423,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>466415</v>
+        <v>466252</v>
       </c>
       <c r="R154" t="n">
-        <v>6820750</v>
+        <v>6820713</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16491,11 +16483,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16522,7 +16509,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>118601776</v>
+        <v>118601830</v>
       </c>
       <c r="B155" t="n">
         <v>78484</v>
@@ -16562,10 +16549,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>466252</v>
+        <v>466471</v>
       </c>
       <c r="R155" t="n">
-        <v>6820713</v>
+        <v>6820355</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16624,10 +16611,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>118601830</v>
+        <v>118601677</v>
       </c>
       <c r="B156" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16640,21 +16627,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16664,10 +16651,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>466471</v>
+        <v>466318</v>
       </c>
       <c r="R156" t="n">
-        <v>6820355</v>
+        <v>6820439</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16726,10 +16713,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>118601677</v>
+        <v>118601749</v>
       </c>
       <c r="B157" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16742,21 +16729,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16766,10 +16753,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>466318</v>
+        <v>466261</v>
       </c>
       <c r="R157" t="n">
-        <v>6820439</v>
+        <v>6821105</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16828,10 +16815,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>118601749</v>
+        <v>118601669</v>
       </c>
       <c r="B158" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16844,21 +16831,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16868,10 +16855,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>466261</v>
+        <v>466233</v>
       </c>
       <c r="R158" t="n">
-        <v>6821105</v>
+        <v>6820720</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16930,10 +16917,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>118601669</v>
+        <v>118601730</v>
       </c>
       <c r="B159" t="n">
-        <v>79102</v>
+        <v>78220</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16946,21 +16933,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16970,10 +16957,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>466233</v>
+        <v>466330</v>
       </c>
       <c r="R159" t="n">
-        <v>6820720</v>
+        <v>6820558</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17032,10 +17019,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>118601730</v>
+        <v>118601682</v>
       </c>
       <c r="B160" t="n">
-        <v>78220</v>
+        <v>79102</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17048,21 +17035,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17072,10 +17059,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>466330</v>
+        <v>466381</v>
       </c>
       <c r="R160" t="n">
-        <v>6820558</v>
+        <v>6820326</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17134,10 +17121,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>118601682</v>
+        <v>118601704</v>
       </c>
       <c r="B161" t="n">
-        <v>79102</v>
+        <v>57290</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17150,34 +17137,42 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>466381</v>
+        <v>466415</v>
       </c>
       <c r="R161" t="n">
-        <v>6820326</v>
+        <v>6820750</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17210,6 +17205,11 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 36883-2023 artfynd.xlsx
+++ b/artfynd/A 36883-2023 artfynd.xlsx
@@ -3666,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118601658</v>
+        <v>118601827</v>
       </c>
       <c r="B30" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466276</v>
+        <v>466466</v>
       </c>
       <c r="R30" t="n">
-        <v>6820477</v>
+        <v>6820369</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3768,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118601727</v>
+        <v>118601661</v>
       </c>
       <c r="B31" t="n">
-        <v>78220</v>
+        <v>78518</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466269</v>
+        <v>466471</v>
       </c>
       <c r="R31" t="n">
-        <v>6821081</v>
+        <v>6820336</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3870,7 +3870,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118601813</v>
+        <v>118601802</v>
       </c>
       <c r="B32" t="n">
         <v>78484</v>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466463</v>
+        <v>466418</v>
       </c>
       <c r="R32" t="n">
-        <v>6820672</v>
+        <v>6820718</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118601732</v>
+        <v>118601752</v>
       </c>
       <c r="B34" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4090,21 +4090,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466287</v>
+        <v>466250</v>
       </c>
       <c r="R34" t="n">
-        <v>6820603</v>
+        <v>6821077</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118601696</v>
+        <v>118601766</v>
       </c>
       <c r="B35" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4192,42 +4192,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466389</v>
+        <v>466247</v>
       </c>
       <c r="R35" t="n">
-        <v>6820384</v>
+        <v>6820929</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4260,11 +4252,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre bo (2-3 år gammalt)</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4291,7 +4278,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118601793</v>
+        <v>118601746</v>
       </c>
       <c r="B36" t="n">
         <v>78484</v>
@@ -4331,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466430</v>
+        <v>466284</v>
       </c>
       <c r="R36" t="n">
-        <v>6820757</v>
+        <v>6821043</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4393,10 +4380,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118601719</v>
+        <v>118601845</v>
       </c>
       <c r="B37" t="n">
-        <v>78510</v>
+        <v>78484</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4405,25 +4392,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4433,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466263</v>
+        <v>466405</v>
       </c>
       <c r="R37" t="n">
-        <v>6820456</v>
+        <v>6820389</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4495,10 +4482,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118601766</v>
+        <v>118601722</v>
       </c>
       <c r="B38" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4511,21 +4498,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4535,10 +4522,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466247</v>
+        <v>466289</v>
       </c>
       <c r="R38" t="n">
-        <v>6820929</v>
+        <v>6820603</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,10 +4584,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118601820</v>
+        <v>118601683</v>
       </c>
       <c r="B39" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4613,21 +4600,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4624,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466299</v>
+        <v>466307</v>
       </c>
       <c r="R39" t="n">
-        <v>6820534</v>
+        <v>6820562</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4681,6 +4668,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4699,7 +4687,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118601779</v>
+        <v>118601810</v>
       </c>
       <c r="B40" t="n">
         <v>78484</v>
@@ -4739,10 +4727,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466285</v>
+        <v>466440</v>
       </c>
       <c r="R40" t="n">
-        <v>6820690</v>
+        <v>6820675</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4801,7 +4789,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118601806</v>
+        <v>118601817</v>
       </c>
       <c r="B41" t="n">
         <v>78484</v>
@@ -4841,10 +4829,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466422</v>
+        <v>466344</v>
       </c>
       <c r="R41" t="n">
-        <v>6820680</v>
+        <v>6820520</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4903,10 +4891,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118601825</v>
+        <v>118601686</v>
       </c>
       <c r="B42" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4919,21 +4907,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4943,10 +4931,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466450</v>
+        <v>466290</v>
       </c>
       <c r="R42" t="n">
-        <v>6820356</v>
+        <v>6820662</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5005,10 +4993,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118601842</v>
+        <v>118601731</v>
       </c>
       <c r="B43" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5021,21 +5009,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5045,10 +5033,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466394</v>
+        <v>466306</v>
       </c>
       <c r="R43" t="n">
-        <v>6820329</v>
+        <v>6820562</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5107,10 +5095,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118601671</v>
+        <v>118601783</v>
       </c>
       <c r="B44" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5123,21 +5111,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5147,10 +5135,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466329</v>
+        <v>466420</v>
       </c>
       <c r="R44" t="n">
-        <v>6820672</v>
+        <v>6820743</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5209,7 +5197,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118601772</v>
+        <v>118601779</v>
       </c>
       <c r="B45" t="n">
         <v>78484</v>
@@ -5249,10 +5237,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466213</v>
+        <v>466285</v>
       </c>
       <c r="R45" t="n">
-        <v>6820752</v>
+        <v>6820690</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5311,10 +5299,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118601659</v>
+        <v>118601742</v>
       </c>
       <c r="B46" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5327,21 +5315,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5351,10 +5339,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466258</v>
+        <v>466344</v>
       </c>
       <c r="R46" t="n">
-        <v>6820476</v>
+        <v>6820993</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5413,10 +5401,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118601703</v>
+        <v>118601747</v>
       </c>
       <c r="B47" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5429,42 +5417,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466470</v>
+        <v>466278</v>
       </c>
       <c r="R47" t="n">
-        <v>6820354</v>
+        <v>6821064</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5497,11 +5477,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5528,10 +5503,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118601686</v>
+        <v>118601824</v>
       </c>
       <c r="B48" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5544,21 +5519,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5568,10 +5543,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466290</v>
+        <v>466445</v>
       </c>
       <c r="R48" t="n">
-        <v>6820662</v>
+        <v>6820355</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5630,7 +5605,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118601835</v>
+        <v>118601844</v>
       </c>
       <c r="B49" t="n">
         <v>78484</v>
@@ -5670,10 +5645,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466455</v>
+        <v>466418</v>
       </c>
       <c r="R49" t="n">
-        <v>6820335</v>
+        <v>6820392</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5732,7 +5707,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118601809</v>
+        <v>118601768</v>
       </c>
       <c r="B50" t="n">
         <v>78484</v>
@@ -5772,10 +5747,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466431</v>
+        <v>466260</v>
       </c>
       <c r="R50" t="n">
-        <v>6820682</v>
+        <v>6820919</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5834,10 +5809,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118601811</v>
+        <v>118601688</v>
       </c>
       <c r="B51" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5850,21 +5825,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5874,10 +5849,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>466447</v>
+        <v>466309</v>
       </c>
       <c r="R51" t="n">
-        <v>6820672</v>
+        <v>6820526</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5936,10 +5911,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118601771</v>
+        <v>118601720</v>
       </c>
       <c r="B52" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5952,21 +5927,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5976,10 +5951,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>466259</v>
+        <v>466331</v>
       </c>
       <c r="R52" t="n">
-        <v>6820893</v>
+        <v>6821018</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6038,7 +6013,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118601739</v>
+        <v>118601777</v>
       </c>
       <c r="B53" t="n">
         <v>78484</v>
@@ -6078,10 +6053,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>466404</v>
+        <v>466261</v>
       </c>
       <c r="R53" t="n">
-        <v>6820864</v>
+        <v>6820701</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6140,7 +6115,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118601822</v>
+        <v>118601753</v>
       </c>
       <c r="B54" t="n">
         <v>78484</v>
@@ -6180,10 +6155,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>466341</v>
+        <v>466257</v>
       </c>
       <c r="R54" t="n">
-        <v>6820450</v>
+        <v>6821074</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6242,10 +6217,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118601679</v>
+        <v>118601770</v>
       </c>
       <c r="B55" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6258,21 +6233,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6282,10 +6257,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466318</v>
+        <v>466256</v>
       </c>
       <c r="R55" t="n">
-        <v>6820464</v>
+        <v>6820907</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6344,10 +6319,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118601722</v>
+        <v>118601826</v>
       </c>
       <c r="B56" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6360,21 +6335,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6384,10 +6359,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>466289</v>
+        <v>466453</v>
       </c>
       <c r="R56" t="n">
-        <v>6820603</v>
+        <v>6820379</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6446,10 +6421,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118601661</v>
+        <v>118601841</v>
       </c>
       <c r="B57" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6462,21 +6437,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6486,10 +6461,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466471</v>
+        <v>466411</v>
       </c>
       <c r="R57" t="n">
-        <v>6820336</v>
+        <v>6820346</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6548,10 +6523,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118601775</v>
+        <v>118601664</v>
       </c>
       <c r="B58" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6564,21 +6539,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6588,10 +6563,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>466245</v>
+        <v>466402</v>
       </c>
       <c r="R58" t="n">
-        <v>6820718</v>
+        <v>6820391</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6650,10 +6625,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118601769</v>
+        <v>118601725</v>
       </c>
       <c r="B59" t="n">
-        <v>78484</v>
+        <v>77421</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6666,21 +6641,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6690,10 +6665,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466252</v>
+        <v>466297</v>
       </c>
       <c r="R59" t="n">
-        <v>6820916</v>
+        <v>6820527</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6734,6 +6709,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6752,10 +6728,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118601818</v>
+        <v>118601654</v>
       </c>
       <c r="B60" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6768,21 +6744,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6792,10 +6768,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466307</v>
+        <v>466318</v>
       </c>
       <c r="R60" t="n">
-        <v>6820533</v>
+        <v>6820669</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6854,10 +6830,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118601748</v>
+        <v>118601680</v>
       </c>
       <c r="B61" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6870,21 +6846,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6894,10 +6870,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466269</v>
+        <v>466464</v>
       </c>
       <c r="R61" t="n">
-        <v>6821098</v>
+        <v>6820342</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6956,7 +6932,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118601743</v>
+        <v>118601842</v>
       </c>
       <c r="B62" t="n">
         <v>78484</v>
@@ -6996,10 +6972,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466336</v>
+        <v>466394</v>
       </c>
       <c r="R62" t="n">
-        <v>6820998</v>
+        <v>6820329</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7058,7 +7034,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118601800</v>
+        <v>118601807</v>
       </c>
       <c r="B63" t="n">
         <v>78484</v>
@@ -7098,10 +7074,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>466414</v>
+        <v>466428</v>
       </c>
       <c r="R63" t="n">
-        <v>6820727</v>
+        <v>6820671</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7160,10 +7136,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118601810</v>
+        <v>118601726</v>
       </c>
       <c r="B64" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7176,21 +7152,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7200,10 +7176,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466440</v>
+        <v>466331</v>
       </c>
       <c r="R64" t="n">
-        <v>6820675</v>
+        <v>6821018</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7262,10 +7238,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118601819</v>
+        <v>118601727</v>
       </c>
       <c r="B65" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7278,21 +7254,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7302,10 +7278,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>466294</v>
+        <v>466269</v>
       </c>
       <c r="R65" t="n">
-        <v>6820528</v>
+        <v>6821081</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7364,7 +7340,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118601817</v>
+        <v>118601818</v>
       </c>
       <c r="B66" t="n">
         <v>78484</v>
@@ -7404,10 +7380,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>466344</v>
+        <v>466307</v>
       </c>
       <c r="R66" t="n">
-        <v>6820520</v>
+        <v>6820533</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7466,10 +7442,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118601792</v>
+        <v>118601734</v>
       </c>
       <c r="B67" t="n">
-        <v>78484</v>
+        <v>90522</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7482,21 +7458,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7506,10 +7482,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466431</v>
+        <v>466389</v>
       </c>
       <c r="R67" t="n">
-        <v>6820760</v>
+        <v>6820384</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7568,10 +7544,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118601664</v>
+        <v>118601744</v>
       </c>
       <c r="B68" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7584,21 +7560,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7608,10 +7584,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466402</v>
+        <v>466316</v>
       </c>
       <c r="R68" t="n">
-        <v>6820391</v>
+        <v>6821025</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7670,10 +7646,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118601663</v>
+        <v>118601831</v>
       </c>
       <c r="B69" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7686,21 +7662,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7710,10 +7686,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466405</v>
+        <v>466463</v>
       </c>
       <c r="R69" t="n">
-        <v>6820390</v>
+        <v>6820344</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7772,10 +7748,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118601690</v>
+        <v>118601809</v>
       </c>
       <c r="B70" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7788,21 +7764,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7812,10 +7788,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466438</v>
+        <v>466431</v>
       </c>
       <c r="R70" t="n">
-        <v>6820356</v>
+        <v>6820682</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7874,10 +7850,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118601734</v>
+        <v>118601750</v>
       </c>
       <c r="B71" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7890,21 +7866,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7914,10 +7890,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466389</v>
+        <v>466256</v>
       </c>
       <c r="R71" t="n">
-        <v>6820384</v>
+        <v>6821102</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7976,10 +7952,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118601855</v>
+        <v>118601836</v>
       </c>
       <c r="B72" t="n">
-        <v>5166</v>
+        <v>78484</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7988,25 +7964,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8019,7 +7995,7 @@
         <v>466454</v>
       </c>
       <c r="R72" t="n">
-        <v>6820379</v>
+        <v>6820333</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8078,7 +8054,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118601683</v>
+        <v>118601690</v>
       </c>
       <c r="B73" t="n">
         <v>79073</v>
@@ -8118,10 +8094,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>466307</v>
+        <v>466438</v>
       </c>
       <c r="R73" t="n">
-        <v>6820562</v>
+        <v>6820356</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8162,7 +8138,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8181,7 +8156,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118601657</v>
+        <v>118601660</v>
       </c>
       <c r="B74" t="n">
         <v>78518</v>
@@ -8221,10 +8196,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>466303</v>
+        <v>466432</v>
       </c>
       <c r="R74" t="n">
-        <v>6820542</v>
+        <v>6820354</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8283,10 +8258,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118601834</v>
+        <v>118601854</v>
       </c>
       <c r="B75" t="n">
-        <v>78484</v>
+        <v>5166</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8295,25 +8270,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8323,10 +8298,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>466471</v>
+        <v>466505</v>
       </c>
       <c r="R75" t="n">
-        <v>6820336</v>
+        <v>6820638</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8385,10 +8360,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118601844</v>
+        <v>118601715</v>
       </c>
       <c r="B76" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8401,34 +8376,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>466418</v>
+        <v>466440</v>
       </c>
       <c r="R76" t="n">
-        <v>6820392</v>
+        <v>6820684</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8461,6 +8444,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Två nyligen ringhackade granar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8487,10 +8475,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118601765</v>
+        <v>118601674</v>
       </c>
       <c r="B77" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8503,21 +8491,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8527,10 +8515,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>466239</v>
+        <v>466487</v>
       </c>
       <c r="R77" t="n">
-        <v>6820936</v>
+        <v>6820639</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8589,7 +8577,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118601815</v>
+        <v>118601846</v>
       </c>
       <c r="B78" t="n">
         <v>78484</v>
@@ -8629,10 +8617,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>466490</v>
+        <v>466402</v>
       </c>
       <c r="R78" t="n">
-        <v>6820635</v>
+        <v>6820391</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8691,7 +8679,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118601843</v>
+        <v>118601832</v>
       </c>
       <c r="B79" t="n">
         <v>78484</v>
@@ -8731,10 +8719,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>466412</v>
+        <v>466471</v>
       </c>
       <c r="R79" t="n">
-        <v>6820369</v>
+        <v>6820340</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8793,10 +8781,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118601731</v>
+        <v>118601685</v>
       </c>
       <c r="B80" t="n">
-        <v>78220</v>
+        <v>79073</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8809,21 +8797,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8833,10 +8821,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>466306</v>
+        <v>466265</v>
       </c>
       <c r="R80" t="n">
-        <v>6820562</v>
+        <v>6821100</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8895,10 +8883,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118601706</v>
+        <v>118601668</v>
       </c>
       <c r="B81" t="n">
-        <v>57290</v>
+        <v>79102</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8911,42 +8899,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>466265</v>
+        <v>466198</v>
       </c>
       <c r="R81" t="n">
-        <v>6820475</v>
+        <v>6820787</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8979,11 +8959,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9010,10 +8985,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118601702</v>
+        <v>118601801</v>
       </c>
       <c r="B82" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9026,42 +9001,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>466455</v>
+        <v>466410</v>
       </c>
       <c r="R82" t="n">
-        <v>6820642</v>
+        <v>6820722</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9094,11 +9061,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9125,10 +9087,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118601684</v>
+        <v>118601781</v>
       </c>
       <c r="B83" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9141,21 +9103,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9165,10 +9127,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>466268</v>
+        <v>466322</v>
       </c>
       <c r="R83" t="n">
-        <v>6821079</v>
+        <v>6820686</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9227,7 +9189,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118601768</v>
+        <v>118601835</v>
       </c>
       <c r="B84" t="n">
         <v>78484</v>
@@ -9267,10 +9229,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>466260</v>
+        <v>466455</v>
       </c>
       <c r="R84" t="n">
-        <v>6820919</v>
+        <v>6820335</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9329,7 +9291,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118601747</v>
+        <v>118601833</v>
       </c>
       <c r="B85" t="n">
         <v>78484</v>
@@ -9369,10 +9331,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>466278</v>
+        <v>466472</v>
       </c>
       <c r="R85" t="n">
-        <v>6821064</v>
+        <v>6820338</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9431,7 +9393,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118601790</v>
+        <v>118601771</v>
       </c>
       <c r="B86" t="n">
         <v>78484</v>
@@ -9471,10 +9433,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>466453</v>
+        <v>466259</v>
       </c>
       <c r="R86" t="n">
-        <v>6820774</v>
+        <v>6820893</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9533,7 +9495,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118601753</v>
+        <v>118601739</v>
       </c>
       <c r="B87" t="n">
         <v>78484</v>
@@ -9573,10 +9535,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>466257</v>
+        <v>466404</v>
       </c>
       <c r="R87" t="n">
-        <v>6821074</v>
+        <v>6820864</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9635,10 +9597,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118601802</v>
+        <v>118601848</v>
       </c>
       <c r="B88" t="n">
-        <v>78484</v>
+        <v>94513</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9647,25 +9609,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9675,10 +9637,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>466418</v>
+        <v>466442</v>
       </c>
       <c r="R88" t="n">
-        <v>6820718</v>
+        <v>6820579</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9737,10 +9699,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118601715</v>
+        <v>118601657</v>
       </c>
       <c r="B89" t="n">
-        <v>57290</v>
+        <v>78518</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9753,42 +9715,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>466440</v>
+        <v>466303</v>
       </c>
       <c r="R89" t="n">
-        <v>6820684</v>
+        <v>6820542</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9821,11 +9775,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Två nyligen ringhackade granar</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9852,10 +9801,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118601848</v>
+        <v>118601754</v>
       </c>
       <c r="B90" t="n">
-        <v>94513</v>
+        <v>78484</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9864,25 +9813,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9892,10 +9841,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>466442</v>
+        <v>466257</v>
       </c>
       <c r="R90" t="n">
-        <v>6820579</v>
+        <v>6821042</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9954,10 +9903,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118601750</v>
+        <v>118601666</v>
       </c>
       <c r="B91" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9970,21 +9919,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9994,10 +9943,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>466256</v>
+        <v>466233</v>
       </c>
       <c r="R91" t="n">
-        <v>6821102</v>
+        <v>6821097</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10056,7 +10005,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118601814</v>
+        <v>118601840</v>
       </c>
       <c r="B92" t="n">
         <v>78484</v>
@@ -10096,10 +10045,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>466476</v>
+        <v>466421</v>
       </c>
       <c r="R92" t="n">
-        <v>6820673</v>
+        <v>6820332</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10158,7 +10107,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118601840</v>
+        <v>118601775</v>
       </c>
       <c r="B93" t="n">
         <v>78484</v>
@@ -10198,10 +10147,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>466421</v>
+        <v>466245</v>
       </c>
       <c r="R93" t="n">
-        <v>6820332</v>
+        <v>6820718</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10260,10 +10209,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118601673</v>
+        <v>118601704</v>
       </c>
       <c r="B94" t="n">
-        <v>79102</v>
+        <v>57290</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10276,34 +10225,42 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>466480</v>
+        <v>466415</v>
       </c>
       <c r="R94" t="n">
-        <v>6820672</v>
+        <v>6820750</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10336,6 +10293,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10362,10 +10324,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118601728</v>
+        <v>118601684</v>
       </c>
       <c r="B95" t="n">
-        <v>78220</v>
+        <v>79073</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10378,21 +10340,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10402,10 +10364,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>466290</v>
+        <v>466268</v>
       </c>
       <c r="R95" t="n">
-        <v>6820662</v>
+        <v>6821079</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10464,10 +10426,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118601668</v>
+        <v>118601721</v>
       </c>
       <c r="B96" t="n">
-        <v>79102</v>
+        <v>78221</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10480,21 +10442,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10504,10 +10466,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>466198</v>
+        <v>466487</v>
       </c>
       <c r="R96" t="n">
-        <v>6820787</v>
+        <v>6820641</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10566,7 +10528,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118601666</v>
+        <v>118601672</v>
       </c>
       <c r="B97" t="n">
         <v>79102</v>
@@ -10606,10 +10568,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>466233</v>
+        <v>466343</v>
       </c>
       <c r="R97" t="n">
-        <v>6821097</v>
+        <v>6820677</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10668,10 +10630,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118601841</v>
+        <v>118601700</v>
       </c>
       <c r="B98" t="n">
-        <v>78484</v>
+        <v>78573</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10680,25 +10642,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10708,10 +10670,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>466411</v>
+        <v>466247</v>
       </c>
       <c r="R98" t="n">
-        <v>6820346</v>
+        <v>6821087</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10770,10 +10732,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118601680</v>
+        <v>118601773</v>
       </c>
       <c r="B99" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10786,21 +10748,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10810,10 +10772,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>466464</v>
+        <v>466222</v>
       </c>
       <c r="R99" t="n">
-        <v>6820342</v>
+        <v>6820731</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10872,7 +10834,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118601845</v>
+        <v>118601823</v>
       </c>
       <c r="B100" t="n">
         <v>78484</v>
@@ -10912,10 +10874,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>466405</v>
+        <v>466416</v>
       </c>
       <c r="R100" t="n">
-        <v>6820389</v>
+        <v>6820391</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10974,10 +10936,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118601801</v>
+        <v>118601687</v>
       </c>
       <c r="B101" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10990,21 +10952,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11014,10 +10976,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>466410</v>
+        <v>466330</v>
       </c>
       <c r="R101" t="n">
-        <v>6820722</v>
+        <v>6820551</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11076,7 +11038,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118601777</v>
+        <v>118601819</v>
       </c>
       <c r="B102" t="n">
         <v>78484</v>
@@ -11116,10 +11078,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>466261</v>
+        <v>466294</v>
       </c>
       <c r="R102" t="n">
-        <v>6820701</v>
+        <v>6820528</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11178,10 +11140,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118601850</v>
+        <v>118601755</v>
       </c>
       <c r="B103" t="n">
-        <v>78129</v>
+        <v>78484</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11194,21 +11156,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11218,10 +11180,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>466318</v>
+        <v>466248</v>
       </c>
       <c r="R103" t="n">
-        <v>6820439</v>
+        <v>6821008</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11280,10 +11242,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118601688</v>
+        <v>118601811</v>
       </c>
       <c r="B104" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11296,21 +11258,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11320,10 +11282,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>466309</v>
+        <v>466447</v>
       </c>
       <c r="R104" t="n">
-        <v>6820526</v>
+        <v>6820672</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11382,10 +11344,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118601780</v>
+        <v>118601850</v>
       </c>
       <c r="B105" t="n">
-        <v>78484</v>
+        <v>78129</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11398,21 +11360,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11422,10 +11384,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>466301</v>
+        <v>466318</v>
       </c>
       <c r="R105" t="n">
-        <v>6820686</v>
+        <v>6820439</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11484,10 +11446,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118601791</v>
+        <v>118601695</v>
       </c>
       <c r="B106" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11500,34 +11462,42 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>466470</v>
+        <v>466298</v>
       </c>
       <c r="R106" t="n">
-        <v>6820774</v>
+        <v>6820554</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11560,6 +11530,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11586,7 +11561,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118601774</v>
+        <v>118601790</v>
       </c>
       <c r="B107" t="n">
         <v>78484</v>
@@ -11626,10 +11601,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>466223</v>
+        <v>466453</v>
       </c>
       <c r="R107" t="n">
-        <v>6820728</v>
+        <v>6820774</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11688,10 +11663,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118601700</v>
+        <v>118601793</v>
       </c>
       <c r="B108" t="n">
-        <v>78573</v>
+        <v>78484</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11700,25 +11675,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11728,10 +11703,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>466247</v>
+        <v>466430</v>
       </c>
       <c r="R108" t="n">
-        <v>6821087</v>
+        <v>6820757</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11790,10 +11765,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118601724</v>
+        <v>118601698</v>
       </c>
       <c r="B109" t="n">
-        <v>79565</v>
+        <v>57443</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11806,21 +11781,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11830,10 +11805,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>466276</v>
+        <v>466319</v>
       </c>
       <c r="R109" t="n">
-        <v>6821068</v>
+        <v>6820440</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11892,10 +11867,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118601751</v>
+        <v>118601658</v>
       </c>
       <c r="B110" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11908,21 +11883,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11932,10 +11907,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>466237</v>
+        <v>466276</v>
       </c>
       <c r="R110" t="n">
-        <v>6821090</v>
+        <v>6820477</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11994,10 +11969,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118601755</v>
+        <v>118601663</v>
       </c>
       <c r="B111" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12010,21 +11985,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12034,10 +12009,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>466248</v>
+        <v>466405</v>
       </c>
       <c r="R111" t="n">
-        <v>6821008</v>
+        <v>6820390</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12096,10 +12071,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118601698</v>
+        <v>118601702</v>
       </c>
       <c r="B112" t="n">
-        <v>57443</v>
+        <v>57290</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12112,34 +12087,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>466319</v>
+        <v>466455</v>
       </c>
       <c r="R112" t="n">
-        <v>6820440</v>
+        <v>6820642</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12172,6 +12155,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12198,10 +12186,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118601726</v>
+        <v>118601671</v>
       </c>
       <c r="B113" t="n">
-        <v>78220</v>
+        <v>79102</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12214,21 +12202,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12238,10 +12226,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>466331</v>
+        <v>466329</v>
       </c>
       <c r="R113" t="n">
-        <v>6821018</v>
+        <v>6820672</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12300,7 +12288,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118601831</v>
+        <v>118601800</v>
       </c>
       <c r="B114" t="n">
         <v>78484</v>
@@ -12340,10 +12328,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>466463</v>
+        <v>466414</v>
       </c>
       <c r="R114" t="n">
-        <v>6820344</v>
+        <v>6820727</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12402,7 +12390,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118601824</v>
+        <v>118601751</v>
       </c>
       <c r="B115" t="n">
         <v>78484</v>
@@ -12442,10 +12430,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>466445</v>
+        <v>466237</v>
       </c>
       <c r="R115" t="n">
-        <v>6820355</v>
+        <v>6821090</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12504,10 +12492,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118601770</v>
+        <v>118601728</v>
       </c>
       <c r="B116" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12520,21 +12508,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12544,10 +12532,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>466256</v>
+        <v>466290</v>
       </c>
       <c r="R116" t="n">
-        <v>6820907</v>
+        <v>6820662</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12606,10 +12594,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118601837</v>
+        <v>118601732</v>
       </c>
       <c r="B117" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12622,21 +12610,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12646,10 +12634,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>466436</v>
+        <v>466287</v>
       </c>
       <c r="R117" t="n">
-        <v>6820340</v>
+        <v>6820603</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12708,7 +12696,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118601807</v>
+        <v>118601813</v>
       </c>
       <c r="B118" t="n">
         <v>78484</v>
@@ -12748,10 +12736,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>466428</v>
+        <v>466463</v>
       </c>
       <c r="R118" t="n">
-        <v>6820671</v>
+        <v>6820672</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12810,7 +12798,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118601836</v>
+        <v>118601808</v>
       </c>
       <c r="B119" t="n">
         <v>78484</v>
@@ -12850,10 +12838,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>466454</v>
+        <v>466433</v>
       </c>
       <c r="R119" t="n">
-        <v>6820333</v>
+        <v>6820675</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12912,10 +12900,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118601713</v>
+        <v>118601812</v>
       </c>
       <c r="B120" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12928,42 +12916,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>466317</v>
+        <v>466454</v>
       </c>
       <c r="R120" t="n">
-        <v>6820668</v>
+        <v>6820670</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12996,11 +12976,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13027,10 +13002,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118601695</v>
+        <v>118601673</v>
       </c>
       <c r="B121" t="n">
-        <v>57290</v>
+        <v>79102</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13043,42 +13018,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>466298</v>
+        <v>466480</v>
       </c>
       <c r="R121" t="n">
-        <v>6820554</v>
+        <v>6820672</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13111,11 +13078,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13142,7 +13104,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118601746</v>
+        <v>118601806</v>
       </c>
       <c r="B122" t="n">
         <v>78484</v>
@@ -13182,10 +13144,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>466284</v>
+        <v>466422</v>
       </c>
       <c r="R122" t="n">
-        <v>6821043</v>
+        <v>6820680</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13244,10 +13206,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118601674</v>
+        <v>118601713</v>
       </c>
       <c r="B123" t="n">
-        <v>79102</v>
+        <v>57290</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13260,34 +13222,42 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>466487</v>
+        <v>466317</v>
       </c>
       <c r="R123" t="n">
-        <v>6820639</v>
+        <v>6820668</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13320,6 +13290,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13346,10 +13321,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118601799</v>
+        <v>118601706</v>
       </c>
       <c r="B124" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13362,34 +13337,42 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>466416</v>
+        <v>466265</v>
       </c>
       <c r="R124" t="n">
-        <v>6820728</v>
+        <v>6820475</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13422,6 +13405,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13448,10 +13436,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118601721</v>
+        <v>118601699</v>
       </c>
       <c r="B125" t="n">
-        <v>78221</v>
+        <v>90524</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13464,21 +13452,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13488,10 +13476,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>466487</v>
+        <v>466261</v>
       </c>
       <c r="R125" t="n">
-        <v>6820641</v>
+        <v>6821105</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13550,10 +13538,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118601685</v>
+        <v>118601825</v>
       </c>
       <c r="B126" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13566,21 +13554,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13590,10 +13578,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>466265</v>
+        <v>466450</v>
       </c>
       <c r="R126" t="n">
-        <v>6821100</v>
+        <v>6820356</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13652,7 +13640,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118601826</v>
+        <v>118601820</v>
       </c>
       <c r="B127" t="n">
         <v>78484</v>
@@ -13692,10 +13680,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>466453</v>
+        <v>466299</v>
       </c>
       <c r="R127" t="n">
-        <v>6820379</v>
+        <v>6820534</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13754,7 +13742,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118601752</v>
+        <v>118601837</v>
       </c>
       <c r="B128" t="n">
         <v>78484</v>
@@ -13794,10 +13782,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>466250</v>
+        <v>466436</v>
       </c>
       <c r="R128" t="n">
-        <v>6821077</v>
+        <v>6820340</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13856,7 +13844,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118601773</v>
+        <v>118601796</v>
       </c>
       <c r="B129" t="n">
         <v>78484</v>
@@ -13896,10 +13884,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>466222</v>
+        <v>466413</v>
       </c>
       <c r="R129" t="n">
-        <v>6820731</v>
+        <v>6820733</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13958,7 +13946,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118601846</v>
+        <v>118601745</v>
       </c>
       <c r="B130" t="n">
         <v>78484</v>
@@ -13998,10 +13986,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>466402</v>
+        <v>466308</v>
       </c>
       <c r="R130" t="n">
-        <v>6820391</v>
+        <v>6821040</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14060,7 +14048,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118601823</v>
+        <v>118601749</v>
       </c>
       <c r="B131" t="n">
         <v>78484</v>
@@ -14100,10 +14088,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>466416</v>
+        <v>466261</v>
       </c>
       <c r="R131" t="n">
-        <v>6820391</v>
+        <v>6821105</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14162,10 +14150,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118601778</v>
+        <v>118601669</v>
       </c>
       <c r="B132" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14178,21 +14166,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14202,10 +14190,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>466283</v>
+        <v>466233</v>
       </c>
       <c r="R132" t="n">
-        <v>6820697</v>
+        <v>6820720</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14264,7 +14252,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118601745</v>
+        <v>118601776</v>
       </c>
       <c r="B133" t="n">
         <v>78484</v>
@@ -14304,10 +14292,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>466308</v>
+        <v>466252</v>
       </c>
       <c r="R133" t="n">
-        <v>6821040</v>
+        <v>6820713</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14366,10 +14354,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118601796</v>
+        <v>118601696</v>
       </c>
       <c r="B134" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14382,34 +14370,42 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>466413</v>
+        <v>466389</v>
       </c>
       <c r="R134" t="n">
-        <v>6820733</v>
+        <v>6820384</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14442,6 +14438,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Äldre bo (2-3 år gammalt)</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14468,7 +14469,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118601812</v>
+        <v>118601748</v>
       </c>
       <c r="B135" t="n">
         <v>78484</v>
@@ -14508,10 +14509,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>466454</v>
+        <v>466269</v>
       </c>
       <c r="R135" t="n">
-        <v>6820670</v>
+        <v>6821098</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14570,10 +14571,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118601654</v>
+        <v>118601778</v>
       </c>
       <c r="B136" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14586,21 +14587,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14610,10 +14611,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>466318</v>
+        <v>466283</v>
       </c>
       <c r="R136" t="n">
-        <v>6820669</v>
+        <v>6820697</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14672,7 +14673,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118601742</v>
+        <v>118601830</v>
       </c>
       <c r="B137" t="n">
         <v>78484</v>
@@ -14712,10 +14713,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>466344</v>
+        <v>466471</v>
       </c>
       <c r="R137" t="n">
-        <v>6820993</v>
+        <v>6820355</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14774,10 +14775,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118601672</v>
+        <v>118601703</v>
       </c>
       <c r="B138" t="n">
-        <v>79102</v>
+        <v>57290</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14790,34 +14791,42 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>466343</v>
+        <v>466470</v>
       </c>
       <c r="R138" t="n">
-        <v>6820677</v>
+        <v>6820354</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14850,6 +14859,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14876,10 +14890,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118601781</v>
+        <v>118601677</v>
       </c>
       <c r="B139" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14892,21 +14906,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14916,10 +14930,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>466322</v>
+        <v>466318</v>
       </c>
       <c r="R139" t="n">
-        <v>6820686</v>
+        <v>6820439</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14978,10 +14992,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118601754</v>
+        <v>118601679</v>
       </c>
       <c r="B140" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14994,21 +15008,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15018,10 +15032,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>466257</v>
+        <v>466318</v>
       </c>
       <c r="R140" t="n">
-        <v>6821042</v>
+        <v>6820464</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15080,10 +15094,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118601720</v>
+        <v>118601724</v>
       </c>
       <c r="B141" t="n">
-        <v>78221</v>
+        <v>79565</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15096,21 +15110,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15120,10 +15134,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>466331</v>
+        <v>466276</v>
       </c>
       <c r="R141" t="n">
-        <v>6821018</v>
+        <v>6821068</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15182,10 +15196,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118601725</v>
+        <v>118601682</v>
       </c>
       <c r="B142" t="n">
-        <v>77421</v>
+        <v>79102</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15198,21 +15212,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228579</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15222,10 +15236,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>466297</v>
+        <v>466381</v>
       </c>
       <c r="R142" t="n">
-        <v>6820527</v>
+        <v>6820326</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15266,7 +15280,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15285,10 +15298,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118601854</v>
+        <v>118601828</v>
       </c>
       <c r="B143" t="n">
-        <v>5166</v>
+        <v>78484</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15297,25 +15310,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15325,10 +15338,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>466505</v>
+        <v>466454</v>
       </c>
       <c r="R143" t="n">
-        <v>6820638</v>
+        <v>6820362</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15387,7 +15400,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118601660</v>
+        <v>118601659</v>
       </c>
       <c r="B144" t="n">
         <v>78518</v>
@@ -15427,10 +15440,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>466432</v>
+        <v>466258</v>
       </c>
       <c r="R144" t="n">
-        <v>6820354</v>
+        <v>6820476</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15489,10 +15502,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118601699</v>
+        <v>118601780</v>
       </c>
       <c r="B145" t="n">
-        <v>90524</v>
+        <v>78484</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15505,21 +15518,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15529,10 +15542,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>466261</v>
+        <v>466301</v>
       </c>
       <c r="R145" t="n">
-        <v>6821105</v>
+        <v>6820686</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15591,7 +15604,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118601808</v>
+        <v>118601815</v>
       </c>
       <c r="B146" t="n">
         <v>78484</v>
@@ -15631,10 +15644,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>466433</v>
+        <v>466490</v>
       </c>
       <c r="R146" t="n">
-        <v>6820675</v>
+        <v>6820635</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15693,10 +15706,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118601832</v>
+        <v>118601855</v>
       </c>
       <c r="B147" t="n">
-        <v>78484</v>
+        <v>5166</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15705,25 +15718,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15733,10 +15746,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>466471</v>
+        <v>466454</v>
       </c>
       <c r="R147" t="n">
-        <v>6820340</v>
+        <v>6820379</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15795,7 +15808,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>118601828</v>
+        <v>118601765</v>
       </c>
       <c r="B148" t="n">
         <v>78484</v>
@@ -15835,10 +15848,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>466454</v>
+        <v>466239</v>
       </c>
       <c r="R148" t="n">
-        <v>6820362</v>
+        <v>6820936</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15897,7 +15910,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118601744</v>
+        <v>118601743</v>
       </c>
       <c r="B149" t="n">
         <v>78484</v>
@@ -15937,10 +15950,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>466316</v>
+        <v>466336</v>
       </c>
       <c r="R149" t="n">
-        <v>6821025</v>
+        <v>6820998</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15999,7 +16012,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118601833</v>
+        <v>118601769</v>
       </c>
       <c r="B150" t="n">
         <v>78484</v>
@@ -16039,10 +16052,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>466472</v>
+        <v>466252</v>
       </c>
       <c r="R150" t="n">
-        <v>6820338</v>
+        <v>6820916</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16101,7 +16114,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118601783</v>
+        <v>118601772</v>
       </c>
       <c r="B151" t="n">
         <v>78484</v>
@@ -16141,10 +16154,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>466420</v>
+        <v>466213</v>
       </c>
       <c r="R151" t="n">
-        <v>6820743</v>
+        <v>6820752</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16203,7 +16216,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118601827</v>
+        <v>118601834</v>
       </c>
       <c r="B152" t="n">
         <v>78484</v>
@@ -16243,10 +16256,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>466466</v>
+        <v>466471</v>
       </c>
       <c r="R152" t="n">
-        <v>6820369</v>
+        <v>6820336</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16305,10 +16318,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>118601687</v>
+        <v>118601843</v>
       </c>
       <c r="B153" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16321,21 +16334,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16345,10 +16358,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>466330</v>
+        <v>466412</v>
       </c>
       <c r="R153" t="n">
-        <v>6820551</v>
+        <v>6820369</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16407,10 +16420,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118601776</v>
+        <v>118601730</v>
       </c>
       <c r="B154" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16423,21 +16436,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16447,10 +16460,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>466252</v>
+        <v>466330</v>
       </c>
       <c r="R154" t="n">
-        <v>6820713</v>
+        <v>6820558</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16509,7 +16522,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>118601830</v>
+        <v>118601791</v>
       </c>
       <c r="B155" t="n">
         <v>78484</v>
@@ -16549,10 +16562,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>466471</v>
+        <v>466470</v>
       </c>
       <c r="R155" t="n">
-        <v>6820355</v>
+        <v>6820774</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16611,10 +16624,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>118601677</v>
+        <v>118601792</v>
       </c>
       <c r="B156" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16627,21 +16640,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16651,10 +16664,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>466318</v>
+        <v>466431</v>
       </c>
       <c r="R156" t="n">
-        <v>6820439</v>
+        <v>6820760</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16713,10 +16726,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>118601749</v>
+        <v>118601719</v>
       </c>
       <c r="B157" t="n">
-        <v>78484</v>
+        <v>78510</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16725,25 +16738,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16753,10 +16766,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>466261</v>
+        <v>466263</v>
       </c>
       <c r="R157" t="n">
-        <v>6821105</v>
+        <v>6820456</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16815,10 +16828,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>118601669</v>
+        <v>118601822</v>
       </c>
       <c r="B158" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16831,21 +16844,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16855,10 +16868,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>466233</v>
+        <v>466341</v>
       </c>
       <c r="R158" t="n">
-        <v>6820720</v>
+        <v>6820450</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16917,10 +16930,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>118601730</v>
+        <v>118601814</v>
       </c>
       <c r="B159" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16933,21 +16946,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16957,10 +16970,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>466330</v>
+        <v>466476</v>
       </c>
       <c r="R159" t="n">
-        <v>6820558</v>
+        <v>6820673</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17019,10 +17032,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>118601682</v>
+        <v>118601774</v>
       </c>
       <c r="B160" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17035,21 +17048,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17059,10 +17072,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>466381</v>
+        <v>466223</v>
       </c>
       <c r="R160" t="n">
-        <v>6820326</v>
+        <v>6820728</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17121,10 +17134,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>118601704</v>
+        <v>118601799</v>
       </c>
       <c r="B161" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17137,42 +17150,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>466415</v>
+        <v>466416</v>
       </c>
       <c r="R161" t="n">
-        <v>6820750</v>
+        <v>6820728</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17205,11 +17210,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 36883-2023 artfynd.xlsx
+++ b/artfynd/A 36883-2023 artfynd.xlsx
@@ -3666,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118601827</v>
+        <v>118601729</v>
       </c>
       <c r="B30" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466466</v>
+        <v>466487</v>
       </c>
       <c r="R30" t="n">
-        <v>6820369</v>
+        <v>6820641</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3768,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118601661</v>
+        <v>118601752</v>
       </c>
       <c r="B31" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466471</v>
+        <v>466250</v>
       </c>
       <c r="R31" t="n">
-        <v>6820336</v>
+        <v>6821077</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3870,7 +3870,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118601802</v>
+        <v>118601766</v>
       </c>
       <c r="B32" t="n">
         <v>78484</v>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466418</v>
+        <v>466247</v>
       </c>
       <c r="R32" t="n">
-        <v>6820718</v>
+        <v>6820929</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3972,10 +3972,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118601729</v>
+        <v>118601746</v>
       </c>
       <c r="B33" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3988,21 +3988,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466487</v>
+        <v>466284</v>
       </c>
       <c r="R33" t="n">
-        <v>6820641</v>
+        <v>6821043</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118601752</v>
+        <v>118601845</v>
       </c>
       <c r="B34" t="n">
         <v>78484</v>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466250</v>
+        <v>466405</v>
       </c>
       <c r="R34" t="n">
-        <v>6821077</v>
+        <v>6820389</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4176,7 +4176,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118601766</v>
+        <v>118601827</v>
       </c>
       <c r="B35" t="n">
         <v>78484</v>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466247</v>
+        <v>466466</v>
       </c>
       <c r="R35" t="n">
-        <v>6820929</v>
+        <v>6820369</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4278,7 +4278,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118601746</v>
+        <v>118601802</v>
       </c>
       <c r="B36" t="n">
         <v>78484</v>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466284</v>
+        <v>466418</v>
       </c>
       <c r="R36" t="n">
-        <v>6821043</v>
+        <v>6820718</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4380,10 +4380,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118601845</v>
+        <v>118601661</v>
       </c>
       <c r="B37" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466405</v>
+        <v>466471</v>
       </c>
       <c r="R37" t="n">
-        <v>6820389</v>
+        <v>6820336</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118601722</v>
+        <v>118601683</v>
       </c>
       <c r="B38" t="n">
-        <v>78221</v>
+        <v>79073</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4498,21 +4498,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466289</v>
+        <v>466307</v>
       </c>
       <c r="R38" t="n">
-        <v>6820603</v>
+        <v>6820562</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,6 +4566,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4584,10 +4585,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118601683</v>
+        <v>118601722</v>
       </c>
       <c r="B39" t="n">
-        <v>79073</v>
+        <v>78221</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4600,21 +4601,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4624,10 +4625,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466307</v>
+        <v>466289</v>
       </c>
       <c r="R39" t="n">
-        <v>6820562</v>
+        <v>6820603</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4668,7 +4669,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -6013,10 +6013,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118601777</v>
+        <v>118601664</v>
       </c>
       <c r="B53" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6029,21 +6029,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6053,10 +6053,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>466261</v>
+        <v>466402</v>
       </c>
       <c r="R53" t="n">
-        <v>6820701</v>
+        <v>6820391</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6115,7 +6115,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118601753</v>
+        <v>118601777</v>
       </c>
       <c r="B54" t="n">
         <v>78484</v>
@@ -6155,10 +6155,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>466257</v>
+        <v>466261</v>
       </c>
       <c r="R54" t="n">
-        <v>6821074</v>
+        <v>6820701</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6217,7 +6217,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118601770</v>
+        <v>118601753</v>
       </c>
       <c r="B55" t="n">
         <v>78484</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466256</v>
+        <v>466257</v>
       </c>
       <c r="R55" t="n">
-        <v>6820907</v>
+        <v>6821074</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6319,7 +6319,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118601826</v>
+        <v>118601770</v>
       </c>
       <c r="B56" t="n">
         <v>78484</v>
@@ -6359,10 +6359,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>466453</v>
+        <v>466256</v>
       </c>
       <c r="R56" t="n">
-        <v>6820379</v>
+        <v>6820907</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6421,7 +6421,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118601841</v>
+        <v>118601826</v>
       </c>
       <c r="B57" t="n">
         <v>78484</v>
@@ -6461,10 +6461,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466411</v>
+        <v>466453</v>
       </c>
       <c r="R57" t="n">
-        <v>6820346</v>
+        <v>6820379</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6523,10 +6523,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118601664</v>
+        <v>118601841</v>
       </c>
       <c r="B58" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6539,21 +6539,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6563,10 +6563,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>466402</v>
+        <v>466411</v>
       </c>
       <c r="R58" t="n">
-        <v>6820391</v>
+        <v>6820346</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8156,10 +8156,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118601660</v>
+        <v>118601854</v>
       </c>
       <c r="B74" t="n">
-        <v>78518</v>
+        <v>5166</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8168,25 +8168,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>466432</v>
+        <v>466505</v>
       </c>
       <c r="R74" t="n">
-        <v>6820354</v>
+        <v>6820638</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8258,10 +8258,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118601854</v>
+        <v>118601674</v>
       </c>
       <c r="B75" t="n">
-        <v>5166</v>
+        <v>79102</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8270,25 +8270,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8298,10 +8298,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>466505</v>
+        <v>466487</v>
       </c>
       <c r="R75" t="n">
-        <v>6820638</v>
+        <v>6820639</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8360,10 +8360,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118601715</v>
+        <v>118601846</v>
       </c>
       <c r="B76" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8376,42 +8376,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>466440</v>
+        <v>466402</v>
       </c>
       <c r="R76" t="n">
-        <v>6820684</v>
+        <v>6820391</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8444,11 +8436,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Två nyligen ringhackade granar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8475,10 +8462,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118601674</v>
+        <v>118601832</v>
       </c>
       <c r="B77" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8491,21 +8478,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8515,10 +8502,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>466487</v>
+        <v>466471</v>
       </c>
       <c r="R77" t="n">
-        <v>6820639</v>
+        <v>6820340</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8577,10 +8564,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118601846</v>
+        <v>118601660</v>
       </c>
       <c r="B78" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8593,21 +8580,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8617,10 +8604,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>466402</v>
+        <v>466432</v>
       </c>
       <c r="R78" t="n">
-        <v>6820391</v>
+        <v>6820354</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8679,10 +8666,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118601832</v>
+        <v>118601715</v>
       </c>
       <c r="B79" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8695,34 +8682,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>466471</v>
+        <v>466440</v>
       </c>
       <c r="R79" t="n">
-        <v>6820340</v>
+        <v>6820684</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8755,6 +8750,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Två nyligen ringhackade granar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9597,10 +9597,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118601848</v>
+        <v>118601666</v>
       </c>
       <c r="B88" t="n">
-        <v>94513</v>
+        <v>79102</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9609,25 +9609,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9637,10 +9637,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>466442</v>
+        <v>466233</v>
       </c>
       <c r="R88" t="n">
-        <v>6820579</v>
+        <v>6821097</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9699,10 +9699,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118601657</v>
+        <v>118601848</v>
       </c>
       <c r="B89" t="n">
-        <v>78518</v>
+        <v>94513</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9711,25 +9711,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>185</v>
+        <v>2170</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9739,10 +9739,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>466303</v>
+        <v>466442</v>
       </c>
       <c r="R89" t="n">
-        <v>6820542</v>
+        <v>6820579</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9801,7 +9801,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118601754</v>
+        <v>118601840</v>
       </c>
       <c r="B90" t="n">
         <v>78484</v>
@@ -9841,10 +9841,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>466257</v>
+        <v>466421</v>
       </c>
       <c r="R90" t="n">
-        <v>6821042</v>
+        <v>6820332</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9903,10 +9903,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118601666</v>
+        <v>118601775</v>
       </c>
       <c r="B91" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9919,21 +9919,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9943,10 +9943,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>466233</v>
+        <v>466245</v>
       </c>
       <c r="R91" t="n">
-        <v>6821097</v>
+        <v>6820718</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10005,7 +10005,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118601840</v>
+        <v>118601754</v>
       </c>
       <c r="B92" t="n">
         <v>78484</v>
@@ -10045,10 +10045,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>466421</v>
+        <v>466257</v>
       </c>
       <c r="R92" t="n">
-        <v>6820332</v>
+        <v>6821042</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10107,10 +10107,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118601775</v>
+        <v>118601657</v>
       </c>
       <c r="B93" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10123,21 +10123,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10147,10 +10147,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>466245</v>
+        <v>466303</v>
       </c>
       <c r="R93" t="n">
-        <v>6820718</v>
+        <v>6820542</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10936,10 +10936,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118601687</v>
+        <v>118601819</v>
       </c>
       <c r="B101" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10952,21 +10952,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10976,10 +10976,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>466330</v>
+        <v>466294</v>
       </c>
       <c r="R101" t="n">
-        <v>6820551</v>
+        <v>6820528</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11038,7 +11038,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118601819</v>
+        <v>118601755</v>
       </c>
       <c r="B102" t="n">
         <v>78484</v>
@@ -11078,10 +11078,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>466294</v>
+        <v>466248</v>
       </c>
       <c r="R102" t="n">
-        <v>6820528</v>
+        <v>6821008</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11140,10 +11140,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118601755</v>
+        <v>118601687</v>
       </c>
       <c r="B103" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11156,21 +11156,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11180,10 +11180,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>466248</v>
+        <v>466330</v>
       </c>
       <c r="R103" t="n">
-        <v>6821008</v>
+        <v>6820551</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11344,10 +11344,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118601850</v>
+        <v>118601793</v>
       </c>
       <c r="B105" t="n">
-        <v>78129</v>
+        <v>78484</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11360,21 +11360,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11384,10 +11384,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>466318</v>
+        <v>466430</v>
       </c>
       <c r="R105" t="n">
-        <v>6820439</v>
+        <v>6820757</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11446,10 +11446,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118601695</v>
+        <v>118601850</v>
       </c>
       <c r="B106" t="n">
-        <v>57290</v>
+        <v>78129</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11462,42 +11462,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>466298</v>
+        <v>466318</v>
       </c>
       <c r="R106" t="n">
-        <v>6820554</v>
+        <v>6820439</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11530,11 +11522,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11663,10 +11650,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118601793</v>
+        <v>118601695</v>
       </c>
       <c r="B108" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11679,34 +11666,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>466430</v>
+        <v>466298</v>
       </c>
       <c r="R108" t="n">
-        <v>6820757</v>
+        <v>6820554</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11739,6 +11734,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13002,10 +13002,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118601673</v>
+        <v>118601699</v>
       </c>
       <c r="B121" t="n">
-        <v>79102</v>
+        <v>90524</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13018,21 +13018,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13042,10 +13042,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>466480</v>
+        <v>466261</v>
       </c>
       <c r="R121" t="n">
-        <v>6820672</v>
+        <v>6821105</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13104,7 +13104,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118601806</v>
+        <v>118601796</v>
       </c>
       <c r="B122" t="n">
         <v>78484</v>
@@ -13144,10 +13144,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>466422</v>
+        <v>466413</v>
       </c>
       <c r="R122" t="n">
-        <v>6820680</v>
+        <v>6820733</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13436,10 +13436,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118601699</v>
+        <v>118601673</v>
       </c>
       <c r="B125" t="n">
-        <v>90524</v>
+        <v>79102</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13452,21 +13452,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13476,10 +13476,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>466261</v>
+        <v>466480</v>
       </c>
       <c r="R125" t="n">
-        <v>6821105</v>
+        <v>6820672</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13538,7 +13538,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118601825</v>
+        <v>118601806</v>
       </c>
       <c r="B126" t="n">
         <v>78484</v>
@@ -13578,10 +13578,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>466450</v>
+        <v>466422</v>
       </c>
       <c r="R126" t="n">
-        <v>6820356</v>
+        <v>6820680</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13640,7 +13640,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118601820</v>
+        <v>118601825</v>
       </c>
       <c r="B127" t="n">
         <v>78484</v>
@@ -13680,10 +13680,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>466299</v>
+        <v>466450</v>
       </c>
       <c r="R127" t="n">
-        <v>6820534</v>
+        <v>6820356</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13742,7 +13742,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118601837</v>
+        <v>118601820</v>
       </c>
       <c r="B128" t="n">
         <v>78484</v>
@@ -13782,10 +13782,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>466436</v>
+        <v>466299</v>
       </c>
       <c r="R128" t="n">
-        <v>6820340</v>
+        <v>6820534</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13844,7 +13844,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118601796</v>
+        <v>118601837</v>
       </c>
       <c r="B129" t="n">
         <v>78484</v>
@@ -13884,10 +13884,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>466413</v>
+        <v>466436</v>
       </c>
       <c r="R129" t="n">
-        <v>6820733</v>
+        <v>6820340</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15706,10 +15706,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118601855</v>
+        <v>118601765</v>
       </c>
       <c r="B147" t="n">
-        <v>5166</v>
+        <v>78484</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15718,25 +15718,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15746,10 +15746,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>466454</v>
+        <v>466239</v>
       </c>
       <c r="R147" t="n">
-        <v>6820379</v>
+        <v>6820936</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15808,7 +15808,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>118601765</v>
+        <v>118601743</v>
       </c>
       <c r="B148" t="n">
         <v>78484</v>
@@ -15848,10 +15848,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>466239</v>
+        <v>466336</v>
       </c>
       <c r="R148" t="n">
-        <v>6820936</v>
+        <v>6820998</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15910,7 +15910,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118601743</v>
+        <v>118601769</v>
       </c>
       <c r="B149" t="n">
         <v>78484</v>
@@ -15950,10 +15950,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>466336</v>
+        <v>466252</v>
       </c>
       <c r="R149" t="n">
-        <v>6820998</v>
+        <v>6820916</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16012,7 +16012,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118601769</v>
+        <v>118601772</v>
       </c>
       <c r="B150" t="n">
         <v>78484</v>
@@ -16052,10 +16052,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>466252</v>
+        <v>466213</v>
       </c>
       <c r="R150" t="n">
-        <v>6820916</v>
+        <v>6820752</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16114,7 +16114,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118601772</v>
+        <v>118601834</v>
       </c>
       <c r="B151" t="n">
         <v>78484</v>
@@ -16154,10 +16154,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>466213</v>
+        <v>466471</v>
       </c>
       <c r="R151" t="n">
-        <v>6820752</v>
+        <v>6820336</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16216,7 +16216,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118601834</v>
+        <v>118601843</v>
       </c>
       <c r="B152" t="n">
         <v>78484</v>
@@ -16256,10 +16256,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>466471</v>
+        <v>466412</v>
       </c>
       <c r="R152" t="n">
-        <v>6820336</v>
+        <v>6820369</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16318,10 +16318,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>118601843</v>
+        <v>118601855</v>
       </c>
       <c r="B153" t="n">
-        <v>78484</v>
+        <v>5166</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16330,25 +16330,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16358,10 +16358,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>466412</v>
+        <v>466454</v>
       </c>
       <c r="R153" t="n">
-        <v>6820369</v>
+        <v>6820379</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>

--- a/artfynd/A 36883-2023 artfynd.xlsx
+++ b/artfynd/A 36883-2023 artfynd.xlsx
@@ -3666,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118601729</v>
+        <v>118601666</v>
       </c>
       <c r="B30" t="n">
-        <v>78220</v>
+        <v>79102</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466487</v>
+        <v>466233</v>
       </c>
       <c r="R30" t="n">
-        <v>6820641</v>
+        <v>6821097</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3768,7 +3768,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118601752</v>
+        <v>118601841</v>
       </c>
       <c r="B31" t="n">
         <v>78484</v>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466250</v>
+        <v>466411</v>
       </c>
       <c r="R31" t="n">
-        <v>6821077</v>
+        <v>6820346</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3870,7 +3870,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118601766</v>
+        <v>118601809</v>
       </c>
       <c r="B32" t="n">
         <v>78484</v>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466247</v>
+        <v>466431</v>
       </c>
       <c r="R32" t="n">
-        <v>6820929</v>
+        <v>6820682</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118601746</v>
+        <v>118601810</v>
       </c>
       <c r="B33" t="n">
         <v>78484</v>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466284</v>
+        <v>466440</v>
       </c>
       <c r="R33" t="n">
-        <v>6821043</v>
+        <v>6820675</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118601845</v>
+        <v>118601819</v>
       </c>
       <c r="B34" t="n">
         <v>78484</v>
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466405</v>
+        <v>466294</v>
       </c>
       <c r="R34" t="n">
-        <v>6820389</v>
+        <v>6820528</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118601827</v>
+        <v>118601660</v>
       </c>
       <c r="B35" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4192,21 +4192,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466466</v>
+        <v>466432</v>
       </c>
       <c r="R35" t="n">
-        <v>6820369</v>
+        <v>6820354</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4278,7 +4278,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118601802</v>
+        <v>118601781</v>
       </c>
       <c r="B36" t="n">
         <v>78484</v>
@@ -4318,10 +4318,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466418</v>
+        <v>466322</v>
       </c>
       <c r="R36" t="n">
-        <v>6820718</v>
+        <v>6820686</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4380,10 +4380,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118601661</v>
+        <v>118601745</v>
       </c>
       <c r="B37" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466471</v>
+        <v>466308</v>
       </c>
       <c r="R37" t="n">
-        <v>6820336</v>
+        <v>6821040</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118601683</v>
+        <v>118601854</v>
       </c>
       <c r="B38" t="n">
-        <v>79073</v>
+        <v>5166</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4494,25 +4494,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466307</v>
+        <v>466505</v>
       </c>
       <c r="R38" t="n">
-        <v>6820562</v>
+        <v>6820638</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4585,10 +4584,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118601722</v>
+        <v>118601822</v>
       </c>
       <c r="B39" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4601,21 +4600,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4625,10 +4624,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466289</v>
+        <v>466341</v>
       </c>
       <c r="R39" t="n">
-        <v>6820603</v>
+        <v>6820450</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4687,7 +4686,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118601810</v>
+        <v>118601834</v>
       </c>
       <c r="B40" t="n">
         <v>78484</v>
@@ -4727,10 +4726,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466440</v>
+        <v>466471</v>
       </c>
       <c r="R40" t="n">
-        <v>6820675</v>
+        <v>6820336</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4789,7 +4788,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118601817</v>
+        <v>118601754</v>
       </c>
       <c r="B41" t="n">
         <v>78484</v>
@@ -4829,10 +4828,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466344</v>
+        <v>466257</v>
       </c>
       <c r="R41" t="n">
-        <v>6820520</v>
+        <v>6821042</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4891,10 +4890,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118601686</v>
+        <v>118601679</v>
       </c>
       <c r="B42" t="n">
-        <v>79073</v>
+        <v>79102</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4907,21 +4906,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4931,10 +4930,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466290</v>
+        <v>466318</v>
       </c>
       <c r="R42" t="n">
-        <v>6820662</v>
+        <v>6820464</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,7 +4992,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118601731</v>
+        <v>118601729</v>
       </c>
       <c r="B43" t="n">
         <v>78220</v>
@@ -5033,10 +5032,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466306</v>
+        <v>466487</v>
       </c>
       <c r="R43" t="n">
-        <v>6820562</v>
+        <v>6820641</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5095,10 +5094,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118601783</v>
+        <v>118601690</v>
       </c>
       <c r="B44" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5111,21 +5110,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5135,10 +5134,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466420</v>
+        <v>466438</v>
       </c>
       <c r="R44" t="n">
-        <v>6820743</v>
+        <v>6820356</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5197,7 +5196,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118601779</v>
+        <v>118601749</v>
       </c>
       <c r="B45" t="n">
         <v>78484</v>
@@ -5237,10 +5236,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466285</v>
+        <v>466261</v>
       </c>
       <c r="R45" t="n">
-        <v>6820690</v>
+        <v>6821105</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5299,7 +5298,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118601742</v>
+        <v>118601832</v>
       </c>
       <c r="B46" t="n">
         <v>78484</v>
@@ -5339,10 +5338,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466344</v>
+        <v>466471</v>
       </c>
       <c r="R46" t="n">
-        <v>6820993</v>
+        <v>6820340</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5401,10 +5400,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118601747</v>
+        <v>118601685</v>
       </c>
       <c r="B47" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5417,21 +5416,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5441,10 +5440,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466278</v>
+        <v>466265</v>
       </c>
       <c r="R47" t="n">
-        <v>6821064</v>
+        <v>6821100</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5503,10 +5502,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118601824</v>
+        <v>118601664</v>
       </c>
       <c r="B48" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5519,21 +5518,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5543,10 +5542,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466445</v>
+        <v>466402</v>
       </c>
       <c r="R48" t="n">
-        <v>6820355</v>
+        <v>6820391</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5605,10 +5604,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118601844</v>
+        <v>118601682</v>
       </c>
       <c r="B49" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5621,21 +5620,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5645,10 +5644,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466418</v>
+        <v>466381</v>
       </c>
       <c r="R49" t="n">
-        <v>6820392</v>
+        <v>6820326</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5707,7 +5706,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118601768</v>
+        <v>118601746</v>
       </c>
       <c r="B50" t="n">
         <v>78484</v>
@@ -5747,10 +5746,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466260</v>
+        <v>466284</v>
       </c>
       <c r="R50" t="n">
-        <v>6820919</v>
+        <v>6821043</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5809,10 +5808,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118601688</v>
+        <v>118601773</v>
       </c>
       <c r="B51" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5825,21 +5824,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5849,10 +5848,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>466309</v>
+        <v>466222</v>
       </c>
       <c r="R51" t="n">
-        <v>6820526</v>
+        <v>6820731</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5911,10 +5910,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118601720</v>
+        <v>118601835</v>
       </c>
       <c r="B52" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5927,21 +5926,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5951,10 +5950,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>466331</v>
+        <v>466455</v>
       </c>
       <c r="R52" t="n">
-        <v>6821018</v>
+        <v>6820335</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6013,10 +6012,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118601664</v>
+        <v>118601815</v>
       </c>
       <c r="B53" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6029,21 +6028,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6053,10 +6052,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>466402</v>
+        <v>466490</v>
       </c>
       <c r="R53" t="n">
-        <v>6820391</v>
+        <v>6820635</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6115,7 +6114,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118601777</v>
+        <v>118601820</v>
       </c>
       <c r="B54" t="n">
         <v>78484</v>
@@ -6155,10 +6154,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>466261</v>
+        <v>466299</v>
       </c>
       <c r="R54" t="n">
-        <v>6820701</v>
+        <v>6820534</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6217,7 +6216,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118601753</v>
+        <v>118601770</v>
       </c>
       <c r="B55" t="n">
         <v>78484</v>
@@ -6257,10 +6256,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466257</v>
+        <v>466256</v>
       </c>
       <c r="R55" t="n">
-        <v>6821074</v>
+        <v>6820907</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6319,7 +6318,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118601770</v>
+        <v>118601833</v>
       </c>
       <c r="B56" t="n">
         <v>78484</v>
@@ -6359,10 +6358,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>466256</v>
+        <v>466472</v>
       </c>
       <c r="R56" t="n">
-        <v>6820907</v>
+        <v>6820338</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6421,10 +6420,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118601826</v>
+        <v>118601671</v>
       </c>
       <c r="B57" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6437,21 +6436,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6461,10 +6460,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466453</v>
+        <v>466329</v>
       </c>
       <c r="R57" t="n">
-        <v>6820379</v>
+        <v>6820672</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6523,10 +6522,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118601841</v>
+        <v>118601732</v>
       </c>
       <c r="B58" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6539,21 +6538,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6563,10 +6562,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>466411</v>
+        <v>466287</v>
       </c>
       <c r="R58" t="n">
-        <v>6820346</v>
+        <v>6820603</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6625,10 +6624,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118601725</v>
+        <v>118601783</v>
       </c>
       <c r="B59" t="n">
-        <v>77421</v>
+        <v>78484</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6641,21 +6640,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6665,10 +6664,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466297</v>
+        <v>466420</v>
       </c>
       <c r="R59" t="n">
-        <v>6820527</v>
+        <v>6820743</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6709,7 +6708,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6728,10 +6726,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118601654</v>
+        <v>118601793</v>
       </c>
       <c r="B60" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6744,21 +6742,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6768,10 +6766,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466318</v>
+        <v>466430</v>
       </c>
       <c r="R60" t="n">
-        <v>6820669</v>
+        <v>6820757</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6830,10 +6828,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118601680</v>
+        <v>118601744</v>
       </c>
       <c r="B61" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6846,21 +6844,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6870,10 +6868,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466464</v>
+        <v>466316</v>
       </c>
       <c r="R61" t="n">
-        <v>6820342</v>
+        <v>6821025</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6932,7 +6930,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118601842</v>
+        <v>118601837</v>
       </c>
       <c r="B62" t="n">
         <v>78484</v>
@@ -6972,10 +6970,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466394</v>
+        <v>466436</v>
       </c>
       <c r="R62" t="n">
-        <v>6820329</v>
+        <v>6820340</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7136,10 +7134,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118601726</v>
+        <v>118601792</v>
       </c>
       <c r="B64" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7152,21 +7150,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7176,10 +7174,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466331</v>
+        <v>466431</v>
       </c>
       <c r="R64" t="n">
-        <v>6821018</v>
+        <v>6820760</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7238,7 +7236,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118601727</v>
+        <v>118601730</v>
       </c>
       <c r="B65" t="n">
         <v>78220</v>
@@ -7278,10 +7276,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>466269</v>
+        <v>466330</v>
       </c>
       <c r="R65" t="n">
-        <v>6821081</v>
+        <v>6820558</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7340,10 +7338,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118601818</v>
+        <v>118601721</v>
       </c>
       <c r="B66" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7356,21 +7354,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7380,10 +7378,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>466307</v>
+        <v>466487</v>
       </c>
       <c r="R66" t="n">
-        <v>6820533</v>
+        <v>6820641</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7442,10 +7440,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118601734</v>
+        <v>118601719</v>
       </c>
       <c r="B67" t="n">
-        <v>90522</v>
+        <v>78510</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7454,25 +7452,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7482,10 +7480,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466389</v>
+        <v>466263</v>
       </c>
       <c r="R67" t="n">
-        <v>6820384</v>
+        <v>6820456</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7544,10 +7542,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118601744</v>
+        <v>118601699</v>
       </c>
       <c r="B68" t="n">
-        <v>78484</v>
+        <v>90524</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7560,21 +7558,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7584,10 +7582,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466316</v>
+        <v>466261</v>
       </c>
       <c r="R68" t="n">
-        <v>6821025</v>
+        <v>6821105</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7646,7 +7644,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118601831</v>
+        <v>118601811</v>
       </c>
       <c r="B69" t="n">
         <v>78484</v>
@@ -7686,10 +7684,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466463</v>
+        <v>466447</v>
       </c>
       <c r="R69" t="n">
-        <v>6820344</v>
+        <v>6820672</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7748,7 +7746,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118601809</v>
+        <v>118601750</v>
       </c>
       <c r="B70" t="n">
         <v>78484</v>
@@ -7788,10 +7786,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466431</v>
+        <v>466256</v>
       </c>
       <c r="R70" t="n">
-        <v>6820682</v>
+        <v>6821102</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7850,7 +7848,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118601750</v>
+        <v>118601843</v>
       </c>
       <c r="B71" t="n">
         <v>78484</v>
@@ -7890,10 +7888,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466256</v>
+        <v>466412</v>
       </c>
       <c r="R71" t="n">
-        <v>6821102</v>
+        <v>6820369</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7952,7 +7950,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118601836</v>
+        <v>118601771</v>
       </c>
       <c r="B72" t="n">
         <v>78484</v>
@@ -7992,10 +7990,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466454</v>
+        <v>466259</v>
       </c>
       <c r="R72" t="n">
-        <v>6820333</v>
+        <v>6820893</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8054,10 +8052,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118601690</v>
+        <v>118601748</v>
       </c>
       <c r="B73" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8070,21 +8068,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8094,10 +8092,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>466438</v>
+        <v>466269</v>
       </c>
       <c r="R73" t="n">
-        <v>6820356</v>
+        <v>6821098</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8156,10 +8154,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118601854</v>
+        <v>118601731</v>
       </c>
       <c r="B74" t="n">
-        <v>5166</v>
+        <v>78220</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8168,25 +8166,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100526</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8196,10 +8194,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>466505</v>
+        <v>466306</v>
       </c>
       <c r="R74" t="n">
-        <v>6820638</v>
+        <v>6820562</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8258,10 +8256,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118601674</v>
+        <v>118601663</v>
       </c>
       <c r="B75" t="n">
-        <v>79102</v>
+        <v>78518</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8274,21 +8272,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8298,10 +8296,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>466487</v>
+        <v>466405</v>
       </c>
       <c r="R75" t="n">
-        <v>6820639</v>
+        <v>6820390</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8360,10 +8358,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118601846</v>
+        <v>118601657</v>
       </c>
       <c r="B76" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8376,21 +8374,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8400,10 +8398,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>466402</v>
+        <v>466303</v>
       </c>
       <c r="R76" t="n">
-        <v>6820391</v>
+        <v>6820542</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8462,7 +8460,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118601832</v>
+        <v>118601846</v>
       </c>
       <c r="B77" t="n">
         <v>78484</v>
@@ -8502,10 +8500,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>466471</v>
+        <v>466402</v>
       </c>
       <c r="R77" t="n">
-        <v>6820340</v>
+        <v>6820391</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8564,10 +8562,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118601660</v>
+        <v>118601824</v>
       </c>
       <c r="B78" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8580,21 +8578,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8604,10 +8602,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>466432</v>
+        <v>466445</v>
       </c>
       <c r="R78" t="n">
-        <v>6820354</v>
+        <v>6820355</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8666,10 +8664,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118601715</v>
+        <v>118601755</v>
       </c>
       <c r="B79" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8682,42 +8680,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>466440</v>
+        <v>466248</v>
       </c>
       <c r="R79" t="n">
-        <v>6820684</v>
+        <v>6821008</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8750,11 +8740,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Två nyligen ringhackade granar</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8781,10 +8766,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118601685</v>
+        <v>118601713</v>
       </c>
       <c r="B80" t="n">
-        <v>79073</v>
+        <v>57290</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8797,34 +8782,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>466265</v>
+        <v>466317</v>
       </c>
       <c r="R80" t="n">
-        <v>6821100</v>
+        <v>6820668</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8857,6 +8850,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8883,10 +8881,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118601668</v>
+        <v>118601855</v>
       </c>
       <c r="B81" t="n">
-        <v>79102</v>
+        <v>5166</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8895,25 +8893,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8923,10 +8921,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>466198</v>
+        <v>466454</v>
       </c>
       <c r="R81" t="n">
-        <v>6820787</v>
+        <v>6820379</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8985,10 +8983,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118601801</v>
+        <v>118601695</v>
       </c>
       <c r="B82" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9001,34 +8999,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>466410</v>
+        <v>466298</v>
       </c>
       <c r="R82" t="n">
-        <v>6820722</v>
+        <v>6820554</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9061,6 +9067,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9087,10 +9098,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118601781</v>
+        <v>118601686</v>
       </c>
       <c r="B83" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9103,21 +9114,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9127,10 +9138,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>466322</v>
+        <v>466290</v>
       </c>
       <c r="R83" t="n">
-        <v>6820686</v>
+        <v>6820662</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9189,10 +9200,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118601835</v>
+        <v>118601684</v>
       </c>
       <c r="B84" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9205,21 +9216,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9229,10 +9240,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>466455</v>
+        <v>466268</v>
       </c>
       <c r="R84" t="n">
-        <v>6820335</v>
+        <v>6821079</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9291,10 +9302,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118601833</v>
+        <v>118601674</v>
       </c>
       <c r="B85" t="n">
-        <v>78484</v>
+        <v>79102</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9307,21 +9318,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9331,10 +9342,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>466472</v>
+        <v>466487</v>
       </c>
       <c r="R85" t="n">
-        <v>6820338</v>
+        <v>6820639</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9393,10 +9404,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118601771</v>
+        <v>118601728</v>
       </c>
       <c r="B86" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9409,21 +9420,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9433,10 +9444,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>466259</v>
+        <v>466290</v>
       </c>
       <c r="R86" t="n">
-        <v>6820893</v>
+        <v>6820662</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9495,10 +9506,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118601739</v>
+        <v>118601706</v>
       </c>
       <c r="B87" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9511,34 +9522,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>466404</v>
+        <v>466265</v>
       </c>
       <c r="R87" t="n">
-        <v>6820864</v>
+        <v>6820475</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9571,6 +9590,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9597,10 +9621,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118601666</v>
+        <v>118601825</v>
       </c>
       <c r="B88" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9613,21 +9637,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9637,10 +9661,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>466233</v>
+        <v>466450</v>
       </c>
       <c r="R88" t="n">
-        <v>6821097</v>
+        <v>6820356</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9699,10 +9723,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118601848</v>
+        <v>118601747</v>
       </c>
       <c r="B89" t="n">
-        <v>94513</v>
+        <v>78484</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9711,25 +9735,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9739,10 +9763,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>466442</v>
+        <v>466278</v>
       </c>
       <c r="R89" t="n">
-        <v>6820579</v>
+        <v>6821064</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9801,7 +9825,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118601840</v>
+        <v>118601796</v>
       </c>
       <c r="B90" t="n">
         <v>78484</v>
@@ -9841,10 +9865,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>466421</v>
+        <v>466413</v>
       </c>
       <c r="R90" t="n">
-        <v>6820332</v>
+        <v>6820733</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9903,10 +9927,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118601775</v>
+        <v>118601722</v>
       </c>
       <c r="B91" t="n">
-        <v>78484</v>
+        <v>78221</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9919,21 +9943,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9943,10 +9967,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>466245</v>
+        <v>466289</v>
       </c>
       <c r="R91" t="n">
-        <v>6820718</v>
+        <v>6820603</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10005,7 +10029,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118601754</v>
+        <v>118601752</v>
       </c>
       <c r="B92" t="n">
         <v>78484</v>
@@ -10045,10 +10069,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>466257</v>
+        <v>466250</v>
       </c>
       <c r="R92" t="n">
-        <v>6821042</v>
+        <v>6821077</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10107,10 +10131,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118601657</v>
+        <v>118601672</v>
       </c>
       <c r="B93" t="n">
-        <v>78518</v>
+        <v>79102</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10123,21 +10147,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10147,10 +10171,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>466303</v>
+        <v>466343</v>
       </c>
       <c r="R93" t="n">
-        <v>6820542</v>
+        <v>6820677</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10209,10 +10233,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118601704</v>
+        <v>118601780</v>
       </c>
       <c r="B94" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10225,42 +10249,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>466415</v>
+        <v>466301</v>
       </c>
       <c r="R94" t="n">
-        <v>6820750</v>
+        <v>6820686</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10293,11 +10309,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10324,10 +10335,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118601684</v>
+        <v>118601830</v>
       </c>
       <c r="B95" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10340,21 +10351,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10364,10 +10375,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>466268</v>
+        <v>466471</v>
       </c>
       <c r="R95" t="n">
-        <v>6821079</v>
+        <v>6820355</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10426,10 +10437,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118601721</v>
+        <v>118601779</v>
       </c>
       <c r="B96" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10442,21 +10453,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10466,10 +10477,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>466487</v>
+        <v>466285</v>
       </c>
       <c r="R96" t="n">
-        <v>6820641</v>
+        <v>6820690</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10528,10 +10539,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118601672</v>
+        <v>118601836</v>
       </c>
       <c r="B97" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10544,21 +10555,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10568,10 +10579,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>466343</v>
+        <v>466454</v>
       </c>
       <c r="R97" t="n">
-        <v>6820677</v>
+        <v>6820333</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10630,10 +10641,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118601700</v>
+        <v>118601715</v>
       </c>
       <c r="B98" t="n">
-        <v>78573</v>
+        <v>57290</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10642,38 +10653,46 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6450</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>466247</v>
+        <v>466440</v>
       </c>
       <c r="R98" t="n">
-        <v>6821087</v>
+        <v>6820684</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10706,6 +10725,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Två nyligen ringhackade granar</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10732,10 +10756,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118601773</v>
+        <v>118601683</v>
       </c>
       <c r="B99" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10748,21 +10772,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10772,10 +10796,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>466222</v>
+        <v>466307</v>
       </c>
       <c r="R99" t="n">
-        <v>6820731</v>
+        <v>6820562</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10816,6 +10840,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10834,10 +10859,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118601823</v>
+        <v>118601659</v>
       </c>
       <c r="B100" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10850,21 +10875,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10874,10 +10899,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>466416</v>
+        <v>466258</v>
       </c>
       <c r="R100" t="n">
-        <v>6820391</v>
+        <v>6820476</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10936,7 +10961,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118601819</v>
+        <v>118601769</v>
       </c>
       <c r="B101" t="n">
         <v>78484</v>
@@ -10976,10 +11001,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>466294</v>
+        <v>466252</v>
       </c>
       <c r="R101" t="n">
-        <v>6820528</v>
+        <v>6820916</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11038,7 +11063,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118601755</v>
+        <v>118601743</v>
       </c>
       <c r="B102" t="n">
         <v>78484</v>
@@ -11078,10 +11103,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>466248</v>
+        <v>466336</v>
       </c>
       <c r="R102" t="n">
-        <v>6821008</v>
+        <v>6820998</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11140,10 +11165,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118601687</v>
+        <v>118601753</v>
       </c>
       <c r="B103" t="n">
-        <v>79073</v>
+        <v>78484</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11156,21 +11181,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11180,10 +11205,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>466330</v>
+        <v>466257</v>
       </c>
       <c r="R103" t="n">
-        <v>6820551</v>
+        <v>6821074</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11242,7 +11267,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118601811</v>
+        <v>118601799</v>
       </c>
       <c r="B104" t="n">
         <v>78484</v>
@@ -11282,10 +11307,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>466447</v>
+        <v>466416</v>
       </c>
       <c r="R104" t="n">
-        <v>6820672</v>
+        <v>6820728</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11344,7 +11369,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118601793</v>
+        <v>118601751</v>
       </c>
       <c r="B105" t="n">
         <v>78484</v>
@@ -11384,10 +11409,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>466430</v>
+        <v>466237</v>
       </c>
       <c r="R105" t="n">
-        <v>6820757</v>
+        <v>6821090</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11446,10 +11471,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118601850</v>
+        <v>118601680</v>
       </c>
       <c r="B106" t="n">
-        <v>78129</v>
+        <v>79102</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11462,21 +11487,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11486,10 +11511,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>466318</v>
+        <v>466464</v>
       </c>
       <c r="R106" t="n">
-        <v>6820439</v>
+        <v>6820342</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11548,10 +11573,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118601790</v>
+        <v>118601688</v>
       </c>
       <c r="B107" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11564,21 +11589,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11588,10 +11613,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>466453</v>
+        <v>466309</v>
       </c>
       <c r="R107" t="n">
-        <v>6820774</v>
+        <v>6820526</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11650,10 +11675,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118601695</v>
+        <v>118601720</v>
       </c>
       <c r="B108" t="n">
-        <v>57290</v>
+        <v>78221</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11666,42 +11691,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>466298</v>
+        <v>466331</v>
       </c>
       <c r="R108" t="n">
-        <v>6820554</v>
+        <v>6821018</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11734,11 +11751,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11765,10 +11777,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118601698</v>
+        <v>118601654</v>
       </c>
       <c r="B109" t="n">
-        <v>57443</v>
+        <v>78518</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11781,21 +11793,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103021</v>
+        <v>185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11805,10 +11817,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>466319</v>
+        <v>466318</v>
       </c>
       <c r="R109" t="n">
-        <v>6820440</v>
+        <v>6820669</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11867,10 +11879,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118601658</v>
+        <v>118601765</v>
       </c>
       <c r="B110" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11883,21 +11895,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11907,10 +11919,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>466276</v>
+        <v>466239</v>
       </c>
       <c r="R110" t="n">
-        <v>6820477</v>
+        <v>6820936</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11969,10 +11981,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118601663</v>
+        <v>118601842</v>
       </c>
       <c r="B111" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11985,21 +11997,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12009,10 +12021,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>466405</v>
+        <v>466394</v>
       </c>
       <c r="R111" t="n">
-        <v>6820390</v>
+        <v>6820329</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12071,10 +12083,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118601702</v>
+        <v>118601790</v>
       </c>
       <c r="B112" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12087,42 +12099,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>466455</v>
+        <v>466453</v>
       </c>
       <c r="R112" t="n">
-        <v>6820642</v>
+        <v>6820774</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12155,11 +12159,6 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12186,10 +12185,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118601671</v>
+        <v>118601768</v>
       </c>
       <c r="B113" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12202,21 +12201,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12226,10 +12225,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>466329</v>
+        <v>466260</v>
       </c>
       <c r="R113" t="n">
-        <v>6820672</v>
+        <v>6820919</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12288,10 +12287,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118601800</v>
+        <v>118601704</v>
       </c>
       <c r="B114" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12304,34 +12303,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>466414</v>
+        <v>466415</v>
       </c>
       <c r="R114" t="n">
-        <v>6820727</v>
+        <v>6820750</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12364,6 +12371,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12390,10 +12402,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118601751</v>
+        <v>118601727</v>
       </c>
       <c r="B115" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12406,21 +12418,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12430,10 +12442,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>466237</v>
+        <v>466269</v>
       </c>
       <c r="R115" t="n">
-        <v>6821090</v>
+        <v>6821081</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12492,10 +12504,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118601728</v>
+        <v>118601850</v>
       </c>
       <c r="B116" t="n">
-        <v>78220</v>
+        <v>78129</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12508,21 +12520,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12532,10 +12544,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>466290</v>
+        <v>466318</v>
       </c>
       <c r="R116" t="n">
-        <v>6820662</v>
+        <v>6820439</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12594,10 +12606,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118601732</v>
+        <v>118601661</v>
       </c>
       <c r="B117" t="n">
-        <v>78220</v>
+        <v>78518</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12610,21 +12622,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12634,10 +12646,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>466287</v>
+        <v>466471</v>
       </c>
       <c r="R117" t="n">
-        <v>6820603</v>
+        <v>6820336</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12696,7 +12708,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118601813</v>
+        <v>118601777</v>
       </c>
       <c r="B118" t="n">
         <v>78484</v>
@@ -12736,10 +12748,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>466463</v>
+        <v>466261</v>
       </c>
       <c r="R118" t="n">
-        <v>6820672</v>
+        <v>6820701</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12798,7 +12810,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118601808</v>
+        <v>118601813</v>
       </c>
       <c r="B119" t="n">
         <v>78484</v>
@@ -12838,10 +12850,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>466433</v>
+        <v>466463</v>
       </c>
       <c r="R119" t="n">
-        <v>6820675</v>
+        <v>6820672</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12900,7 +12912,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118601812</v>
+        <v>118601840</v>
       </c>
       <c r="B120" t="n">
         <v>78484</v>
@@ -12940,10 +12952,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>466454</v>
+        <v>466421</v>
       </c>
       <c r="R120" t="n">
-        <v>6820670</v>
+        <v>6820332</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13002,10 +13014,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118601699</v>
+        <v>118601828</v>
       </c>
       <c r="B121" t="n">
-        <v>90524</v>
+        <v>78484</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13018,21 +13030,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13042,10 +13054,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>466261</v>
+        <v>466454</v>
       </c>
       <c r="R121" t="n">
-        <v>6821105</v>
+        <v>6820362</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13104,7 +13116,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118601796</v>
+        <v>118601774</v>
       </c>
       <c r="B122" t="n">
         <v>78484</v>
@@ -13144,10 +13156,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>466413</v>
+        <v>466223</v>
       </c>
       <c r="R122" t="n">
-        <v>6820733</v>
+        <v>6820728</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13206,10 +13218,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118601713</v>
+        <v>118601812</v>
       </c>
       <c r="B123" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13222,42 +13234,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>466317</v>
+        <v>466454</v>
       </c>
       <c r="R123" t="n">
-        <v>6820668</v>
+        <v>6820670</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13290,11 +13294,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13321,7 +13320,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118601706</v>
+        <v>118601703</v>
       </c>
       <c r="B124" t="n">
         <v>57290</v>
@@ -13369,10 +13368,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>466265</v>
+        <v>466470</v>
       </c>
       <c r="R124" t="n">
-        <v>6820475</v>
+        <v>6820354</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13409,7 +13408,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13436,10 +13435,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118601673</v>
+        <v>118601687</v>
       </c>
       <c r="B125" t="n">
-        <v>79102</v>
+        <v>79073</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13452,21 +13451,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13476,10 +13475,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>466480</v>
+        <v>466330</v>
       </c>
       <c r="R125" t="n">
-        <v>6820672</v>
+        <v>6820551</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13538,7 +13537,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118601806</v>
+        <v>118601742</v>
       </c>
       <c r="B126" t="n">
         <v>78484</v>
@@ -13578,10 +13577,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>466422</v>
+        <v>466344</v>
       </c>
       <c r="R126" t="n">
-        <v>6820680</v>
+        <v>6820993</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13640,7 +13639,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118601825</v>
+        <v>118601814</v>
       </c>
       <c r="B127" t="n">
         <v>78484</v>
@@ -13680,10 +13679,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>466450</v>
+        <v>466476</v>
       </c>
       <c r="R127" t="n">
-        <v>6820356</v>
+        <v>6820673</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13742,7 +13741,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118601820</v>
+        <v>118601823</v>
       </c>
       <c r="B128" t="n">
         <v>78484</v>
@@ -13782,10 +13781,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>466299</v>
+        <v>466416</v>
       </c>
       <c r="R128" t="n">
-        <v>6820534</v>
+        <v>6820391</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13844,7 +13843,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118601837</v>
+        <v>118601844</v>
       </c>
       <c r="B129" t="n">
         <v>78484</v>
@@ -13884,10 +13883,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>466436</v>
+        <v>466418</v>
       </c>
       <c r="R129" t="n">
-        <v>6820340</v>
+        <v>6820392</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13946,10 +13945,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118601745</v>
+        <v>118601726</v>
       </c>
       <c r="B130" t="n">
-        <v>78484</v>
+        <v>78220</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13962,21 +13961,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13986,10 +13985,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>466308</v>
+        <v>466331</v>
       </c>
       <c r="R130" t="n">
-        <v>6821040</v>
+        <v>6821018</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14048,10 +14047,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118601749</v>
+        <v>118601700</v>
       </c>
       <c r="B131" t="n">
-        <v>78484</v>
+        <v>78573</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14060,25 +14059,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14088,10 +14087,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>466261</v>
+        <v>466247</v>
       </c>
       <c r="R131" t="n">
-        <v>6821105</v>
+        <v>6821087</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14150,10 +14149,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118601669</v>
+        <v>118601698</v>
       </c>
       <c r="B132" t="n">
-        <v>79102</v>
+        <v>57443</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14166,21 +14165,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14190,10 +14189,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>466233</v>
+        <v>466319</v>
       </c>
       <c r="R132" t="n">
-        <v>6820720</v>
+        <v>6820440</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14252,10 +14251,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118601776</v>
+        <v>118601725</v>
       </c>
       <c r="B133" t="n">
-        <v>78484</v>
+        <v>77421</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14268,21 +14267,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14292,10 +14291,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>466252</v>
+        <v>466297</v>
       </c>
       <c r="R133" t="n">
-        <v>6820713</v>
+        <v>6820527</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14336,6 +14335,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14354,10 +14354,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118601696</v>
+        <v>118601677</v>
       </c>
       <c r="B134" t="n">
-        <v>57290</v>
+        <v>79102</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14370,42 +14370,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>466389</v>
+        <v>466318</v>
       </c>
       <c r="R134" t="n">
-        <v>6820384</v>
+        <v>6820439</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14438,11 +14430,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Äldre bo (2-3 år gammalt)</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14469,7 +14456,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118601748</v>
+        <v>118601801</v>
       </c>
       <c r="B135" t="n">
         <v>78484</v>
@@ -14509,10 +14496,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>466269</v>
+        <v>466410</v>
       </c>
       <c r="R135" t="n">
-        <v>6821098</v>
+        <v>6820722</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14571,7 +14558,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118601778</v>
+        <v>118601766</v>
       </c>
       <c r="B136" t="n">
         <v>78484</v>
@@ -14611,10 +14598,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>466283</v>
+        <v>466247</v>
       </c>
       <c r="R136" t="n">
-        <v>6820697</v>
+        <v>6820929</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14673,7 +14660,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118601830</v>
+        <v>118601791</v>
       </c>
       <c r="B137" t="n">
         <v>78484</v>
@@ -14713,10 +14700,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>466471</v>
+        <v>466470</v>
       </c>
       <c r="R137" t="n">
-        <v>6820355</v>
+        <v>6820774</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14775,10 +14762,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118601703</v>
+        <v>118601668</v>
       </c>
       <c r="B138" t="n">
-        <v>57290</v>
+        <v>79102</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14791,42 +14778,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>466470</v>
+        <v>466198</v>
       </c>
       <c r="R138" t="n">
-        <v>6820354</v>
+        <v>6820787</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14859,11 +14838,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14890,7 +14864,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118601677</v>
+        <v>118601669</v>
       </c>
       <c r="B139" t="n">
         <v>79102</v>
@@ -14930,10 +14904,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>466318</v>
+        <v>466233</v>
       </c>
       <c r="R139" t="n">
-        <v>6820439</v>
+        <v>6820720</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14992,7 +14966,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118601679</v>
+        <v>118601673</v>
       </c>
       <c r="B140" t="n">
         <v>79102</v>
@@ -15032,10 +15006,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>466318</v>
+        <v>466480</v>
       </c>
       <c r="R140" t="n">
-        <v>6820464</v>
+        <v>6820672</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15094,10 +15068,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118601724</v>
+        <v>118601776</v>
       </c>
       <c r="B141" t="n">
-        <v>79565</v>
+        <v>78484</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15110,21 +15084,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15134,10 +15108,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>466276</v>
+        <v>466252</v>
       </c>
       <c r="R141" t="n">
-        <v>6821068</v>
+        <v>6820713</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15196,10 +15170,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118601682</v>
+        <v>118601827</v>
       </c>
       <c r="B142" t="n">
-        <v>79102</v>
+        <v>78484</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15212,21 +15186,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15236,10 +15210,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>466381</v>
+        <v>466466</v>
       </c>
       <c r="R142" t="n">
-        <v>6820326</v>
+        <v>6820369</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15298,7 +15272,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118601828</v>
+        <v>118601802</v>
       </c>
       <c r="B143" t="n">
         <v>78484</v>
@@ -15338,10 +15312,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>466454</v>
+        <v>466418</v>
       </c>
       <c r="R143" t="n">
-        <v>6820362</v>
+        <v>6820718</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15400,10 +15374,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118601659</v>
+        <v>118601817</v>
       </c>
       <c r="B144" t="n">
-        <v>78518</v>
+        <v>78484</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15416,21 +15390,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15440,10 +15414,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>466258</v>
+        <v>466344</v>
       </c>
       <c r="R144" t="n">
-        <v>6820476</v>
+        <v>6820520</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15502,7 +15476,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118601780</v>
+        <v>118601818</v>
       </c>
       <c r="B145" t="n">
         <v>78484</v>
@@ -15542,10 +15516,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>466301</v>
+        <v>466307</v>
       </c>
       <c r="R145" t="n">
-        <v>6820686</v>
+        <v>6820533</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15604,7 +15578,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118601815</v>
+        <v>118601845</v>
       </c>
       <c r="B146" t="n">
         <v>78484</v>
@@ -15644,10 +15618,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>466490</v>
+        <v>466405</v>
       </c>
       <c r="R146" t="n">
-        <v>6820635</v>
+        <v>6820389</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15706,10 +15680,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118601765</v>
+        <v>118601848</v>
       </c>
       <c r="B147" t="n">
-        <v>78484</v>
+        <v>94513</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15718,25 +15692,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15746,10 +15720,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>466239</v>
+        <v>466442</v>
       </c>
       <c r="R147" t="n">
-        <v>6820936</v>
+        <v>6820579</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15808,7 +15782,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>118601743</v>
+        <v>118601739</v>
       </c>
       <c r="B148" t="n">
         <v>78484</v>
@@ -15848,10 +15822,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>466336</v>
+        <v>466404</v>
       </c>
       <c r="R148" t="n">
-        <v>6820998</v>
+        <v>6820864</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15910,10 +15884,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118601769</v>
+        <v>118601658</v>
       </c>
       <c r="B149" t="n">
-        <v>78484</v>
+        <v>78518</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15926,21 +15900,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15950,10 +15924,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>466252</v>
+        <v>466276</v>
       </c>
       <c r="R149" t="n">
-        <v>6820916</v>
+        <v>6820477</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16012,7 +15986,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118601772</v>
+        <v>118601826</v>
       </c>
       <c r="B150" t="n">
         <v>78484</v>
@@ -16052,10 +16026,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>466213</v>
+        <v>466453</v>
       </c>
       <c r="R150" t="n">
-        <v>6820752</v>
+        <v>6820379</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16114,7 +16088,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118601834</v>
+        <v>118601772</v>
       </c>
       <c r="B151" t="n">
         <v>78484</v>
@@ -16154,10 +16128,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>466471</v>
+        <v>466213</v>
       </c>
       <c r="R151" t="n">
-        <v>6820336</v>
+        <v>6820752</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16216,7 +16190,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118601843</v>
+        <v>118601831</v>
       </c>
       <c r="B152" t="n">
         <v>78484</v>
@@ -16256,10 +16230,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>466412</v>
+        <v>466463</v>
       </c>
       <c r="R152" t="n">
-        <v>6820369</v>
+        <v>6820344</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16318,10 +16292,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>118601855</v>
+        <v>118601800</v>
       </c>
       <c r="B153" t="n">
-        <v>5166</v>
+        <v>78484</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16330,25 +16304,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16358,10 +16332,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>466454</v>
+        <v>466414</v>
       </c>
       <c r="R153" t="n">
-        <v>6820379</v>
+        <v>6820727</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16420,10 +16394,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118601730</v>
+        <v>118601734</v>
       </c>
       <c r="B154" t="n">
-        <v>78220</v>
+        <v>90522</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16436,21 +16410,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16460,10 +16434,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>466330</v>
+        <v>466389</v>
       </c>
       <c r="R154" t="n">
-        <v>6820558</v>
+        <v>6820384</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16522,7 +16496,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>118601791</v>
+        <v>118601778</v>
       </c>
       <c r="B155" t="n">
         <v>78484</v>
@@ -16562,10 +16536,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>466470</v>
+        <v>466283</v>
       </c>
       <c r="R155" t="n">
-        <v>6820774</v>
+        <v>6820697</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16624,7 +16598,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>118601792</v>
+        <v>118601808</v>
       </c>
       <c r="B156" t="n">
         <v>78484</v>
@@ -16664,10 +16638,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>466431</v>
+        <v>466433</v>
       </c>
       <c r="R156" t="n">
-        <v>6820760</v>
+        <v>6820675</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16726,10 +16700,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>118601719</v>
+        <v>118601775</v>
       </c>
       <c r="B157" t="n">
-        <v>78510</v>
+        <v>78484</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16738,25 +16712,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16766,10 +16740,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>466263</v>
+        <v>466245</v>
       </c>
       <c r="R157" t="n">
-        <v>6820456</v>
+        <v>6820718</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16828,7 +16802,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>118601822</v>
+        <v>118601806</v>
       </c>
       <c r="B158" t="n">
         <v>78484</v>
@@ -16868,10 +16842,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>466341</v>
+        <v>466422</v>
       </c>
       <c r="R158" t="n">
-        <v>6820450</v>
+        <v>6820680</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16930,10 +16904,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>118601814</v>
+        <v>118601724</v>
       </c>
       <c r="B159" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16946,21 +16920,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16970,10 +16944,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>466476</v>
+        <v>466276</v>
       </c>
       <c r="R159" t="n">
-        <v>6820673</v>
+        <v>6821068</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17032,10 +17006,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>118601774</v>
+        <v>118601696</v>
       </c>
       <c r="B160" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17048,34 +17022,42 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>466223</v>
+        <v>466389</v>
       </c>
       <c r="R160" t="n">
-        <v>6820728</v>
+        <v>6820384</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17108,6 +17090,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Äldre bo (2-3 år gammalt)</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17134,10 +17121,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>118601799</v>
+        <v>118601702</v>
       </c>
       <c r="B161" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17150,34 +17137,42 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>466416</v>
+        <v>466455</v>
       </c>
       <c r="R161" t="n">
-        <v>6820728</v>
+        <v>6820642</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17210,6 +17205,11 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 36883-2023 artfynd.xlsx
+++ b/artfynd/A 36883-2023 artfynd.xlsx
@@ -3666,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118601666</v>
+        <v>118601660</v>
       </c>
       <c r="B30" t="n">
-        <v>79102</v>
+        <v>78525</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466233</v>
+        <v>466432</v>
       </c>
       <c r="R30" t="n">
-        <v>6821097</v>
+        <v>6820354</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3768,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118601841</v>
+        <v>118601766</v>
       </c>
       <c r="B31" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466411</v>
+        <v>466247</v>
       </c>
       <c r="R31" t="n">
-        <v>6820346</v>
+        <v>6820929</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118601809</v>
+        <v>118601744</v>
       </c>
       <c r="B32" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466431</v>
+        <v>466316</v>
       </c>
       <c r="R32" t="n">
-        <v>6820682</v>
+        <v>6821025</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3972,10 +3972,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118601810</v>
+        <v>118601742</v>
       </c>
       <c r="B33" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466440</v>
+        <v>466344</v>
       </c>
       <c r="R33" t="n">
-        <v>6820675</v>
+        <v>6820993</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118601819</v>
+        <v>118601713</v>
       </c>
       <c r="B34" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4090,34 +4090,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466294</v>
+        <v>466317</v>
       </c>
       <c r="R34" t="n">
-        <v>6820528</v>
+        <v>6820668</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4150,6 +4158,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4176,10 +4189,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118601660</v>
+        <v>118601685</v>
       </c>
       <c r="B35" t="n">
-        <v>78518</v>
+        <v>79080</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4192,21 +4205,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4216,10 +4229,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466432</v>
+        <v>466265</v>
       </c>
       <c r="R35" t="n">
-        <v>6820354</v>
+        <v>6821100</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4278,10 +4291,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118601781</v>
+        <v>118601841</v>
       </c>
       <c r="B36" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4318,10 +4331,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466322</v>
+        <v>466411</v>
       </c>
       <c r="R36" t="n">
-        <v>6820686</v>
+        <v>6820346</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4380,10 +4393,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118601745</v>
+        <v>118601807</v>
       </c>
       <c r="B37" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4420,10 +4433,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466308</v>
+        <v>466428</v>
       </c>
       <c r="R37" t="n">
-        <v>6821040</v>
+        <v>6820671</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4482,7 +4495,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118601854</v>
+        <v>118601855</v>
       </c>
       <c r="B38" t="n">
         <v>5166</v>
@@ -4522,10 +4535,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466505</v>
+        <v>466454</v>
       </c>
       <c r="R38" t="n">
-        <v>6820638</v>
+        <v>6820379</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4584,10 +4597,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118601822</v>
+        <v>118601674</v>
       </c>
       <c r="B39" t="n">
-        <v>78484</v>
+        <v>79109</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4600,21 +4613,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4624,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466341</v>
+        <v>466487</v>
       </c>
       <c r="R39" t="n">
-        <v>6820450</v>
+        <v>6820639</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4686,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118601834</v>
+        <v>118601728</v>
       </c>
       <c r="B40" t="n">
-        <v>78484</v>
+        <v>78227</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4702,21 +4715,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4726,10 +4739,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466471</v>
+        <v>466290</v>
       </c>
       <c r="R40" t="n">
-        <v>6820336</v>
+        <v>6820662</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4788,10 +4801,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118601754</v>
+        <v>118601729</v>
       </c>
       <c r="B41" t="n">
-        <v>78484</v>
+        <v>78227</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4804,21 +4817,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4828,10 +4841,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466257</v>
+        <v>466487</v>
       </c>
       <c r="R41" t="n">
-        <v>6821042</v>
+        <v>6820641</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4890,10 +4903,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118601679</v>
+        <v>118601745</v>
       </c>
       <c r="B42" t="n">
-        <v>79102</v>
+        <v>78491</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4906,21 +4919,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4930,10 +4943,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466318</v>
+        <v>466308</v>
       </c>
       <c r="R42" t="n">
-        <v>6820464</v>
+        <v>6821040</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4992,10 +5005,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118601729</v>
+        <v>118601722</v>
       </c>
       <c r="B43" t="n">
-        <v>78220</v>
+        <v>78228</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5008,21 +5021,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5032,10 +5045,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466487</v>
+        <v>466289</v>
       </c>
       <c r="R43" t="n">
-        <v>6820641</v>
+        <v>6820603</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5094,10 +5107,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118601690</v>
+        <v>118601743</v>
       </c>
       <c r="B44" t="n">
-        <v>79073</v>
+        <v>78491</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5110,21 +5123,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5134,10 +5147,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466438</v>
+        <v>466336</v>
       </c>
       <c r="R44" t="n">
-        <v>6820356</v>
+        <v>6820998</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5196,10 +5209,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118601749</v>
+        <v>118601810</v>
       </c>
       <c r="B45" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5236,10 +5249,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466261</v>
+        <v>466440</v>
       </c>
       <c r="R45" t="n">
-        <v>6821105</v>
+        <v>6820675</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5298,10 +5311,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118601832</v>
+        <v>118601750</v>
       </c>
       <c r="B46" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5338,10 +5351,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466471</v>
+        <v>466256</v>
       </c>
       <c r="R46" t="n">
-        <v>6820340</v>
+        <v>6821102</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5400,10 +5413,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118601685</v>
+        <v>118601781</v>
       </c>
       <c r="B47" t="n">
-        <v>79073</v>
+        <v>78491</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5416,21 +5429,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5440,10 +5453,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466265</v>
+        <v>466322</v>
       </c>
       <c r="R47" t="n">
-        <v>6821100</v>
+        <v>6820686</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5502,10 +5515,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118601664</v>
+        <v>118601754</v>
       </c>
       <c r="B48" t="n">
-        <v>78518</v>
+        <v>78491</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5518,21 +5531,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5542,10 +5555,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466402</v>
+        <v>466257</v>
       </c>
       <c r="R48" t="n">
-        <v>6820391</v>
+        <v>6821042</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5604,10 +5617,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118601682</v>
+        <v>118601739</v>
       </c>
       <c r="B49" t="n">
-        <v>79102</v>
+        <v>78491</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5620,21 +5633,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5644,10 +5657,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466381</v>
+        <v>466404</v>
       </c>
       <c r="R49" t="n">
-        <v>6820326</v>
+        <v>6820864</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5706,10 +5719,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118601746</v>
+        <v>118601812</v>
       </c>
       <c r="B50" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5746,10 +5759,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466284</v>
+        <v>466454</v>
       </c>
       <c r="R50" t="n">
-        <v>6821043</v>
+        <v>6820670</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5808,10 +5821,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118601773</v>
+        <v>118601699</v>
       </c>
       <c r="B51" t="n">
-        <v>78484</v>
+        <v>90531</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5824,21 +5837,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5848,10 +5861,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>466222</v>
+        <v>466261</v>
       </c>
       <c r="R51" t="n">
-        <v>6820731</v>
+        <v>6821105</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5910,10 +5923,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118601835</v>
+        <v>118601673</v>
       </c>
       <c r="B52" t="n">
-        <v>78484</v>
+        <v>79109</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5926,21 +5939,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5950,10 +5963,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>466455</v>
+        <v>466480</v>
       </c>
       <c r="R52" t="n">
-        <v>6820335</v>
+        <v>6820672</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6012,10 +6025,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118601815</v>
+        <v>118601700</v>
       </c>
       <c r="B53" t="n">
-        <v>78484</v>
+        <v>78580</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6024,25 +6037,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6052,10 +6065,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>466490</v>
+        <v>466247</v>
       </c>
       <c r="R53" t="n">
-        <v>6820635</v>
+        <v>6821087</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6114,10 +6127,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118601820</v>
+        <v>118601664</v>
       </c>
       <c r="B54" t="n">
-        <v>78484</v>
+        <v>78525</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6130,21 +6143,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6154,10 +6167,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>466299</v>
+        <v>466402</v>
       </c>
       <c r="R54" t="n">
-        <v>6820534</v>
+        <v>6820391</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6216,10 +6229,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118601770</v>
+        <v>118601818</v>
       </c>
       <c r="B55" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6256,10 +6269,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466256</v>
+        <v>466307</v>
       </c>
       <c r="R55" t="n">
-        <v>6820907</v>
+        <v>6820533</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6318,10 +6331,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118601833</v>
+        <v>118601768</v>
       </c>
       <c r="B56" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6358,10 +6371,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>466472</v>
+        <v>466260</v>
       </c>
       <c r="R56" t="n">
-        <v>6820338</v>
+        <v>6820919</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6420,10 +6433,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118601671</v>
+        <v>118601771</v>
       </c>
       <c r="B57" t="n">
-        <v>79102</v>
+        <v>78491</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6436,21 +6449,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6460,10 +6473,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466329</v>
+        <v>466259</v>
       </c>
       <c r="R57" t="n">
-        <v>6820672</v>
+        <v>6820893</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6522,10 +6535,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118601732</v>
+        <v>118601814</v>
       </c>
       <c r="B58" t="n">
-        <v>78220</v>
+        <v>78491</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6538,21 +6551,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6562,10 +6575,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>466287</v>
+        <v>466476</v>
       </c>
       <c r="R58" t="n">
-        <v>6820603</v>
+        <v>6820673</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6624,10 +6637,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118601783</v>
+        <v>118601725</v>
       </c>
       <c r="B59" t="n">
-        <v>78484</v>
+        <v>77428</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6640,21 +6653,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6664,10 +6677,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466420</v>
+        <v>466297</v>
       </c>
       <c r="R59" t="n">
-        <v>6820743</v>
+        <v>6820527</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6708,6 +6721,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6726,10 +6740,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118601793</v>
+        <v>118601773</v>
       </c>
       <c r="B60" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6766,10 +6780,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466430</v>
+        <v>466222</v>
       </c>
       <c r="R60" t="n">
-        <v>6820757</v>
+        <v>6820731</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6828,10 +6842,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118601744</v>
+        <v>118601796</v>
       </c>
       <c r="B61" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6868,10 +6882,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466316</v>
+        <v>466413</v>
       </c>
       <c r="R61" t="n">
-        <v>6821025</v>
+        <v>6820733</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6930,10 +6944,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118601837</v>
+        <v>118601752</v>
       </c>
       <c r="B62" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6970,10 +6984,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466436</v>
+        <v>466250</v>
       </c>
       <c r="R62" t="n">
-        <v>6820340</v>
+        <v>6821077</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7032,10 +7046,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118601807</v>
+        <v>118601671</v>
       </c>
       <c r="B63" t="n">
-        <v>78484</v>
+        <v>79109</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7048,21 +7062,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7072,10 +7086,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>466428</v>
+        <v>466329</v>
       </c>
       <c r="R63" t="n">
-        <v>6820671</v>
+        <v>6820672</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7134,10 +7148,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118601792</v>
+        <v>118601679</v>
       </c>
       <c r="B64" t="n">
-        <v>78484</v>
+        <v>79109</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7150,21 +7164,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7174,10 +7188,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466431</v>
+        <v>466318</v>
       </c>
       <c r="R64" t="n">
-        <v>6820760</v>
+        <v>6820464</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7236,10 +7250,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118601730</v>
+        <v>118601668</v>
       </c>
       <c r="B65" t="n">
-        <v>78220</v>
+        <v>79109</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7252,21 +7266,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7276,10 +7290,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>466330</v>
+        <v>466198</v>
       </c>
       <c r="R65" t="n">
-        <v>6820558</v>
+        <v>6820787</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7338,10 +7352,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118601721</v>
+        <v>118601809</v>
       </c>
       <c r="B66" t="n">
-        <v>78221</v>
+        <v>78491</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7354,21 +7368,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7378,10 +7392,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>466487</v>
+        <v>466431</v>
       </c>
       <c r="R66" t="n">
-        <v>6820641</v>
+        <v>6820682</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7440,10 +7454,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118601719</v>
+        <v>118601848</v>
       </c>
       <c r="B67" t="n">
-        <v>78510</v>
+        <v>94520</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7456,21 +7470,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6434</v>
+        <v>2170</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7480,10 +7494,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466263</v>
+        <v>466442</v>
       </c>
       <c r="R67" t="n">
-        <v>6820456</v>
+        <v>6820579</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7542,10 +7556,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118601699</v>
+        <v>118601775</v>
       </c>
       <c r="B68" t="n">
-        <v>90524</v>
+        <v>78491</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7558,21 +7572,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7582,10 +7596,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466261</v>
+        <v>466245</v>
       </c>
       <c r="R68" t="n">
-        <v>6821105</v>
+        <v>6820718</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7644,10 +7658,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118601811</v>
+        <v>118601806</v>
       </c>
       <c r="B69" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7684,10 +7698,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466447</v>
+        <v>466422</v>
       </c>
       <c r="R69" t="n">
-        <v>6820672</v>
+        <v>6820680</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7746,10 +7760,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118601750</v>
+        <v>118601755</v>
       </c>
       <c r="B70" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7786,10 +7800,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466256</v>
+        <v>466248</v>
       </c>
       <c r="R70" t="n">
-        <v>6821102</v>
+        <v>6821008</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7848,10 +7862,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118601843</v>
+        <v>118601695</v>
       </c>
       <c r="B71" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7864,34 +7878,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466412</v>
+        <v>466298</v>
       </c>
       <c r="R71" t="n">
-        <v>6820369</v>
+        <v>6820554</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7924,6 +7946,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7950,10 +7977,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118601771</v>
+        <v>118601828</v>
       </c>
       <c r="B72" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7990,10 +8017,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466259</v>
+        <v>466454</v>
       </c>
       <c r="R72" t="n">
-        <v>6820893</v>
+        <v>6820362</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8052,10 +8079,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118601748</v>
+        <v>118601827</v>
       </c>
       <c r="B73" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8092,10 +8119,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>466269</v>
+        <v>466466</v>
       </c>
       <c r="R73" t="n">
-        <v>6821098</v>
+        <v>6820369</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8154,10 +8181,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118601731</v>
+        <v>118601808</v>
       </c>
       <c r="B74" t="n">
-        <v>78220</v>
+        <v>78491</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8170,21 +8197,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8194,10 +8221,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>466306</v>
+        <v>466433</v>
       </c>
       <c r="R74" t="n">
-        <v>6820562</v>
+        <v>6820675</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8256,10 +8283,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118601663</v>
+        <v>118601769</v>
       </c>
       <c r="B75" t="n">
-        <v>78518</v>
+        <v>78491</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8272,21 +8299,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8296,10 +8323,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>466405</v>
+        <v>466252</v>
       </c>
       <c r="R75" t="n">
-        <v>6820390</v>
+        <v>6820916</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8358,10 +8385,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118601657</v>
+        <v>118601779</v>
       </c>
       <c r="B76" t="n">
-        <v>78518</v>
+        <v>78491</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8374,21 +8401,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8398,10 +8425,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>466303</v>
+        <v>466285</v>
       </c>
       <c r="R76" t="n">
-        <v>6820542</v>
+        <v>6820690</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8460,10 +8487,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118601846</v>
+        <v>118601734</v>
       </c>
       <c r="B77" t="n">
-        <v>78484</v>
+        <v>90529</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8476,21 +8503,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8500,10 +8527,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>466402</v>
+        <v>466389</v>
       </c>
       <c r="R77" t="n">
-        <v>6820391</v>
+        <v>6820384</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8562,10 +8589,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118601824</v>
+        <v>118601850</v>
       </c>
       <c r="B78" t="n">
-        <v>78484</v>
+        <v>78136</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8578,21 +8605,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8602,10 +8629,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>466445</v>
+        <v>466318</v>
       </c>
       <c r="R78" t="n">
-        <v>6820355</v>
+        <v>6820439</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8664,10 +8691,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118601755</v>
+        <v>118601658</v>
       </c>
       <c r="B79" t="n">
-        <v>78484</v>
+        <v>78525</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8680,21 +8707,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8704,10 +8731,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>466248</v>
+        <v>466276</v>
       </c>
       <c r="R79" t="n">
-        <v>6821008</v>
+        <v>6820477</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8766,7 +8793,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118601713</v>
+        <v>118601706</v>
       </c>
       <c r="B80" t="n">
         <v>57290</v>
@@ -8804,7 +8831,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8814,10 +8841,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>466317</v>
+        <v>466265</v>
       </c>
       <c r="R80" t="n">
-        <v>6820668</v>
+        <v>6820475</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8854,7 +8881,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8881,10 +8908,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118601855</v>
+        <v>118601680</v>
       </c>
       <c r="B81" t="n">
-        <v>5166</v>
+        <v>79109</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8893,25 +8920,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8921,10 +8948,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>466454</v>
+        <v>466464</v>
       </c>
       <c r="R81" t="n">
-        <v>6820379</v>
+        <v>6820342</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8983,10 +9010,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118601695</v>
+        <v>118601846</v>
       </c>
       <c r="B82" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8999,42 +9026,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>466298</v>
+        <v>466402</v>
       </c>
       <c r="R82" t="n">
-        <v>6820554</v>
+        <v>6820391</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9067,11 +9086,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9098,10 +9112,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118601686</v>
+        <v>118601721</v>
       </c>
       <c r="B83" t="n">
-        <v>79073</v>
+        <v>78228</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9114,21 +9128,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9138,10 +9152,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>466290</v>
+        <v>466487</v>
       </c>
       <c r="R83" t="n">
-        <v>6820662</v>
+        <v>6820641</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9200,10 +9214,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118601684</v>
+        <v>118601792</v>
       </c>
       <c r="B84" t="n">
-        <v>79073</v>
+        <v>78491</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9216,21 +9230,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9240,10 +9254,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>466268</v>
+        <v>466431</v>
       </c>
       <c r="R84" t="n">
-        <v>6821079</v>
+        <v>6820760</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9302,10 +9316,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118601674</v>
+        <v>118601811</v>
       </c>
       <c r="B85" t="n">
-        <v>79102</v>
+        <v>78491</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9318,21 +9332,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9342,10 +9356,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>466487</v>
+        <v>466447</v>
       </c>
       <c r="R85" t="n">
-        <v>6820639</v>
+        <v>6820672</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9404,10 +9418,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118601728</v>
+        <v>118601720</v>
       </c>
       <c r="B86" t="n">
-        <v>78220</v>
+        <v>78228</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9420,21 +9434,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9444,10 +9458,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>466290</v>
+        <v>466331</v>
       </c>
       <c r="R86" t="n">
-        <v>6820662</v>
+        <v>6821018</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9506,10 +9520,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118601706</v>
+        <v>118601686</v>
       </c>
       <c r="B87" t="n">
-        <v>57290</v>
+        <v>79080</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9522,42 +9536,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>466265</v>
+        <v>466290</v>
       </c>
       <c r="R87" t="n">
-        <v>6820475</v>
+        <v>6820662</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9590,11 +9596,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9621,10 +9622,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118601825</v>
+        <v>118601677</v>
       </c>
       <c r="B88" t="n">
-        <v>78484</v>
+        <v>79109</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9637,21 +9638,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9661,10 +9662,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>466450</v>
+        <v>466318</v>
       </c>
       <c r="R88" t="n">
-        <v>6820356</v>
+        <v>6820439</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9723,10 +9724,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118601747</v>
+        <v>118601726</v>
       </c>
       <c r="B89" t="n">
-        <v>78484</v>
+        <v>78227</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9739,21 +9740,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9763,10 +9764,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>466278</v>
+        <v>466331</v>
       </c>
       <c r="R89" t="n">
-        <v>6821064</v>
+        <v>6821018</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9825,10 +9826,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118601796</v>
+        <v>118601657</v>
       </c>
       <c r="B90" t="n">
-        <v>78484</v>
+        <v>78525</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9841,21 +9842,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9865,10 +9866,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>466413</v>
+        <v>466303</v>
       </c>
       <c r="R90" t="n">
-        <v>6820733</v>
+        <v>6820542</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9927,10 +9928,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118601722</v>
+        <v>118601835</v>
       </c>
       <c r="B91" t="n">
-        <v>78221</v>
+        <v>78491</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9943,21 +9944,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9967,10 +9968,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>466289</v>
+        <v>466455</v>
       </c>
       <c r="R91" t="n">
-        <v>6820603</v>
+        <v>6820335</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10029,10 +10030,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118601752</v>
+        <v>118601776</v>
       </c>
       <c r="B92" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10069,10 +10070,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>466250</v>
+        <v>466252</v>
       </c>
       <c r="R92" t="n">
-        <v>6821077</v>
+        <v>6820713</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10131,10 +10132,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118601672</v>
+        <v>118601819</v>
       </c>
       <c r="B93" t="n">
-        <v>79102</v>
+        <v>78491</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10147,21 +10148,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10171,10 +10172,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>466343</v>
+        <v>466294</v>
       </c>
       <c r="R93" t="n">
-        <v>6820677</v>
+        <v>6820528</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10233,10 +10234,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118601780</v>
+        <v>118601845</v>
       </c>
       <c r="B94" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10273,10 +10274,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>466301</v>
+        <v>466405</v>
       </c>
       <c r="R94" t="n">
-        <v>6820686</v>
+        <v>6820389</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10335,10 +10336,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118601830</v>
+        <v>118601854</v>
       </c>
       <c r="B95" t="n">
-        <v>78484</v>
+        <v>5166</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10347,25 +10348,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10375,10 +10376,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>466471</v>
+        <v>466505</v>
       </c>
       <c r="R95" t="n">
-        <v>6820355</v>
+        <v>6820638</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10437,10 +10438,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118601779</v>
+        <v>118601749</v>
       </c>
       <c r="B96" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10477,10 +10478,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>466285</v>
+        <v>466261</v>
       </c>
       <c r="R96" t="n">
-        <v>6820690</v>
+        <v>6821105</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10539,10 +10540,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118601836</v>
+        <v>118601793</v>
       </c>
       <c r="B97" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10579,10 +10580,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>466454</v>
+        <v>466430</v>
       </c>
       <c r="R97" t="n">
-        <v>6820333</v>
+        <v>6820757</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10641,10 +10642,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118601715</v>
+        <v>118601822</v>
       </c>
       <c r="B98" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10657,42 +10658,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>466440</v>
+        <v>466341</v>
       </c>
       <c r="R98" t="n">
-        <v>6820684</v>
+        <v>6820450</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10725,11 +10718,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Två nyligen ringhackade granar</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10756,10 +10744,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118601683</v>
+        <v>118601834</v>
       </c>
       <c r="B99" t="n">
-        <v>79073</v>
+        <v>78491</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10772,21 +10760,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10796,10 +10784,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>466307</v>
+        <v>466471</v>
       </c>
       <c r="R99" t="n">
-        <v>6820562</v>
+        <v>6820336</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10840,7 +10828,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10859,10 +10846,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118601659</v>
+        <v>118601672</v>
       </c>
       <c r="B100" t="n">
-        <v>78518</v>
+        <v>79109</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10875,21 +10862,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10899,10 +10886,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>466258</v>
+        <v>466343</v>
       </c>
       <c r="R100" t="n">
-        <v>6820476</v>
+        <v>6820677</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10961,10 +10948,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118601769</v>
+        <v>118601702</v>
       </c>
       <c r="B101" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10977,34 +10964,42 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>466252</v>
+        <v>466455</v>
       </c>
       <c r="R101" t="n">
-        <v>6820916</v>
+        <v>6820642</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11037,6 +11032,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11063,10 +11063,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118601743</v>
+        <v>118601698</v>
       </c>
       <c r="B102" t="n">
-        <v>78484</v>
+        <v>57443</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11079,21 +11079,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11103,10 +11103,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>466336</v>
+        <v>466319</v>
       </c>
       <c r="R102" t="n">
-        <v>6820998</v>
+        <v>6820440</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11165,10 +11165,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118601753</v>
+        <v>118601683</v>
       </c>
       <c r="B103" t="n">
-        <v>78484</v>
+        <v>79080</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11181,21 +11181,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11205,10 +11205,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>466257</v>
+        <v>466307</v>
       </c>
       <c r="R103" t="n">
-        <v>6821074</v>
+        <v>6820562</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11249,6 +11249,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11267,10 +11268,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118601799</v>
+        <v>118601663</v>
       </c>
       <c r="B104" t="n">
-        <v>78484</v>
+        <v>78525</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11283,21 +11284,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11307,10 +11308,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>466416</v>
+        <v>466405</v>
       </c>
       <c r="R104" t="n">
-        <v>6820728</v>
+        <v>6820390</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11369,10 +11370,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118601751</v>
+        <v>118601783</v>
       </c>
       <c r="B105" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11409,10 +11410,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>466237</v>
+        <v>466420</v>
       </c>
       <c r="R105" t="n">
-        <v>6821090</v>
+        <v>6820743</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11471,10 +11472,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118601680</v>
+        <v>118601777</v>
       </c>
       <c r="B106" t="n">
-        <v>79102</v>
+        <v>78491</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11487,21 +11488,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11511,10 +11512,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>466464</v>
+        <v>466261</v>
       </c>
       <c r="R106" t="n">
-        <v>6820342</v>
+        <v>6820701</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11573,10 +11574,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118601688</v>
+        <v>118601830</v>
       </c>
       <c r="B107" t="n">
-        <v>79073</v>
+        <v>78491</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11589,21 +11590,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11613,10 +11614,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>466309</v>
+        <v>466471</v>
       </c>
       <c r="R107" t="n">
-        <v>6820526</v>
+        <v>6820355</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11675,10 +11676,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118601720</v>
+        <v>118601799</v>
       </c>
       <c r="B108" t="n">
-        <v>78221</v>
+        <v>78491</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11691,21 +11692,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11715,10 +11716,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>466331</v>
+        <v>466416</v>
       </c>
       <c r="R108" t="n">
-        <v>6821018</v>
+        <v>6820728</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11777,10 +11778,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118601654</v>
+        <v>118601817</v>
       </c>
       <c r="B109" t="n">
-        <v>78518</v>
+        <v>78491</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11793,21 +11794,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11817,10 +11818,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>466318</v>
+        <v>466344</v>
       </c>
       <c r="R109" t="n">
-        <v>6820669</v>
+        <v>6820520</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11879,10 +11880,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118601765</v>
+        <v>118601825</v>
       </c>
       <c r="B110" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11919,10 +11920,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>466239</v>
+        <v>466450</v>
       </c>
       <c r="R110" t="n">
-        <v>6820936</v>
+        <v>6820356</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11981,10 +11982,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118601842</v>
+        <v>118601791</v>
       </c>
       <c r="B111" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12021,10 +12022,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>466394</v>
+        <v>466470</v>
       </c>
       <c r="R111" t="n">
-        <v>6820329</v>
+        <v>6820774</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12083,10 +12084,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118601790</v>
+        <v>118601661</v>
       </c>
       <c r="B112" t="n">
-        <v>78484</v>
+        <v>78525</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12099,21 +12100,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12123,10 +12124,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>466453</v>
+        <v>466471</v>
       </c>
       <c r="R112" t="n">
-        <v>6820774</v>
+        <v>6820336</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12185,10 +12186,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118601768</v>
+        <v>118601747</v>
       </c>
       <c r="B113" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12225,10 +12226,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>466260</v>
+        <v>466278</v>
       </c>
       <c r="R113" t="n">
-        <v>6820919</v>
+        <v>6821064</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12287,10 +12288,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118601704</v>
+        <v>118601772</v>
       </c>
       <c r="B114" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12303,42 +12304,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>466415</v>
+        <v>466213</v>
       </c>
       <c r="R114" t="n">
-        <v>6820750</v>
+        <v>6820752</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12371,11 +12364,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12402,10 +12390,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118601727</v>
+        <v>118601824</v>
       </c>
       <c r="B115" t="n">
-        <v>78220</v>
+        <v>78491</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12418,21 +12406,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12442,10 +12430,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>466269</v>
+        <v>466445</v>
       </c>
       <c r="R115" t="n">
-        <v>6821081</v>
+        <v>6820355</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12504,10 +12492,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118601850</v>
+        <v>118601684</v>
       </c>
       <c r="B116" t="n">
-        <v>78129</v>
+        <v>79080</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12520,21 +12508,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12544,10 +12532,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>466318</v>
+        <v>466268</v>
       </c>
       <c r="R116" t="n">
-        <v>6820439</v>
+        <v>6821079</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12606,10 +12594,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118601661</v>
+        <v>118601813</v>
       </c>
       <c r="B117" t="n">
-        <v>78518</v>
+        <v>78491</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12622,21 +12610,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12646,10 +12634,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>466471</v>
+        <v>466463</v>
       </c>
       <c r="R117" t="n">
-        <v>6820336</v>
+        <v>6820672</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12708,10 +12696,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118601777</v>
+        <v>118601719</v>
       </c>
       <c r="B118" t="n">
-        <v>78484</v>
+        <v>78517</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12720,25 +12708,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12748,10 +12736,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>466261</v>
+        <v>466263</v>
       </c>
       <c r="R118" t="n">
-        <v>6820701</v>
+        <v>6820456</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12810,10 +12798,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118601813</v>
+        <v>118601753</v>
       </c>
       <c r="B119" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12850,10 +12838,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>466463</v>
+        <v>466257</v>
       </c>
       <c r="R119" t="n">
-        <v>6820672</v>
+        <v>6821074</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12912,10 +12900,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118601840</v>
+        <v>118601820</v>
       </c>
       <c r="B120" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12952,10 +12940,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>466421</v>
+        <v>466299</v>
       </c>
       <c r="R120" t="n">
-        <v>6820332</v>
+        <v>6820534</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13014,10 +13002,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118601828</v>
+        <v>118601837</v>
       </c>
       <c r="B121" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13054,10 +13042,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>466454</v>
+        <v>466436</v>
       </c>
       <c r="R121" t="n">
-        <v>6820362</v>
+        <v>6820340</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13116,10 +13104,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118601774</v>
+        <v>118601731</v>
       </c>
       <c r="B122" t="n">
-        <v>78484</v>
+        <v>78227</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13132,21 +13120,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13156,10 +13144,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>466223</v>
+        <v>466306</v>
       </c>
       <c r="R122" t="n">
-        <v>6820728</v>
+        <v>6820562</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13218,10 +13206,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118601812</v>
+        <v>118601682</v>
       </c>
       <c r="B123" t="n">
-        <v>78484</v>
+        <v>79109</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13234,21 +13222,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13258,10 +13246,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>466454</v>
+        <v>466381</v>
       </c>
       <c r="R123" t="n">
-        <v>6820670</v>
+        <v>6820326</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13320,10 +13308,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118601703</v>
+        <v>118601688</v>
       </c>
       <c r="B124" t="n">
-        <v>57290</v>
+        <v>79080</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13336,42 +13324,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>466470</v>
+        <v>466309</v>
       </c>
       <c r="R124" t="n">
-        <v>6820354</v>
+        <v>6820526</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13404,11 +13384,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13435,10 +13410,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118601687</v>
+        <v>118601831</v>
       </c>
       <c r="B125" t="n">
-        <v>79073</v>
+        <v>78491</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13451,21 +13426,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13475,10 +13450,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>466330</v>
+        <v>466463</v>
       </c>
       <c r="R125" t="n">
-        <v>6820551</v>
+        <v>6820344</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13537,10 +13512,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118601742</v>
+        <v>118601690</v>
       </c>
       <c r="B126" t="n">
-        <v>78484</v>
+        <v>79080</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13553,21 +13528,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13577,10 +13552,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>466344</v>
+        <v>466438</v>
       </c>
       <c r="R126" t="n">
-        <v>6820993</v>
+        <v>6820356</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13639,10 +13614,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118601814</v>
+        <v>118601687</v>
       </c>
       <c r="B127" t="n">
-        <v>78484</v>
+        <v>79080</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13655,21 +13630,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13679,10 +13654,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>466476</v>
+        <v>466330</v>
       </c>
       <c r="R127" t="n">
-        <v>6820673</v>
+        <v>6820551</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13741,10 +13716,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118601823</v>
+        <v>118601704</v>
       </c>
       <c r="B128" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13757,34 +13732,42 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>466416</v>
+        <v>466415</v>
       </c>
       <c r="R128" t="n">
-        <v>6820391</v>
+        <v>6820750</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13817,6 +13800,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13843,10 +13831,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118601844</v>
+        <v>118601746</v>
       </c>
       <c r="B129" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13883,10 +13871,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>466418</v>
+        <v>466284</v>
       </c>
       <c r="R129" t="n">
-        <v>6820392</v>
+        <v>6821043</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13945,10 +13933,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118601726</v>
+        <v>118601780</v>
       </c>
       <c r="B130" t="n">
-        <v>78220</v>
+        <v>78491</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13961,21 +13949,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13985,10 +13973,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>466331</v>
+        <v>466301</v>
       </c>
       <c r="R130" t="n">
-        <v>6821018</v>
+        <v>6820686</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14047,10 +14035,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118601700</v>
+        <v>118601833</v>
       </c>
       <c r="B131" t="n">
-        <v>78573</v>
+        <v>78491</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14059,25 +14047,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14087,10 +14075,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>466247</v>
+        <v>466472</v>
       </c>
       <c r="R131" t="n">
-        <v>6821087</v>
+        <v>6820338</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14149,10 +14137,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118601698</v>
+        <v>118601832</v>
       </c>
       <c r="B132" t="n">
-        <v>57443</v>
+        <v>78491</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14165,21 +14153,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14189,10 +14177,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>466319</v>
+        <v>466471</v>
       </c>
       <c r="R132" t="n">
-        <v>6820440</v>
+        <v>6820340</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14251,10 +14239,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118601725</v>
+        <v>118601802</v>
       </c>
       <c r="B133" t="n">
-        <v>77421</v>
+        <v>78491</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14267,21 +14255,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14291,10 +14279,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>466297</v>
+        <v>466418</v>
       </c>
       <c r="R133" t="n">
-        <v>6820527</v>
+        <v>6820718</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14335,7 +14323,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14354,10 +14341,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118601677</v>
+        <v>118601844</v>
       </c>
       <c r="B134" t="n">
-        <v>79102</v>
+        <v>78491</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14370,21 +14357,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14394,10 +14381,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>466318</v>
+        <v>466418</v>
       </c>
       <c r="R134" t="n">
-        <v>6820439</v>
+        <v>6820392</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14456,10 +14443,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118601801</v>
+        <v>118601659</v>
       </c>
       <c r="B135" t="n">
-        <v>78484</v>
+        <v>78525</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14472,21 +14459,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14496,10 +14483,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>466410</v>
+        <v>466258</v>
       </c>
       <c r="R135" t="n">
-        <v>6820722</v>
+        <v>6820476</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14558,10 +14545,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118601766</v>
+        <v>118601801</v>
       </c>
       <c r="B136" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14598,10 +14585,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>466247</v>
+        <v>466410</v>
       </c>
       <c r="R136" t="n">
-        <v>6820929</v>
+        <v>6820722</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14660,10 +14647,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118601791</v>
+        <v>118601840</v>
       </c>
       <c r="B137" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14700,10 +14687,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>466470</v>
+        <v>466421</v>
       </c>
       <c r="R137" t="n">
-        <v>6820774</v>
+        <v>6820332</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14762,10 +14749,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118601668</v>
+        <v>118601727</v>
       </c>
       <c r="B138" t="n">
-        <v>79102</v>
+        <v>78227</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14778,21 +14765,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14802,10 +14789,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>466198</v>
+        <v>466269</v>
       </c>
       <c r="R138" t="n">
-        <v>6820787</v>
+        <v>6821081</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14864,10 +14851,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118601669</v>
+        <v>118601732</v>
       </c>
       <c r="B139" t="n">
-        <v>79102</v>
+        <v>78227</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14880,21 +14867,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14904,10 +14891,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>466233</v>
+        <v>466287</v>
       </c>
       <c r="R139" t="n">
-        <v>6820720</v>
+        <v>6820603</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14966,10 +14953,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118601673</v>
+        <v>118601666</v>
       </c>
       <c r="B140" t="n">
-        <v>79102</v>
+        <v>79109</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15006,10 +14993,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>466480</v>
+        <v>466233</v>
       </c>
       <c r="R140" t="n">
-        <v>6820672</v>
+        <v>6821097</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15068,10 +15055,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118601776</v>
+        <v>118601696</v>
       </c>
       <c r="B141" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15084,34 +15071,42 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>466252</v>
+        <v>466389</v>
       </c>
       <c r="R141" t="n">
-        <v>6820713</v>
+        <v>6820384</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15144,6 +15139,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Äldre bo (2-3 år gammalt)</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15170,10 +15170,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118601827</v>
+        <v>118601800</v>
       </c>
       <c r="B142" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15210,10 +15210,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>466466</v>
+        <v>466414</v>
       </c>
       <c r="R142" t="n">
-        <v>6820369</v>
+        <v>6820727</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15272,10 +15272,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118601802</v>
+        <v>118601774</v>
       </c>
       <c r="B143" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15312,10 +15312,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>466418</v>
+        <v>466223</v>
       </c>
       <c r="R143" t="n">
-        <v>6820718</v>
+        <v>6820728</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15374,10 +15374,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118601817</v>
+        <v>118601778</v>
       </c>
       <c r="B144" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15414,10 +15414,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>466344</v>
+        <v>466283</v>
       </c>
       <c r="R144" t="n">
-        <v>6820520</v>
+        <v>6820697</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15476,10 +15476,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118601818</v>
+        <v>118601826</v>
       </c>
       <c r="B145" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15516,10 +15516,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>466307</v>
+        <v>466453</v>
       </c>
       <c r="R145" t="n">
-        <v>6820533</v>
+        <v>6820379</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15578,10 +15578,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118601845</v>
+        <v>118601790</v>
       </c>
       <c r="B146" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15618,10 +15618,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>466405</v>
+        <v>466453</v>
       </c>
       <c r="R146" t="n">
-        <v>6820389</v>
+        <v>6820774</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15680,10 +15680,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118601848</v>
+        <v>118601823</v>
       </c>
       <c r="B147" t="n">
-        <v>94513</v>
+        <v>78491</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15692,25 +15692,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15720,10 +15720,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>466442</v>
+        <v>466416</v>
       </c>
       <c r="R147" t="n">
-        <v>6820579</v>
+        <v>6820391</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15782,10 +15782,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>118601739</v>
+        <v>118601843</v>
       </c>
       <c r="B148" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15822,10 +15822,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>466404</v>
+        <v>466412</v>
       </c>
       <c r="R148" t="n">
-        <v>6820864</v>
+        <v>6820369</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15884,10 +15884,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118601658</v>
+        <v>118601751</v>
       </c>
       <c r="B149" t="n">
-        <v>78518</v>
+        <v>78491</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15900,21 +15900,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15924,10 +15924,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>466276</v>
+        <v>466237</v>
       </c>
       <c r="R149" t="n">
-        <v>6820477</v>
+        <v>6821090</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15986,10 +15986,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118601826</v>
+        <v>118601730</v>
       </c>
       <c r="B150" t="n">
-        <v>78484</v>
+        <v>78227</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16002,21 +16002,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16026,10 +16026,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>466453</v>
+        <v>466330</v>
       </c>
       <c r="R150" t="n">
-        <v>6820379</v>
+        <v>6820558</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16088,10 +16088,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118601772</v>
+        <v>118601715</v>
       </c>
       <c r="B151" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16104,34 +16104,42 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>466213</v>
+        <v>466440</v>
       </c>
       <c r="R151" t="n">
-        <v>6820752</v>
+        <v>6820684</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16164,6 +16172,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Två nyligen ringhackade granar</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16190,10 +16203,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118601831</v>
+        <v>118601842</v>
       </c>
       <c r="B152" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16230,10 +16243,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>466463</v>
+        <v>466394</v>
       </c>
       <c r="R152" t="n">
-        <v>6820344</v>
+        <v>6820329</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16292,10 +16305,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>118601800</v>
+        <v>118601654</v>
       </c>
       <c r="B153" t="n">
-        <v>78484</v>
+        <v>78525</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16308,21 +16321,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16332,10 +16345,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>466414</v>
+        <v>466318</v>
       </c>
       <c r="R153" t="n">
-        <v>6820727</v>
+        <v>6820669</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16394,10 +16407,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118601734</v>
+        <v>118601815</v>
       </c>
       <c r="B154" t="n">
-        <v>90522</v>
+        <v>78491</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16410,21 +16423,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16434,10 +16447,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>466389</v>
+        <v>466490</v>
       </c>
       <c r="R154" t="n">
-        <v>6820384</v>
+        <v>6820635</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16496,10 +16509,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>118601778</v>
+        <v>118601748</v>
       </c>
       <c r="B155" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16536,10 +16549,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>466283</v>
+        <v>466269</v>
       </c>
       <c r="R155" t="n">
-        <v>6820697</v>
+        <v>6821098</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16598,10 +16611,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>118601808</v>
+        <v>118601836</v>
       </c>
       <c r="B156" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16638,10 +16651,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>466433</v>
+        <v>466454</v>
       </c>
       <c r="R156" t="n">
-        <v>6820675</v>
+        <v>6820333</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16700,10 +16713,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>118601775</v>
+        <v>118601765</v>
       </c>
       <c r="B157" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16740,10 +16753,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>466245</v>
+        <v>466239</v>
       </c>
       <c r="R157" t="n">
-        <v>6820718</v>
+        <v>6820936</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16802,10 +16815,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>118601806</v>
+        <v>118601770</v>
       </c>
       <c r="B158" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16842,10 +16855,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>466422</v>
+        <v>466256</v>
       </c>
       <c r="R158" t="n">
-        <v>6820680</v>
+        <v>6820907</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16907,7 +16920,7 @@
         <v>118601724</v>
       </c>
       <c r="B159" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17006,10 +17019,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>118601696</v>
+        <v>118601669</v>
       </c>
       <c r="B160" t="n">
-        <v>57290</v>
+        <v>79109</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17022,42 +17035,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>466389</v>
+        <v>466233</v>
       </c>
       <c r="R160" t="n">
-        <v>6820384</v>
+        <v>6820720</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17090,11 +17095,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Äldre bo (2-3 år gammalt)</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17121,7 +17121,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>118601702</v>
+        <v>118601703</v>
       </c>
       <c r="B161" t="n">
         <v>57290</v>
@@ -17159,7 +17159,7 @@
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
@@ -17169,10 +17169,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>466455</v>
+        <v>466470</v>
       </c>
       <c r="R161" t="n">
-        <v>6820642</v>
+        <v>6820354</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17209,7 +17209,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Färska ringhack (gran)</t>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 36883-2023 artfynd.xlsx
+++ b/artfynd/A 36883-2023 artfynd.xlsx
@@ -6025,10 +6025,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118601700</v>
+        <v>118601664</v>
       </c>
       <c r="B53" t="n">
-        <v>78580</v>
+        <v>78525</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6037,25 +6037,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6450</v>
+        <v>185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6065,10 +6065,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>466247</v>
+        <v>466402</v>
       </c>
       <c r="R53" t="n">
-        <v>6821087</v>
+        <v>6820391</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6127,10 +6127,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118601664</v>
+        <v>118601818</v>
       </c>
       <c r="B54" t="n">
-        <v>78525</v>
+        <v>78491</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6143,21 +6143,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>466402</v>
+        <v>466307</v>
       </c>
       <c r="R54" t="n">
-        <v>6820391</v>
+        <v>6820533</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6229,7 +6229,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118601818</v>
+        <v>118601768</v>
       </c>
       <c r="B55" t="n">
         <v>78491</v>
@@ -6269,10 +6269,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466307</v>
+        <v>466260</v>
       </c>
       <c r="R55" t="n">
-        <v>6820533</v>
+        <v>6820919</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6331,7 +6331,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118601768</v>
+        <v>118601771</v>
       </c>
       <c r="B56" t="n">
         <v>78491</v>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>466260</v>
+        <v>466259</v>
       </c>
       <c r="R56" t="n">
-        <v>6820919</v>
+        <v>6820893</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118601771</v>
+        <v>118601814</v>
       </c>
       <c r="B57" t="n">
         <v>78491</v>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466259</v>
+        <v>466476</v>
       </c>
       <c r="R57" t="n">
-        <v>6820893</v>
+        <v>6820673</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6535,10 +6535,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118601814</v>
+        <v>118601700</v>
       </c>
       <c r="B58" t="n">
-        <v>78491</v>
+        <v>78580</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6547,25 +6547,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6575,10 +6575,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>466476</v>
+        <v>466247</v>
       </c>
       <c r="R58" t="n">
-        <v>6820673</v>
+        <v>6821087</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7862,10 +7862,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118601695</v>
+        <v>118601734</v>
       </c>
       <c r="B71" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7878,42 +7878,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466298</v>
+        <v>466389</v>
       </c>
       <c r="R71" t="n">
-        <v>6820554</v>
+        <v>6820384</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7946,11 +7938,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8487,10 +8474,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118601734</v>
+        <v>118601695</v>
       </c>
       <c r="B77" t="n">
-        <v>90529</v>
+        <v>57290</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8503,34 +8490,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>466389</v>
+        <v>466298</v>
       </c>
       <c r="R77" t="n">
-        <v>6820384</v>
+        <v>6820554</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8563,6 +8558,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -11268,10 +11268,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118601663</v>
+        <v>118601825</v>
       </c>
       <c r="B104" t="n">
-        <v>78525</v>
+        <v>78491</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11284,21 +11284,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11308,10 +11308,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>466405</v>
+        <v>466450</v>
       </c>
       <c r="R104" t="n">
-        <v>6820390</v>
+        <v>6820356</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11370,7 +11370,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118601783</v>
+        <v>118601791</v>
       </c>
       <c r="B105" t="n">
         <v>78491</v>
@@ -11410,10 +11410,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>466420</v>
+        <v>466470</v>
       </c>
       <c r="R105" t="n">
-        <v>6820743</v>
+        <v>6820774</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11472,10 +11472,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118601777</v>
+        <v>118601663</v>
       </c>
       <c r="B106" t="n">
-        <v>78491</v>
+        <v>78525</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11488,21 +11488,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11512,10 +11512,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>466261</v>
+        <v>466405</v>
       </c>
       <c r="R106" t="n">
-        <v>6820701</v>
+        <v>6820390</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11574,7 +11574,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118601830</v>
+        <v>118601783</v>
       </c>
       <c r="B107" t="n">
         <v>78491</v>
@@ -11614,10 +11614,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>466471</v>
+        <v>466420</v>
       </c>
       <c r="R107" t="n">
-        <v>6820355</v>
+        <v>6820743</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11676,7 +11676,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118601799</v>
+        <v>118601777</v>
       </c>
       <c r="B108" t="n">
         <v>78491</v>
@@ -11716,10 +11716,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>466416</v>
+        <v>466261</v>
       </c>
       <c r="R108" t="n">
-        <v>6820728</v>
+        <v>6820701</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11778,7 +11778,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118601817</v>
+        <v>118601830</v>
       </c>
       <c r="B109" t="n">
         <v>78491</v>
@@ -11818,10 +11818,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>466344</v>
+        <v>466471</v>
       </c>
       <c r="R109" t="n">
-        <v>6820520</v>
+        <v>6820355</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11880,7 +11880,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118601825</v>
+        <v>118601799</v>
       </c>
       <c r="B110" t="n">
         <v>78491</v>
@@ -11920,10 +11920,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>466450</v>
+        <v>466416</v>
       </c>
       <c r="R110" t="n">
-        <v>6820356</v>
+        <v>6820728</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11982,7 +11982,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118601791</v>
+        <v>118601817</v>
       </c>
       <c r="B111" t="n">
         <v>78491</v>
@@ -12022,10 +12022,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>466470</v>
+        <v>466344</v>
       </c>
       <c r="R111" t="n">
-        <v>6820774</v>
+        <v>6820520</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12594,10 +12594,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118601813</v>
+        <v>118601719</v>
       </c>
       <c r="B117" t="n">
-        <v>78491</v>
+        <v>78517</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12606,25 +12606,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12634,10 +12634,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>466463</v>
+        <v>466263</v>
       </c>
       <c r="R117" t="n">
-        <v>6820672</v>
+        <v>6820456</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12696,10 +12696,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118601719</v>
+        <v>118601753</v>
       </c>
       <c r="B118" t="n">
-        <v>78517</v>
+        <v>78491</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12708,25 +12708,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>466263</v>
+        <v>466257</v>
       </c>
       <c r="R118" t="n">
-        <v>6820456</v>
+        <v>6821074</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12798,7 +12798,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118601753</v>
+        <v>118601820</v>
       </c>
       <c r="B119" t="n">
         <v>78491</v>
@@ -12838,10 +12838,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>466257</v>
+        <v>466299</v>
       </c>
       <c r="R119" t="n">
-        <v>6821074</v>
+        <v>6820534</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12900,7 +12900,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118601820</v>
+        <v>118601837</v>
       </c>
       <c r="B120" t="n">
         <v>78491</v>
@@ -12940,10 +12940,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>466299</v>
+        <v>466436</v>
       </c>
       <c r="R120" t="n">
-        <v>6820534</v>
+        <v>6820340</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13002,7 +13002,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118601837</v>
+        <v>118601813</v>
       </c>
       <c r="B121" t="n">
         <v>78491</v>
@@ -13042,10 +13042,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>466436</v>
+        <v>466463</v>
       </c>
       <c r="R121" t="n">
-        <v>6820340</v>
+        <v>6820672</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15170,7 +15170,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118601800</v>
+        <v>118601826</v>
       </c>
       <c r="B142" t="n">
         <v>78491</v>
@@ -15210,10 +15210,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>466414</v>
+        <v>466453</v>
       </c>
       <c r="R142" t="n">
-        <v>6820727</v>
+        <v>6820379</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15272,7 +15272,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118601774</v>
+        <v>118601790</v>
       </c>
       <c r="B143" t="n">
         <v>78491</v>
@@ -15312,10 +15312,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>466223</v>
+        <v>466453</v>
       </c>
       <c r="R143" t="n">
-        <v>6820728</v>
+        <v>6820774</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15374,7 +15374,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118601778</v>
+        <v>118601823</v>
       </c>
       <c r="B144" t="n">
         <v>78491</v>
@@ -15414,10 +15414,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>466283</v>
+        <v>466416</v>
       </c>
       <c r="R144" t="n">
-        <v>6820697</v>
+        <v>6820391</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15476,7 +15476,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118601826</v>
+        <v>118601843</v>
       </c>
       <c r="B145" t="n">
         <v>78491</v>
@@ -15516,10 +15516,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>466453</v>
+        <v>466412</v>
       </c>
       <c r="R145" t="n">
-        <v>6820379</v>
+        <v>6820369</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15578,7 +15578,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118601790</v>
+        <v>118601751</v>
       </c>
       <c r="B146" t="n">
         <v>78491</v>
@@ -15618,10 +15618,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>466453</v>
+        <v>466237</v>
       </c>
       <c r="R146" t="n">
-        <v>6820774</v>
+        <v>6821090</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15680,10 +15680,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118601823</v>
+        <v>118601730</v>
       </c>
       <c r="B147" t="n">
-        <v>78491</v>
+        <v>78227</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15696,21 +15696,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15720,10 +15720,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>466416</v>
+        <v>466330</v>
       </c>
       <c r="R147" t="n">
-        <v>6820391</v>
+        <v>6820558</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15782,10 +15782,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>118601843</v>
+        <v>118601715</v>
       </c>
       <c r="B148" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15798,34 +15798,42 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>466412</v>
+        <v>466440</v>
       </c>
       <c r="R148" t="n">
-        <v>6820369</v>
+        <v>6820684</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15858,6 +15866,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Två nyligen ringhackade granar</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15884,7 +15897,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118601751</v>
+        <v>118601800</v>
       </c>
       <c r="B149" t="n">
         <v>78491</v>
@@ -15924,10 +15937,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>466237</v>
+        <v>466414</v>
       </c>
       <c r="R149" t="n">
-        <v>6821090</v>
+        <v>6820727</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15986,10 +15999,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118601730</v>
+        <v>118601774</v>
       </c>
       <c r="B150" t="n">
-        <v>78227</v>
+        <v>78491</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16002,21 +16015,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16026,10 +16039,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>466330</v>
+        <v>466223</v>
       </c>
       <c r="R150" t="n">
-        <v>6820558</v>
+        <v>6820728</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16088,10 +16101,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118601715</v>
+        <v>118601778</v>
       </c>
       <c r="B151" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16104,42 +16117,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>466440</v>
+        <v>466283</v>
       </c>
       <c r="R151" t="n">
-        <v>6820684</v>
+        <v>6820697</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16172,11 +16177,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Två nyligen ringhackade granar</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16713,10 +16713,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>118601765</v>
+        <v>118601669</v>
       </c>
       <c r="B157" t="n">
-        <v>78491</v>
+        <v>79109</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16729,21 +16729,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16753,10 +16753,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>466239</v>
+        <v>466233</v>
       </c>
       <c r="R157" t="n">
-        <v>6820936</v>
+        <v>6820720</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16815,10 +16815,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>118601770</v>
+        <v>118601703</v>
       </c>
       <c r="B158" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16831,34 +16831,42 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>466256</v>
+        <v>466470</v>
       </c>
       <c r="R158" t="n">
-        <v>6820907</v>
+        <v>6820354</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16891,6 +16899,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16917,10 +16930,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>118601724</v>
+        <v>118601765</v>
       </c>
       <c r="B159" t="n">
-        <v>79572</v>
+        <v>78491</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16933,21 +16946,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16957,10 +16970,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>466276</v>
+        <v>466239</v>
       </c>
       <c r="R159" t="n">
-        <v>6821068</v>
+        <v>6820936</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17019,10 +17032,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>118601669</v>
+        <v>118601770</v>
       </c>
       <c r="B160" t="n">
-        <v>79109</v>
+        <v>78491</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17035,21 +17048,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17059,10 +17072,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>466233</v>
+        <v>466256</v>
       </c>
       <c r="R160" t="n">
-        <v>6820720</v>
+        <v>6820907</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17121,10 +17134,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>118601703</v>
+        <v>118601724</v>
       </c>
       <c r="B161" t="n">
-        <v>57290</v>
+        <v>79572</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17137,42 +17150,34 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>466470</v>
+        <v>466276</v>
       </c>
       <c r="R161" t="n">
-        <v>6820354</v>
+        <v>6821068</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17205,11 +17210,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 36883-2023 artfynd.xlsx
+++ b/artfynd/A 36883-2023 artfynd.xlsx
@@ -3666,10 +3666,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118601660</v>
+        <v>118601835</v>
       </c>
       <c r="B30" t="n">
-        <v>78525</v>
+        <v>78491</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3682,21 +3682,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>466432</v>
+        <v>466455</v>
       </c>
       <c r="R30" t="n">
-        <v>6820354</v>
+        <v>6820335</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3768,7 +3768,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118601766</v>
+        <v>118601831</v>
       </c>
       <c r="B31" t="n">
         <v>78491</v>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466247</v>
+        <v>466463</v>
       </c>
       <c r="R31" t="n">
-        <v>6820929</v>
+        <v>6820344</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3870,10 +3870,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118601744</v>
+        <v>118601730</v>
       </c>
       <c r="B32" t="n">
-        <v>78491</v>
+        <v>78227</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3886,21 +3886,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>466316</v>
+        <v>466330</v>
       </c>
       <c r="R32" t="n">
-        <v>6821025</v>
+        <v>6820558</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118601742</v>
+        <v>118601752</v>
       </c>
       <c r="B33" t="n">
         <v>78491</v>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466344</v>
+        <v>466250</v>
       </c>
       <c r="R33" t="n">
-        <v>6820993</v>
+        <v>6821077</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118601713</v>
+        <v>118601668</v>
       </c>
       <c r="B34" t="n">
-        <v>57290</v>
+        <v>79109</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4090,42 +4090,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466317</v>
+        <v>466198</v>
       </c>
       <c r="R34" t="n">
-        <v>6820668</v>
+        <v>6820787</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4158,11 +4150,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4189,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118601685</v>
+        <v>118601754</v>
       </c>
       <c r="B35" t="n">
-        <v>79080</v>
+        <v>78491</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4205,21 +4192,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4229,10 +4216,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466265</v>
+        <v>466257</v>
       </c>
       <c r="R35" t="n">
-        <v>6821100</v>
+        <v>6821042</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4291,10 +4278,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118601841</v>
+        <v>118601696</v>
       </c>
       <c r="B36" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4307,34 +4294,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>466411</v>
+        <v>466389</v>
       </c>
       <c r="R36" t="n">
-        <v>6820346</v>
+        <v>6820384</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4367,6 +4362,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre bo (2-3 år gammalt)</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4393,7 +4393,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118601807</v>
+        <v>118601841</v>
       </c>
       <c r="B37" t="n">
         <v>78491</v>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466428</v>
+        <v>466411</v>
       </c>
       <c r="R37" t="n">
-        <v>6820671</v>
+        <v>6820346</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4495,10 +4495,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118601855</v>
+        <v>118601840</v>
       </c>
       <c r="B38" t="n">
-        <v>5166</v>
+        <v>78491</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4507,25 +4507,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>466454</v>
+        <v>466421</v>
       </c>
       <c r="R38" t="n">
-        <v>6820379</v>
+        <v>6820332</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118601674</v>
+        <v>118601792</v>
       </c>
       <c r="B39" t="n">
-        <v>79109</v>
+        <v>78491</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466487</v>
+        <v>466431</v>
       </c>
       <c r="R39" t="n">
-        <v>6820639</v>
+        <v>6820760</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118601728</v>
+        <v>118601826</v>
       </c>
       <c r="B40" t="n">
-        <v>78227</v>
+        <v>78491</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4715,21 +4715,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4739,10 +4739,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466290</v>
+        <v>466453</v>
       </c>
       <c r="R40" t="n">
-        <v>6820662</v>
+        <v>6820379</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4801,10 +4801,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118601729</v>
+        <v>118601749</v>
       </c>
       <c r="B41" t="n">
-        <v>78227</v>
+        <v>78491</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4817,21 +4817,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4841,10 +4841,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>466487</v>
+        <v>466261</v>
       </c>
       <c r="R41" t="n">
-        <v>6820641</v>
+        <v>6821105</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4903,7 +4903,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118601745</v>
+        <v>118601747</v>
       </c>
       <c r="B42" t="n">
         <v>78491</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>466308</v>
+        <v>466278</v>
       </c>
       <c r="R42" t="n">
-        <v>6821040</v>
+        <v>6821064</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5005,10 +5005,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118601722</v>
+        <v>118601836</v>
       </c>
       <c r="B43" t="n">
-        <v>78228</v>
+        <v>78491</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5021,21 +5021,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466289</v>
+        <v>466454</v>
       </c>
       <c r="R43" t="n">
-        <v>6820603</v>
+        <v>6820333</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5107,7 +5107,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118601743</v>
+        <v>118601793</v>
       </c>
       <c r="B44" t="n">
         <v>78491</v>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466336</v>
+        <v>466430</v>
       </c>
       <c r="R44" t="n">
-        <v>6820998</v>
+        <v>6820757</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5209,10 +5209,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118601810</v>
+        <v>118601726</v>
       </c>
       <c r="B45" t="n">
-        <v>78491</v>
+        <v>78227</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5225,21 +5225,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5249,10 +5249,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466440</v>
+        <v>466331</v>
       </c>
       <c r="R45" t="n">
-        <v>6820675</v>
+        <v>6821018</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5311,10 +5311,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118601750</v>
+        <v>118601713</v>
       </c>
       <c r="B46" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5327,34 +5327,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466256</v>
+        <v>466317</v>
       </c>
       <c r="R46" t="n">
-        <v>6821102</v>
+        <v>6820668</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5387,6 +5395,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5413,7 +5426,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118601781</v>
+        <v>118601777</v>
       </c>
       <c r="B47" t="n">
         <v>78491</v>
@@ -5453,10 +5466,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466322</v>
+        <v>466261</v>
       </c>
       <c r="R47" t="n">
-        <v>6820686</v>
+        <v>6820701</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5515,7 +5528,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118601754</v>
+        <v>118601750</v>
       </c>
       <c r="B48" t="n">
         <v>78491</v>
@@ -5555,10 +5568,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>466257</v>
+        <v>466256</v>
       </c>
       <c r="R48" t="n">
-        <v>6821042</v>
+        <v>6821102</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5719,7 +5732,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118601812</v>
+        <v>118601802</v>
       </c>
       <c r="B50" t="n">
         <v>78491</v>
@@ -5759,10 +5772,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466454</v>
+        <v>466418</v>
       </c>
       <c r="R50" t="n">
-        <v>6820670</v>
+        <v>6820718</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5821,10 +5834,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118601699</v>
+        <v>118601751</v>
       </c>
       <c r="B51" t="n">
-        <v>90531</v>
+        <v>78491</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5837,21 +5850,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5861,10 +5874,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>466261</v>
+        <v>466237</v>
       </c>
       <c r="R51" t="n">
-        <v>6821105</v>
+        <v>6821090</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5923,7 +5936,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118601673</v>
+        <v>118601677</v>
       </c>
       <c r="B52" t="n">
         <v>79109</v>
@@ -5963,10 +5976,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>466480</v>
+        <v>466318</v>
       </c>
       <c r="R52" t="n">
-        <v>6820672</v>
+        <v>6820439</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6025,10 +6038,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118601664</v>
+        <v>118601666</v>
       </c>
       <c r="B53" t="n">
-        <v>78525</v>
+        <v>79109</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6041,21 +6054,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6065,10 +6078,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>466402</v>
+        <v>466233</v>
       </c>
       <c r="R53" t="n">
-        <v>6820391</v>
+        <v>6821097</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6127,7 +6140,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118601818</v>
+        <v>118601799</v>
       </c>
       <c r="B54" t="n">
         <v>78491</v>
@@ -6167,10 +6180,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>466307</v>
+        <v>466416</v>
       </c>
       <c r="R54" t="n">
-        <v>6820533</v>
+        <v>6820728</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6229,7 +6242,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118601768</v>
+        <v>118601773</v>
       </c>
       <c r="B55" t="n">
         <v>78491</v>
@@ -6269,10 +6282,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>466260</v>
+        <v>466222</v>
       </c>
       <c r="R55" t="n">
-        <v>6820919</v>
+        <v>6820731</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6331,7 +6344,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118601771</v>
+        <v>118601780</v>
       </c>
       <c r="B56" t="n">
         <v>78491</v>
@@ -6371,10 +6384,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>466259</v>
+        <v>466301</v>
       </c>
       <c r="R56" t="n">
-        <v>6820893</v>
+        <v>6820686</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6433,7 +6446,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118601814</v>
+        <v>118601817</v>
       </c>
       <c r="B57" t="n">
         <v>78491</v>
@@ -6473,10 +6486,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466476</v>
+        <v>466344</v>
       </c>
       <c r="R57" t="n">
-        <v>6820673</v>
+        <v>6820520</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6535,10 +6548,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118601700</v>
+        <v>118601834</v>
       </c>
       <c r="B58" t="n">
-        <v>78580</v>
+        <v>78491</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6547,25 +6560,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6575,10 +6588,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>466247</v>
+        <v>466471</v>
       </c>
       <c r="R58" t="n">
-        <v>6821087</v>
+        <v>6820336</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6637,10 +6650,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118601725</v>
+        <v>118601719</v>
       </c>
       <c r="B59" t="n">
-        <v>77428</v>
+        <v>78517</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6649,25 +6662,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228579</v>
+        <v>6434</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6677,10 +6690,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466297</v>
+        <v>466263</v>
       </c>
       <c r="R59" t="n">
-        <v>6820527</v>
+        <v>6820456</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6721,7 +6734,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6740,7 +6752,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118601773</v>
+        <v>118601801</v>
       </c>
       <c r="B60" t="n">
         <v>78491</v>
@@ -6780,10 +6792,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466222</v>
+        <v>466410</v>
       </c>
       <c r="R60" t="n">
-        <v>6820731</v>
+        <v>6820722</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6842,10 +6854,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118601796</v>
+        <v>118601688</v>
       </c>
       <c r="B61" t="n">
-        <v>78491</v>
+        <v>79080</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6858,21 +6870,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6882,10 +6894,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466413</v>
+        <v>466309</v>
       </c>
       <c r="R61" t="n">
-        <v>6820733</v>
+        <v>6820526</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6944,10 +6956,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118601752</v>
+        <v>118601660</v>
       </c>
       <c r="B62" t="n">
-        <v>78491</v>
+        <v>78525</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6960,21 +6972,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6984,10 +6996,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466250</v>
+        <v>466432</v>
       </c>
       <c r="R62" t="n">
-        <v>6821077</v>
+        <v>6820354</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7046,10 +7058,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118601671</v>
+        <v>118601815</v>
       </c>
       <c r="B63" t="n">
-        <v>79109</v>
+        <v>78491</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7062,21 +7074,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7086,10 +7098,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>466329</v>
+        <v>466490</v>
       </c>
       <c r="R63" t="n">
-        <v>6820672</v>
+        <v>6820635</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7148,10 +7160,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118601679</v>
+        <v>118601818</v>
       </c>
       <c r="B64" t="n">
-        <v>79109</v>
+        <v>78491</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7164,21 +7176,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7188,10 +7200,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466318</v>
+        <v>466307</v>
       </c>
       <c r="R64" t="n">
-        <v>6820464</v>
+        <v>6820533</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7250,10 +7262,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118601668</v>
+        <v>118601748</v>
       </c>
       <c r="B65" t="n">
-        <v>79109</v>
+        <v>78491</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7266,21 +7278,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7290,10 +7302,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>466198</v>
+        <v>466269</v>
       </c>
       <c r="R65" t="n">
-        <v>6820787</v>
+        <v>6821098</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7352,7 +7364,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118601809</v>
+        <v>118601806</v>
       </c>
       <c r="B66" t="n">
         <v>78491</v>
@@ -7392,10 +7404,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>466431</v>
+        <v>466422</v>
       </c>
       <c r="R66" t="n">
-        <v>6820682</v>
+        <v>6820680</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7454,10 +7466,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118601848</v>
+        <v>118601837</v>
       </c>
       <c r="B67" t="n">
-        <v>94520</v>
+        <v>78491</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7466,25 +7478,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7494,10 +7506,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466442</v>
+        <v>466436</v>
       </c>
       <c r="R67" t="n">
-        <v>6820579</v>
+        <v>6820340</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7556,10 +7568,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118601775</v>
+        <v>118601729</v>
       </c>
       <c r="B68" t="n">
-        <v>78491</v>
+        <v>78227</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7572,21 +7584,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7596,10 +7608,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466245</v>
+        <v>466487</v>
       </c>
       <c r="R68" t="n">
-        <v>6820718</v>
+        <v>6820641</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7658,10 +7670,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118601806</v>
+        <v>118601850</v>
       </c>
       <c r="B69" t="n">
-        <v>78491</v>
+        <v>78136</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7674,21 +7686,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7698,10 +7710,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466422</v>
+        <v>466318</v>
       </c>
       <c r="R69" t="n">
-        <v>6820680</v>
+        <v>6820439</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7760,7 +7772,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118601755</v>
+        <v>118601830</v>
       </c>
       <c r="B70" t="n">
         <v>78491</v>
@@ -7800,10 +7812,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466248</v>
+        <v>466471</v>
       </c>
       <c r="R70" t="n">
-        <v>6821008</v>
+        <v>6820355</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7862,10 +7874,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118601734</v>
+        <v>118601783</v>
       </c>
       <c r="B71" t="n">
-        <v>90529</v>
+        <v>78491</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7878,21 +7890,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7902,10 +7914,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466389</v>
+        <v>466420</v>
       </c>
       <c r="R71" t="n">
-        <v>6820384</v>
+        <v>6820743</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7964,10 +7976,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118601828</v>
+        <v>118601671</v>
       </c>
       <c r="B72" t="n">
-        <v>78491</v>
+        <v>79109</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7980,21 +7992,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8004,10 +8016,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466454</v>
+        <v>466329</v>
       </c>
       <c r="R72" t="n">
-        <v>6820362</v>
+        <v>6820672</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8066,10 +8078,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118601827</v>
+        <v>118601657</v>
       </c>
       <c r="B73" t="n">
-        <v>78491</v>
+        <v>78525</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8082,21 +8094,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8106,10 +8118,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>466466</v>
+        <v>466303</v>
       </c>
       <c r="R73" t="n">
-        <v>6820369</v>
+        <v>6820542</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8168,7 +8180,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118601808</v>
+        <v>118601766</v>
       </c>
       <c r="B74" t="n">
         <v>78491</v>
@@ -8208,10 +8220,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>466433</v>
+        <v>466247</v>
       </c>
       <c r="R74" t="n">
-        <v>6820675</v>
+        <v>6820929</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8270,7 +8282,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118601769</v>
+        <v>118601814</v>
       </c>
       <c r="B75" t="n">
         <v>78491</v>
@@ -8310,10 +8322,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>466252</v>
+        <v>466476</v>
       </c>
       <c r="R75" t="n">
-        <v>6820916</v>
+        <v>6820673</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8372,7 +8384,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118601779</v>
+        <v>118601808</v>
       </c>
       <c r="B76" t="n">
         <v>78491</v>
@@ -8412,10 +8424,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>466285</v>
+        <v>466433</v>
       </c>
       <c r="R76" t="n">
-        <v>6820690</v>
+        <v>6820675</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8474,10 +8486,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118601695</v>
+        <v>118601832</v>
       </c>
       <c r="B77" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8490,42 +8502,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>466298</v>
+        <v>466471</v>
       </c>
       <c r="R77" t="n">
-        <v>6820554</v>
+        <v>6820340</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8558,11 +8562,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8589,10 +8588,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118601850</v>
+        <v>118601728</v>
       </c>
       <c r="B78" t="n">
-        <v>78136</v>
+        <v>78227</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8605,21 +8604,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8629,10 +8628,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>466318</v>
+        <v>466290</v>
       </c>
       <c r="R78" t="n">
-        <v>6820439</v>
+        <v>6820662</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8691,10 +8690,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118601658</v>
+        <v>118601695</v>
       </c>
       <c r="B79" t="n">
-        <v>78525</v>
+        <v>57290</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8707,34 +8706,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>466276</v>
+        <v>466298</v>
       </c>
       <c r="R79" t="n">
-        <v>6820477</v>
+        <v>6820554</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8767,6 +8774,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8793,10 +8805,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118601706</v>
+        <v>118601684</v>
       </c>
       <c r="B80" t="n">
-        <v>57290</v>
+        <v>79080</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8809,42 +8821,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>466265</v>
+        <v>466268</v>
       </c>
       <c r="R80" t="n">
-        <v>6820475</v>
+        <v>6821079</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8877,11 +8881,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8908,10 +8907,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118601680</v>
+        <v>118601848</v>
       </c>
       <c r="B81" t="n">
-        <v>79109</v>
+        <v>94520</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8920,25 +8919,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8948,10 +8947,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>466464</v>
+        <v>466442</v>
       </c>
       <c r="R81" t="n">
-        <v>6820342</v>
+        <v>6820579</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9010,7 +9009,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118601846</v>
+        <v>118601776</v>
       </c>
       <c r="B82" t="n">
         <v>78491</v>
@@ -9050,10 +9049,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>466402</v>
+        <v>466252</v>
       </c>
       <c r="R82" t="n">
-        <v>6820391</v>
+        <v>6820713</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9112,10 +9111,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118601721</v>
+        <v>118601779</v>
       </c>
       <c r="B83" t="n">
-        <v>78228</v>
+        <v>78491</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9128,21 +9127,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9152,10 +9151,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>466487</v>
+        <v>466285</v>
       </c>
       <c r="R83" t="n">
-        <v>6820641</v>
+        <v>6820690</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9214,10 +9213,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118601792</v>
+        <v>118601682</v>
       </c>
       <c r="B84" t="n">
-        <v>78491</v>
+        <v>79109</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9230,21 +9229,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9254,10 +9253,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>466431</v>
+        <v>466381</v>
       </c>
       <c r="R84" t="n">
-        <v>6820760</v>
+        <v>6820326</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9316,7 +9315,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118601811</v>
+        <v>118601753</v>
       </c>
       <c r="B85" t="n">
         <v>78491</v>
@@ -9356,10 +9355,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>466447</v>
+        <v>466257</v>
       </c>
       <c r="R85" t="n">
-        <v>6820672</v>
+        <v>6821074</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9418,10 +9417,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118601720</v>
+        <v>118601715</v>
       </c>
       <c r="B86" t="n">
-        <v>78228</v>
+        <v>57290</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9434,34 +9433,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>466331</v>
+        <v>466440</v>
       </c>
       <c r="R86" t="n">
-        <v>6821018</v>
+        <v>6820684</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9494,6 +9501,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Två nyligen ringhackade granar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9520,10 +9532,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118601686</v>
+        <v>118601810</v>
       </c>
       <c r="B87" t="n">
-        <v>79080</v>
+        <v>78491</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9536,21 +9548,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9560,10 +9572,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>466290</v>
+        <v>466440</v>
       </c>
       <c r="R87" t="n">
-        <v>6820662</v>
+        <v>6820675</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9622,10 +9634,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118601677</v>
+        <v>118601699</v>
       </c>
       <c r="B88" t="n">
-        <v>79109</v>
+        <v>90531</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9638,21 +9650,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9662,10 +9674,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>466318</v>
+        <v>466261</v>
       </c>
       <c r="R88" t="n">
-        <v>6820439</v>
+        <v>6821105</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9724,10 +9736,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118601726</v>
+        <v>118601769</v>
       </c>
       <c r="B89" t="n">
-        <v>78227</v>
+        <v>78491</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9740,21 +9752,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9764,10 +9776,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>466331</v>
+        <v>466252</v>
       </c>
       <c r="R89" t="n">
-        <v>6821018</v>
+        <v>6820916</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9826,10 +9838,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118601657</v>
+        <v>118601811</v>
       </c>
       <c r="B90" t="n">
-        <v>78525</v>
+        <v>78491</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9842,21 +9854,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9866,10 +9878,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>466303</v>
+        <v>466447</v>
       </c>
       <c r="R90" t="n">
-        <v>6820542</v>
+        <v>6820672</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9928,7 +9940,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118601835</v>
+        <v>118601770</v>
       </c>
       <c r="B91" t="n">
         <v>78491</v>
@@ -9968,10 +9980,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>466455</v>
+        <v>466256</v>
       </c>
       <c r="R91" t="n">
-        <v>6820335</v>
+        <v>6820907</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10030,10 +10042,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118601776</v>
+        <v>118601734</v>
       </c>
       <c r="B92" t="n">
-        <v>78491</v>
+        <v>90529</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10046,21 +10058,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10070,10 +10082,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>466252</v>
+        <v>466389</v>
       </c>
       <c r="R92" t="n">
-        <v>6820713</v>
+        <v>6820384</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10132,7 +10144,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118601819</v>
+        <v>118601845</v>
       </c>
       <c r="B93" t="n">
         <v>78491</v>
@@ -10172,10 +10184,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>466294</v>
+        <v>466405</v>
       </c>
       <c r="R93" t="n">
-        <v>6820528</v>
+        <v>6820389</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10234,10 +10246,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118601845</v>
+        <v>118601683</v>
       </c>
       <c r="B94" t="n">
-        <v>78491</v>
+        <v>79080</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10250,21 +10262,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10274,10 +10286,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>466405</v>
+        <v>466307</v>
       </c>
       <c r="R94" t="n">
-        <v>6820389</v>
+        <v>6820562</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10318,6 +10330,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10336,10 +10349,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118601854</v>
+        <v>118601725</v>
       </c>
       <c r="B95" t="n">
-        <v>5166</v>
+        <v>77428</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10348,25 +10361,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100526</v>
+        <v>228579</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10376,10 +10389,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>466505</v>
+        <v>466297</v>
       </c>
       <c r="R95" t="n">
-        <v>6820638</v>
+        <v>6820527</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10420,6 +10433,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10438,7 +10452,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118601749</v>
+        <v>118601842</v>
       </c>
       <c r="B96" t="n">
         <v>78491</v>
@@ -10478,10 +10492,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>466261</v>
+        <v>466394</v>
       </c>
       <c r="R96" t="n">
-        <v>6821105</v>
+        <v>6820329</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10540,10 +10554,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118601793</v>
+        <v>118601669</v>
       </c>
       <c r="B97" t="n">
-        <v>78491</v>
+        <v>79109</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10556,21 +10570,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10580,10 +10594,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>466430</v>
+        <v>466233</v>
       </c>
       <c r="R97" t="n">
-        <v>6820757</v>
+        <v>6820720</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10642,7 +10656,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118601822</v>
+        <v>118601827</v>
       </c>
       <c r="B98" t="n">
         <v>78491</v>
@@ -10682,10 +10696,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>466341</v>
+        <v>466466</v>
       </c>
       <c r="R98" t="n">
-        <v>6820450</v>
+        <v>6820369</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10744,7 +10758,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118601834</v>
+        <v>118601833</v>
       </c>
       <c r="B99" t="n">
         <v>78491</v>
@@ -10784,10 +10798,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>466471</v>
+        <v>466472</v>
       </c>
       <c r="R99" t="n">
-        <v>6820336</v>
+        <v>6820338</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10846,10 +10860,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118601672</v>
+        <v>118601824</v>
       </c>
       <c r="B100" t="n">
-        <v>79109</v>
+        <v>78491</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10862,21 +10876,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10886,10 +10900,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>466343</v>
+        <v>466445</v>
       </c>
       <c r="R100" t="n">
-        <v>6820677</v>
+        <v>6820355</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10948,7 +10962,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118601702</v>
+        <v>118601706</v>
       </c>
       <c r="B101" t="n">
         <v>57290</v>
@@ -10986,7 +11000,7 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -10996,10 +11010,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>466455</v>
+        <v>466265</v>
       </c>
       <c r="R101" t="n">
-        <v>6820642</v>
+        <v>6820475</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11036,7 +11050,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Färska ringhack (gran)</t>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11063,10 +11077,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118601698</v>
+        <v>118601704</v>
       </c>
       <c r="B102" t="n">
-        <v>57443</v>
+        <v>57290</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11079,34 +11093,42 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>466319</v>
+        <v>466415</v>
       </c>
       <c r="R102" t="n">
-        <v>6820440</v>
+        <v>6820750</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11139,6 +11161,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11165,10 +11192,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118601683</v>
+        <v>118601664</v>
       </c>
       <c r="B103" t="n">
-        <v>79080</v>
+        <v>78525</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11181,21 +11208,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11205,10 +11232,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>466307</v>
+        <v>466402</v>
       </c>
       <c r="R103" t="n">
-        <v>6820562</v>
+        <v>6820391</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11249,7 +11276,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11268,10 +11294,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118601825</v>
+        <v>118601658</v>
       </c>
       <c r="B104" t="n">
-        <v>78491</v>
+        <v>78525</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11284,21 +11310,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11308,10 +11334,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>466450</v>
+        <v>466276</v>
       </c>
       <c r="R104" t="n">
-        <v>6820356</v>
+        <v>6820477</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11370,7 +11396,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118601791</v>
+        <v>118601742</v>
       </c>
       <c r="B105" t="n">
         <v>78491</v>
@@ -11410,10 +11436,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>466470</v>
+        <v>466344</v>
       </c>
       <c r="R105" t="n">
-        <v>6820774</v>
+        <v>6820993</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11472,10 +11498,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118601663</v>
+        <v>118601778</v>
       </c>
       <c r="B106" t="n">
-        <v>78525</v>
+        <v>78491</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11488,21 +11514,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11512,10 +11538,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>466405</v>
+        <v>466283</v>
       </c>
       <c r="R106" t="n">
-        <v>6820390</v>
+        <v>6820697</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11574,7 +11600,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118601783</v>
+        <v>118601812</v>
       </c>
       <c r="B107" t="n">
         <v>78491</v>
@@ -11614,10 +11640,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>466420</v>
+        <v>466454</v>
       </c>
       <c r="R107" t="n">
-        <v>6820743</v>
+        <v>6820670</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11676,10 +11702,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>118601777</v>
+        <v>118601674</v>
       </c>
       <c r="B108" t="n">
-        <v>78491</v>
+        <v>79109</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11692,21 +11718,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11716,10 +11742,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>466261</v>
+        <v>466487</v>
       </c>
       <c r="R108" t="n">
-        <v>6820701</v>
+        <v>6820639</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11778,7 +11804,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>118601830</v>
+        <v>118601844</v>
       </c>
       <c r="B109" t="n">
         <v>78491</v>
@@ -11818,10 +11844,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>466471</v>
+        <v>466418</v>
       </c>
       <c r="R109" t="n">
-        <v>6820355</v>
+        <v>6820392</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11880,7 +11906,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>118601799</v>
+        <v>118601819</v>
       </c>
       <c r="B110" t="n">
         <v>78491</v>
@@ -11920,10 +11946,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>466416</v>
+        <v>466294</v>
       </c>
       <c r="R110" t="n">
-        <v>6820728</v>
+        <v>6820528</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11982,7 +12008,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118601817</v>
+        <v>118601745</v>
       </c>
       <c r="B111" t="n">
         <v>78491</v>
@@ -12022,10 +12048,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>466344</v>
+        <v>466308</v>
       </c>
       <c r="R111" t="n">
-        <v>6820520</v>
+        <v>6821040</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12084,10 +12110,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118601661</v>
+        <v>118601731</v>
       </c>
       <c r="B112" t="n">
-        <v>78525</v>
+        <v>78227</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12100,21 +12126,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12124,10 +12150,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>466471</v>
+        <v>466306</v>
       </c>
       <c r="R112" t="n">
-        <v>6820336</v>
+        <v>6820562</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12186,10 +12212,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118601747</v>
+        <v>118601855</v>
       </c>
       <c r="B113" t="n">
-        <v>78491</v>
+        <v>5166</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12198,25 +12224,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12226,10 +12252,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>466278</v>
+        <v>466454</v>
       </c>
       <c r="R113" t="n">
-        <v>6821064</v>
+        <v>6820379</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12288,7 +12314,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>118601772</v>
+        <v>118601825</v>
       </c>
       <c r="B114" t="n">
         <v>78491</v>
@@ -12328,10 +12354,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>466213</v>
+        <v>466450</v>
       </c>
       <c r="R114" t="n">
-        <v>6820752</v>
+        <v>6820356</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12390,7 +12416,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>118601824</v>
+        <v>118601744</v>
       </c>
       <c r="B115" t="n">
         <v>78491</v>
@@ -12430,10 +12456,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>466445</v>
+        <v>466316</v>
       </c>
       <c r="R115" t="n">
-        <v>6820355</v>
+        <v>6821025</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12492,10 +12518,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118601684</v>
+        <v>118601846</v>
       </c>
       <c r="B116" t="n">
-        <v>79080</v>
+        <v>78491</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12508,21 +12534,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12532,10 +12558,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>466268</v>
+        <v>466402</v>
       </c>
       <c r="R116" t="n">
-        <v>6821079</v>
+        <v>6820391</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12594,10 +12620,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>118601719</v>
+        <v>118601800</v>
       </c>
       <c r="B117" t="n">
-        <v>78517</v>
+        <v>78491</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12606,25 +12632,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12634,10 +12660,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>466263</v>
+        <v>466414</v>
       </c>
       <c r="R117" t="n">
-        <v>6820456</v>
+        <v>6820727</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12696,7 +12722,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>118601753</v>
+        <v>118601796</v>
       </c>
       <c r="B118" t="n">
         <v>78491</v>
@@ -12736,10 +12762,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>466257</v>
+        <v>466413</v>
       </c>
       <c r="R118" t="n">
-        <v>6821074</v>
+        <v>6820733</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12798,10 +12824,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118601820</v>
+        <v>118601679</v>
       </c>
       <c r="B119" t="n">
-        <v>78491</v>
+        <v>79109</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12814,21 +12840,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12838,10 +12864,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>466299</v>
+        <v>466318</v>
       </c>
       <c r="R119" t="n">
-        <v>6820534</v>
+        <v>6820464</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12900,7 +12926,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118601837</v>
+        <v>118601790</v>
       </c>
       <c r="B120" t="n">
         <v>78491</v>
@@ -12940,10 +12966,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>466436</v>
+        <v>466453</v>
       </c>
       <c r="R120" t="n">
-        <v>6820340</v>
+        <v>6820774</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13002,7 +13028,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118601813</v>
+        <v>118601791</v>
       </c>
       <c r="B121" t="n">
         <v>78491</v>
@@ -13042,10 +13068,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>466463</v>
+        <v>466470</v>
       </c>
       <c r="R121" t="n">
-        <v>6820672</v>
+        <v>6820774</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13104,10 +13130,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118601731</v>
+        <v>118601685</v>
       </c>
       <c r="B122" t="n">
-        <v>78227</v>
+        <v>79080</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13120,21 +13146,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13144,10 +13170,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>466306</v>
+        <v>466265</v>
       </c>
       <c r="R122" t="n">
-        <v>6820562</v>
+        <v>6821100</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13206,10 +13232,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118601682</v>
+        <v>118601721</v>
       </c>
       <c r="B123" t="n">
-        <v>79109</v>
+        <v>78228</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13222,21 +13248,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13246,10 +13272,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>466381</v>
+        <v>466487</v>
       </c>
       <c r="R123" t="n">
-        <v>6820326</v>
+        <v>6820641</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13308,10 +13334,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118601688</v>
+        <v>118601659</v>
       </c>
       <c r="B124" t="n">
-        <v>79080</v>
+        <v>78525</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13324,21 +13350,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13348,10 +13374,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>466309</v>
+        <v>466258</v>
       </c>
       <c r="R124" t="n">
-        <v>6820526</v>
+        <v>6820476</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13410,10 +13436,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118601831</v>
+        <v>118601654</v>
       </c>
       <c r="B125" t="n">
-        <v>78491</v>
+        <v>78525</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13426,21 +13452,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13450,10 +13476,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>466463</v>
+        <v>466318</v>
       </c>
       <c r="R125" t="n">
-        <v>6820344</v>
+        <v>6820669</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13512,10 +13538,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118601690</v>
+        <v>118601772</v>
       </c>
       <c r="B126" t="n">
-        <v>79080</v>
+        <v>78491</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13528,21 +13554,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13552,10 +13578,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>466438</v>
+        <v>466213</v>
       </c>
       <c r="R126" t="n">
-        <v>6820356</v>
+        <v>6820752</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13614,10 +13640,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118601687</v>
+        <v>118601672</v>
       </c>
       <c r="B127" t="n">
-        <v>79080</v>
+        <v>79109</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13630,21 +13656,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13654,10 +13680,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>466330</v>
+        <v>466343</v>
       </c>
       <c r="R127" t="n">
-        <v>6820551</v>
+        <v>6820677</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13716,10 +13742,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118601704</v>
+        <v>118601680</v>
       </c>
       <c r="B128" t="n">
-        <v>57290</v>
+        <v>79109</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13732,42 +13758,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>466415</v>
+        <v>466464</v>
       </c>
       <c r="R128" t="n">
-        <v>6820750</v>
+        <v>6820342</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13800,11 +13818,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13831,7 +13844,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118601746</v>
+        <v>118601807</v>
       </c>
       <c r="B129" t="n">
         <v>78491</v>
@@ -13871,10 +13884,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>466284</v>
+        <v>466428</v>
       </c>
       <c r="R129" t="n">
-        <v>6821043</v>
+        <v>6820671</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13933,10 +13946,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118601780</v>
+        <v>118601724</v>
       </c>
       <c r="B130" t="n">
-        <v>78491</v>
+        <v>79572</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13949,21 +13962,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13973,10 +13986,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>466301</v>
+        <v>466276</v>
       </c>
       <c r="R130" t="n">
-        <v>6820686</v>
+        <v>6821068</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14035,10 +14048,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118601833</v>
+        <v>118601732</v>
       </c>
       <c r="B131" t="n">
-        <v>78491</v>
+        <v>78227</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14051,21 +14064,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14075,10 +14088,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>466472</v>
+        <v>466287</v>
       </c>
       <c r="R131" t="n">
-        <v>6820338</v>
+        <v>6820603</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14137,7 +14150,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118601832</v>
+        <v>118601809</v>
       </c>
       <c r="B132" t="n">
         <v>78491</v>
@@ -14177,10 +14190,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>466471</v>
+        <v>466431</v>
       </c>
       <c r="R132" t="n">
-        <v>6820340</v>
+        <v>6820682</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14239,7 +14252,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118601802</v>
+        <v>118601828</v>
       </c>
       <c r="B133" t="n">
         <v>78491</v>
@@ -14279,10 +14292,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>466418</v>
+        <v>466454</v>
       </c>
       <c r="R133" t="n">
-        <v>6820718</v>
+        <v>6820362</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14341,7 +14354,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118601844</v>
+        <v>118601746</v>
       </c>
       <c r="B134" t="n">
         <v>78491</v>
@@ -14381,10 +14394,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>466418</v>
+        <v>466284</v>
       </c>
       <c r="R134" t="n">
-        <v>6820392</v>
+        <v>6821043</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14443,10 +14456,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118601659</v>
+        <v>118601703</v>
       </c>
       <c r="B135" t="n">
-        <v>78525</v>
+        <v>57290</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14459,34 +14472,42 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>466258</v>
+        <v>466470</v>
       </c>
       <c r="R135" t="n">
-        <v>6820476</v>
+        <v>6820354</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14519,6 +14540,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14545,10 +14571,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118601801</v>
+        <v>118601661</v>
       </c>
       <c r="B136" t="n">
-        <v>78491</v>
+        <v>78525</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14561,21 +14587,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14585,10 +14611,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>466410</v>
+        <v>466471</v>
       </c>
       <c r="R136" t="n">
-        <v>6820722</v>
+        <v>6820336</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14647,7 +14673,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118601840</v>
+        <v>118601781</v>
       </c>
       <c r="B137" t="n">
         <v>78491</v>
@@ -14687,10 +14713,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>466421</v>
+        <v>466322</v>
       </c>
       <c r="R137" t="n">
-        <v>6820332</v>
+        <v>6820686</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14749,10 +14775,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118601727</v>
+        <v>118601775</v>
       </c>
       <c r="B138" t="n">
-        <v>78227</v>
+        <v>78491</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14765,21 +14791,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14789,10 +14815,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>466269</v>
+        <v>466245</v>
       </c>
       <c r="R138" t="n">
-        <v>6821081</v>
+        <v>6820718</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14851,10 +14877,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118601732</v>
+        <v>118601822</v>
       </c>
       <c r="B139" t="n">
-        <v>78227</v>
+        <v>78491</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14867,21 +14893,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14891,10 +14917,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>466287</v>
+        <v>466341</v>
       </c>
       <c r="R139" t="n">
-        <v>6820603</v>
+        <v>6820450</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14953,10 +14979,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118601666</v>
+        <v>118601722</v>
       </c>
       <c r="B140" t="n">
-        <v>79109</v>
+        <v>78228</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14969,21 +14995,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14993,10 +15019,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>466233</v>
+        <v>466289</v>
       </c>
       <c r="R140" t="n">
-        <v>6821097</v>
+        <v>6820603</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15055,10 +15081,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118601696</v>
+        <v>118601687</v>
       </c>
       <c r="B141" t="n">
-        <v>57290</v>
+        <v>79080</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15071,42 +15097,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>466389</v>
+        <v>466330</v>
       </c>
       <c r="R141" t="n">
-        <v>6820384</v>
+        <v>6820551</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15139,11 +15157,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Äldre bo (2-3 år gammalt)</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15170,7 +15183,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118601826</v>
+        <v>118601771</v>
       </c>
       <c r="B142" t="n">
         <v>78491</v>
@@ -15210,10 +15223,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>466453</v>
+        <v>466259</v>
       </c>
       <c r="R142" t="n">
-        <v>6820379</v>
+        <v>6820893</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15272,7 +15285,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118601790</v>
+        <v>118601755</v>
       </c>
       <c r="B143" t="n">
         <v>78491</v>
@@ -15312,10 +15325,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>466453</v>
+        <v>466248</v>
       </c>
       <c r="R143" t="n">
-        <v>6820774</v>
+        <v>6821008</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15374,7 +15387,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118601823</v>
+        <v>118601820</v>
       </c>
       <c r="B144" t="n">
         <v>78491</v>
@@ -15414,10 +15427,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>466416</v>
+        <v>466299</v>
       </c>
       <c r="R144" t="n">
-        <v>6820391</v>
+        <v>6820534</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15476,10 +15489,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118601843</v>
+        <v>118601673</v>
       </c>
       <c r="B145" t="n">
-        <v>78491</v>
+        <v>79109</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15492,21 +15505,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15516,10 +15529,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>466412</v>
+        <v>466480</v>
       </c>
       <c r="R145" t="n">
-        <v>6820369</v>
+        <v>6820672</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15578,7 +15591,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118601751</v>
+        <v>118601823</v>
       </c>
       <c r="B146" t="n">
         <v>78491</v>
@@ -15618,10 +15631,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>466237</v>
+        <v>466416</v>
       </c>
       <c r="R146" t="n">
-        <v>6821090</v>
+        <v>6820391</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15680,10 +15693,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118601730</v>
+        <v>118601690</v>
       </c>
       <c r="B147" t="n">
-        <v>78227</v>
+        <v>79080</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15696,21 +15709,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15720,10 +15733,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>466330</v>
+        <v>466438</v>
       </c>
       <c r="R147" t="n">
-        <v>6820558</v>
+        <v>6820356</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15782,10 +15795,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>118601715</v>
+        <v>118601720</v>
       </c>
       <c r="B148" t="n">
-        <v>57290</v>
+        <v>78228</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15798,42 +15811,34 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>466440</v>
+        <v>466331</v>
       </c>
       <c r="R148" t="n">
-        <v>6820684</v>
+        <v>6821018</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15866,11 +15871,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Två nyligen ringhackade granar</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15897,7 +15897,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118601800</v>
+        <v>118601813</v>
       </c>
       <c r="B149" t="n">
         <v>78491</v>
@@ -15937,10 +15937,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>466414</v>
+        <v>466463</v>
       </c>
       <c r="R149" t="n">
-        <v>6820727</v>
+        <v>6820672</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15999,7 +15999,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118601774</v>
+        <v>118601743</v>
       </c>
       <c r="B150" t="n">
         <v>78491</v>
@@ -16039,10 +16039,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>466223</v>
+        <v>466336</v>
       </c>
       <c r="R150" t="n">
-        <v>6820728</v>
+        <v>6820998</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16101,7 +16101,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118601778</v>
+        <v>118601843</v>
       </c>
       <c r="B151" t="n">
         <v>78491</v>
@@ -16141,10 +16141,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>466283</v>
+        <v>466412</v>
       </c>
       <c r="R151" t="n">
-        <v>6820697</v>
+        <v>6820369</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16203,10 +16203,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118601842</v>
+        <v>118601663</v>
       </c>
       <c r="B152" t="n">
-        <v>78491</v>
+        <v>78525</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16219,21 +16219,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16243,10 +16243,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>466394</v>
+        <v>466405</v>
       </c>
       <c r="R152" t="n">
-        <v>6820329</v>
+        <v>6820390</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16305,10 +16305,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>118601654</v>
+        <v>118601698</v>
       </c>
       <c r="B153" t="n">
-        <v>78525</v>
+        <v>57443</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16321,21 +16321,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>185</v>
+        <v>103021</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16345,10 +16345,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>466318</v>
+        <v>466319</v>
       </c>
       <c r="R153" t="n">
-        <v>6820669</v>
+        <v>6820440</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16407,7 +16407,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118601815</v>
+        <v>118601765</v>
       </c>
       <c r="B154" t="n">
         <v>78491</v>
@@ -16447,10 +16447,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>466490</v>
+        <v>466239</v>
       </c>
       <c r="R154" t="n">
-        <v>6820635</v>
+        <v>6820936</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16509,7 +16509,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>118601748</v>
+        <v>118601768</v>
       </c>
       <c r="B155" t="n">
         <v>78491</v>
@@ -16549,10 +16549,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>466269</v>
+        <v>466260</v>
       </c>
       <c r="R155" t="n">
-        <v>6821098</v>
+        <v>6820919</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16611,7 +16611,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>118601836</v>
+        <v>118601774</v>
       </c>
       <c r="B156" t="n">
         <v>78491</v>
@@ -16651,10 +16651,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>466454</v>
+        <v>466223</v>
       </c>
       <c r="R156" t="n">
-        <v>6820333</v>
+        <v>6820728</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16713,10 +16713,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>118601669</v>
+        <v>118601700</v>
       </c>
       <c r="B157" t="n">
-        <v>79109</v>
+        <v>78580</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16725,25 +16725,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16753,10 +16753,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>466233</v>
+        <v>466247</v>
       </c>
       <c r="R157" t="n">
-        <v>6820720</v>
+        <v>6821087</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16815,10 +16815,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>118601703</v>
+        <v>118601727</v>
       </c>
       <c r="B158" t="n">
-        <v>57290</v>
+        <v>78227</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16831,42 +16831,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>466470</v>
+        <v>466269</v>
       </c>
       <c r="R158" t="n">
-        <v>6820354</v>
+        <v>6821081</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16899,11 +16891,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2024-07-20</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16930,10 +16917,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>118601765</v>
+        <v>118601702</v>
       </c>
       <c r="B159" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16946,34 +16933,42 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Eberget Östra, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>466239</v>
+        <v>466455</v>
       </c>
       <c r="R159" t="n">
-        <v>6820936</v>
+        <v>6820642</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17006,6 +17001,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2024-07-20</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17032,10 +17032,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>118601770</v>
+        <v>118601854</v>
       </c>
       <c r="B160" t="n">
-        <v>78491</v>
+        <v>5166</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17044,25 +17044,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17072,10 +17072,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>466256</v>
+        <v>466505</v>
       </c>
       <c r="R160" t="n">
-        <v>6820907</v>
+        <v>6820638</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17134,10 +17134,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>118601724</v>
+        <v>118601686</v>
       </c>
       <c r="B161" t="n">
-        <v>79572</v>
+        <v>79080</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17150,21 +17150,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17174,10 +17174,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>466276</v>
+        <v>466290</v>
       </c>
       <c r="R161" t="n">
-        <v>6821068</v>
+        <v>6820662</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>

--- a/artfynd/A 36883-2023 artfynd.xlsx
+++ b/artfynd/A 36883-2023 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>111941651</v>
       </c>
       <c r="B6" t="n">
-        <v>56430</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466415</v>
+        <v>466416</v>
       </c>
       <c r="R6" t="n">
         <v>6820719</v>
@@ -2381,7 +2381,7 @@
         <v>111941765</v>
       </c>
       <c r="B18" t="n">
-        <v>56430</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>111941831</v>
       </c>
       <c r="B22" t="n">
-        <v>56430</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>111941313</v>
       </c>
       <c r="B28" t="n">
-        <v>56430</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>111941668</v>
       </c>
       <c r="B29" t="n">
-        <v>56430</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>118601695</v>
       </c>
       <c r="B64" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>118601706</v>
       </c>
       <c r="B77" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>118601703</v>
       </c>
       <c r="B78" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>118601713</v>
       </c>
       <c r="B85" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>118601702</v>
       </c>
       <c r="B86" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>118601696</v>
       </c>
       <c r="B92" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>118601704</v>
       </c>
       <c r="B108" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>118601715</v>
       </c>
       <c r="B129" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>

--- a/artfynd/A 36883-2023 artfynd.xlsx
+++ b/artfynd/A 36883-2023 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>111941651</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>111941765</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>111941831</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         <v>111941313</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>111941668</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>118601695</v>
       </c>
       <c r="B64" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>118601706</v>
       </c>
       <c r="B77" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>118601703</v>
       </c>
       <c r="B78" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>118601713</v>
       </c>
       <c r="B85" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>118601702</v>
       </c>
       <c r="B86" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>118601696</v>
       </c>
       <c r="B92" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>118601704</v>
       </c>
       <c r="B108" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>118601715</v>
       </c>
       <c r="B129" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
